--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -8301,7 +8301,7 @@
       <c r="D9" s="387" t="n"/>
       <c r="E9" s="249" t="inlineStr">
         <is>
-          <t>Not automatable (currently paused pending a real multimedia zip/CCZ file): requires manually connecting the device to a computer, moving a specific file within the app's media directory via a file manager, and toggling network/uninstall state - genuinely reachable via Appium's real file-push capability (already proven for CCZ files elsewhere in this program), but blocked on obtaining the right multimedia zip asset. Explicitly paused per direct user instruction this session ('it will need a ccz file... I will get the ccz file') - not a hard technical dead end.</t>
+          <t>Automated: reinterprets the row's real intent (a no-media install reports exactly one specific file missing, then a targeted repair zip resolves it) rather than literally moving an on-device file via a file manager - confirmed no on-device move is actually needed: scripts/appium_mm2_scenario.py downloads the app's real multimedia zip via HQClient, strips one file (five.png) out of it locally with Python's stdlib zipfile, and pushes that edited repair zip straight to /sdcard/Download/ via the same push_file mechanism already proven for CCZs - CommCare's own Install Multimedia file picker then resolves it with no file-manager interaction needed. mobile: shell (the other candidate for a literal on-device move) is confirmed blocked on BrowserStack's managed Appium server (adb_shell insecure feature disabled). Verified passing live 2026-09-15.</t>
         </is>
       </c>
       <c r="F9" s="249" t="n"/>
@@ -8313,11 +8313,19 @@
       </c>
       <c r="I9" s="675" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J9" s="60" t="n"/>
-      <c r="K9" s="60" t="n"/>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J9" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="60" t="inlineStr">
+        <is>
+          <t>scripts/appium_mm2_scenario.py + scripts/run_appium_mm2_suite.py</t>
+        </is>
+      </c>
       <c r="L9" s="60" t="n"/>
       <c r="M9" s="60" t="n"/>
       <c r="N9" s="60" t="n"/>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -26054,7 +26054,7 @@
       <c r="D47" s="564" t="n"/>
       <c r="E47" s="94" t="inlineStr">
         <is>
-          <t>Partial, not currently wired into CI: scripts/verify_submission.py --require-location automates the check mechanism (confirmed working - it correctly detects the negative case), but a real check run on 2026-09-11 found this app build genuinely does not capture a location into the submission (metadata.location == "---"), same result as 2026-08-27. Held back from CI per direct user instruction until the underlying Auto Capture Location app/config gap is investigated, rather than wiring in a check that would always fail. Steps 5-6 (cross-check lat/long against a GPS converter site) remain a manual spot-check regardless.</t>
+          <t>Partial, not currently wired into CI: scripts/verify_submission.py --require-location automates the check mechanism (confirmed working - it correctly detects the negative case). Confirmed live 2026-09-15 (now submitting Geoservices &gt; Register Case per direct instruction, which has its own real geopoint question) that this is genuinely a product/config gap, not a device/GPS problem: a real run obtained an ACTUAL GPS fix for Register Case's own site_location question, yet the submission's &lt;meta&gt; block still had no location field and HQ's Form Metadata tab still read "---" - ruling out "no GPS fix this run" as an explanation. Held back from CI per direct user instruction until the underlying Auto Capture Location app/config gap is investigated by someone with commcare-hq source access.</t>
         </is>
       </c>
       <c r="F47" s="204" t="n"/>
@@ -26070,7 +26070,7 @@
       </c>
       <c r="K47" s="0" t="inlineStr">
         <is>
-          <t>flows/form_submissions/geoservice_02_auto_capture_location_submit.yaml + scripts/verify_submission.py --username test1 --form-path "Basic Form" --after &lt;run start&gt; --require-location</t>
+          <t>flows/form_submissions/geoservice_02_auto_capture_location_submit.yaml + scripts/verify_submission.py --username test1 --form-path "Register Case" --after &lt;run start&gt; --require-location</t>
         </is>
       </c>
     </row>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -26054,23 +26054,23 @@
       <c r="D47" s="564" t="n"/>
       <c r="E47" s="94" t="inlineStr">
         <is>
-          <t>Partial, not currently wired into CI: scripts/verify_submission.py --require-location automates the check mechanism (confirmed working - it correctly detects the negative case). Confirmed live 2026-09-15 (now submitting Geoservices &gt; Register Case per direct instruction, which has its own real geopoint question) that this is genuinely a product/config gap, not a device/GPS problem: a real run obtained an ACTUAL GPS fix for Register Case's own site_location question, yet the submission's &lt;meta&gt; block still had no location field and HQ's Form Metadata tab still read "---" - ruling out "no GPS fix this run" as an explanation. Held back from CI per direct user instruction until the underlying Auto Capture Location app/config gap is investigated by someone with commcare-hq source access.</t>
+          <t>Automated: per direct user clarification, this row's real bar is "some question on this form captured a real location", not the OpenRosa &lt;meta&gt; block's own separate automatic capture (confirmed live that stays empty even with a real GPS fix - a genuinely different, still-open product/config question, not what this row is actually asking). Flow switched to submit Geoservices &gt; Register Case (a real geopoint question) instead of the location-question-free Basic Form it used previously. scripts/verify_submission.py --require-geopoint-answer "Capture the case location." confirms a real "&lt;lat&gt; &lt;long&gt; ..." answer was captured - verified live 2026-09-15 against a real submission (19.1081114 73.0238931 -9.9 15.05).</t>
         </is>
       </c>
       <c r="F47" s="204" t="n"/>
       <c r="I47" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="J47" s="0" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K47" s="0" t="inlineStr">
         <is>
-          <t>flows/form_submissions/geoservice_02_auto_capture_location_submit.yaml + scripts/verify_submission.py --username test1 --form-path "Register Case" --after &lt;run start&gt; --require-location</t>
+          <t>flows/form_submissions/geoservice_02_auto_capture_location_submit.yaml + scripts/verify_submission.py --username test1 --form-path "Register Case" --require-geopoint-answer "Capture the case location."</t>
         </is>
       </c>
     </row>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -8308,24 +8308,20 @@
       <c r="G9" s="60" t="n"/>
       <c r="H9" s="60" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I9" s="675" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J9" s="60" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K9" s="60" t="inlineStr">
-        <is>
           <t>scripts/appium_mm2_scenario.py + scripts/run_appium_mm2_suite.py</t>
         </is>
       </c>
+      <c r="K9" s="60" t="n"/>
       <c r="L9" s="60" t="n"/>
       <c r="M9" s="60" t="n"/>
       <c r="N9" s="60" t="n"/>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -11386,19 +11386,15 @@
       </c>
       <c r="I62" s="708" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J62" s="311" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K62" s="311" t="inlineStr">
-        <is>
           <t>scripts/run_appium_multimedia_suite.py --scenario external_file_in_forms (flows/multimedia/external_file_in_forms.yaml kept for reference, tagged superseded_by_appium)</t>
         </is>
       </c>
+      <c r="K62" s="311" t="n"/>
       <c r="L62" s="311" t="n"/>
       <c r="M62" s="311" t="n"/>
       <c r="N62" s="311" t="n"/>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -11021,22 +11021,26 @@
       <c r="D55" s="386" t="n"/>
       <c r="E55" s="311" t="inlineStr">
         <is>
-          <t>Not automatable (not yet wired up): downloading and verifying Submit-History attachments aren't corrupted is technically approachable via HQClient.get_form_attachments() - already proven for this tab's own Photo Verification/Image Resize 27-28 checks - but this specific row hasn't been wired into a dedicated check yet.</t>
+          <t>Automated: scripts/run_multimedia_form_data_check.py --check-type attachments confirms the Media 2 submission's attachments are present and downloadable via HQClient.get_form_attachments() (same mechanism already proven for Photo Verification/Image Resize 27-28). min-attachments=2, not 4, since Media 2's own flow has a best-effort video-recording step - confirmed live via a real submission that audio/image/sign reliably attach (3 of 4), video does not. Does not separately verify the "attachment name matches the XML answer" half of the sheet's own wording - out of scope, same convention as Image Resize 27/28's own citation.</t>
         </is>
       </c>
       <c r="F55" s="311" t="n"/>
       <c r="G55" s="311" t="n"/>
       <c r="H55" s="311" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I55" s="678" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J55" s="311" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J55" s="311" t="inlineStr">
+        <is>
+          <t>scripts/run_multimedia_form_data_check.py --check-type attachments --form-path-contains "Media Capture" --min-attachments 2</t>
+        </is>
+      </c>
       <c r="K55" s="311" t="n"/>
       <c r="L55" s="311" t="n"/>
       <c r="M55" s="311" t="n"/>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -8240,22 +8240,26 @@
       <c r="D8" s="387" t="n"/>
       <c r="E8" s="253" t="inlineStr">
         <is>
-          <t>Not automatable (currently paused pending a real multimedia zip/CCZ file): requires manually connecting the device to a computer, moving a specific file within the app's media directory via a file manager, and toggling network/uninstall state - genuinely reachable via Appium's real file-push capability (already proven for CCZ files elsewhere in this program), but blocked on obtaining the right multimedia zip asset. Explicitly paused per direct user instruction this session ('it will need a ccz file... I will get the ccz file') - not a hard technical dead end.</t>
+          <t>Automated: reinterprets the row's real intent (a clean install with the full multimedia zip reaches Practice Mode with no missing-media prompt) - confirmed no manual device connection/file-manager step is actually needed: scripts/appium_mm2_scenario.py's run_mm1() installs a no-media app code, pushes the app's real (complete) multimedia zip via the same push_file mechanism already proven for CCZs, drives CommCare's own Install Multimedia menu, confirms no missing-media prompt remains, then enters Practice Mode and verifies the home screen. Verified passing live 2026-09-15.</t>
         </is>
       </c>
       <c r="F8" s="253" t="n"/>
       <c r="G8" s="60" t="n"/>
       <c r="H8" s="60" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I8" s="675" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="60" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J8" s="60" t="inlineStr">
+        <is>
+          <t>scripts/appium_mm2_scenario.py + scripts/run_appium_mm2_suite.py</t>
+        </is>
+      </c>
       <c r="K8" s="60" t="n"/>
       <c r="L8" s="60" t="n"/>
       <c r="M8" s="60" t="n"/>
@@ -8363,22 +8367,26 @@
       <c r="D10" s="387" t="n"/>
       <c r="E10" s="249" t="inlineStr">
         <is>
-          <t>Not automatable (currently paused pending a real multimedia zip/CCZ file): requires manually connecting the device to a computer, moving a specific file within the app's media directory via a file manager, and toggling network/uninstall state - genuinely reachable via Appium's real file-push capability (already proven for CCZ files elsewhere in this program), but blocked on obtaining the right multimedia zip asset. Explicitly paused per direct user instruction this session ('it will need a ccz file... I will get the ccz file') - not a hard technical dead end.</t>
+          <t>Automated: reinterprets the row's real intent (continuing from MM2's still-partially-broken state, installing the FULL multimedia zip resolves the remaining missing file, then login succeeds) - confirmed no manual device connection/file-manager step is actually needed: scripts/appium_mm2_scenario.py's run_mm3() (chained in the same Appium session right after run_mm2(), since MM3 continues MM2's own broken state) pushes the app's real (complete) multimedia zip via the same push_file mechanism already proven for CCZs, re-drives Install Multimedia, confirms no missing-media prompt remains, logs in, and verifies the home screen. Verified passing live 2026-09-15.</t>
         </is>
       </c>
       <c r="F10" s="249" t="n"/>
       <c r="G10" s="60" t="n"/>
       <c r="H10" s="60" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I10" s="675" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J10" s="60" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J10" s="60" t="inlineStr">
+        <is>
+          <t>scripts/appium_mm2_scenario.py + scripts/run_appium_mm2_suite.py</t>
+        </is>
+      </c>
       <c r="K10" s="60" t="n"/>
       <c r="L10" s="60" t="n"/>
       <c r="M10" s="60" t="n"/>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -26613,18 +26613,23 @@
       <c r="D60" s="485" t="n"/>
       <c r="E60" s="493" t="inlineStr">
         <is>
-          <t>Not automatable (not yet wired up): requires a pre-provisioned ACTIVE HQ mobile-worker/web-user account distinct from this program's own fixed test credentials, and hq_client.py has no wrapped action for creating/toggling user activation state - would need new HQClient development, not a hard technical block.</t>
+          <t>Automated: uses a new HQClient.create_mobile_worker()/set_commcare_user_active() (scripts/hq_client.py) to manage user activation state via HQ's real activate/deactivate endpoints (corehq/apps/users/views/mobile/users.py), reused via scripts/appium_user_activation_scenarios.py's run_active_users_login(): installs [Master] Basic Tests and logs in as the already-active mobile_maestro worker (HQ_MOBILE_WORKER_USERNAME, already load-bearing for Install 7/8 - read-only here, never toggled), verifies the home screen. Verified passing live 2026-09-15.</t>
         </is>
       </c>
       <c r="F60" s="494" t="n"/>
       <c r="I60" s="0" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="J60" s="0" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>scripts/appium_user_activation_scenarios.py + scripts/run_appium_user_activation_suite.py</t>
         </is>
       </c>
     </row>
@@ -26650,18 +26655,23 @@
       <c r="D61" s="485" t="n"/>
       <c r="E61" s="493" t="inlineStr">
         <is>
-          <t>Not automatable (not yet wired up): same gap as Active users login, for a pre-provisioned INACTIVE account - no existing hq_client.py action manages user activation state.</t>
+          <t>Automated: uses a dedicated mobile worker (maestro_inactive, password "123", created idempotently via HQClient.create_mobile_worker() so as not to touch CC_TEST_USERNAME/HQ_MOBILE_WORKER_USERNAME, both load-bearing elsewhere) via scripts/appium_user_activation_scenarios.py's run_inactive_users_login(): deactivates it on HQ, installs [Master] Basic Tests, attempts login, verifies rejection. Confirmed live 2026-09-15 that a deactivated account's fresh login attempt reaches the login screen but fails with a real, stable "Invalid Username or Password" message - confirmed by then reactivating the same account and seeing the identical credentials succeed, proving activation state (not a bad password) caused it.</t>
         </is>
       </c>
       <c r="F61" s="494" t="n"/>
       <c r="I61" s="0" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="J61" s="0" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>scripts/appium_user_activation_scenarios.py + scripts/run_appium_user_activation_suite.py</t>
         </is>
       </c>
     </row>
@@ -26688,18 +26698,23 @@
       <c r="D62" s="500" t="n"/>
       <c r="E62" s="493" t="inlineStr">
         <is>
-          <t>Not automatable (not yet wired up): same gap as Active users login, plus a real-time deactivate/reactivate/deactivate cycle - no existing hq_client.py action manages user activation state.</t>
+          <t>Automated: reinterprets the row's real intent - the sheet's own steps are "login (rejected) - reactivate - login (succeeds) - deactivate again - sync - see a deactivation message", not just a login retry - via scripts/appium_user_activation_scenarios.py's run_deactivated_user_login(), using the same maestro_inactive account as Inactive users login: deactivate -&gt; attempt login (rejected, "Invalid Username or Password") -&gt; reactivate -&gt; log in again (succeeds, home screen) -&gt; deactivate again while still logged in on-device -&gt; tap Sync with Server -&gt; verify a real, distinct message ("Your account has been deactivated, please contact your domain admin to reactivate"). Ends deactivated, matching Inactive users login's own precondition. Verified passing live 2026-09-15.</t>
         </is>
       </c>
       <c r="F62" s="494" t="n"/>
       <c r="I62" s="0" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="J62" s="0" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>scripts/appium_user_activation_scenarios.py + scripts/run_appium_user_activation_suite.py</t>
         </is>
       </c>
     </row>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -19333,22 +19333,26 @@
       <c r="D23" s="399" t="n"/>
       <c r="E23" s="410" t="inlineStr">
         <is>
-          <t>Home tile inversion (Sync left / Start+Logout right) IS a real element-to-element position claim, not intra-widget alignment - genuinely testable via Maestro's rightOf/leftOf between the 'Start'/'Sync'/'Logout' tiles. Marked Not automatable here only because Confirmed live 2026-08-10: this app has real Arabic translations for common strings ('Start', 'Log out of CommCare', menu items), so English text selectors stop matching once the in-app language is switched to Arabic - a build attempt using English fallback selectors failed almost everywhere in CI for this reason. A build using these exact English labels as selectors failed live 2026-08-10 for that reason; would need the real Arabic strings (or an id-based selector, which square_card.xml's tile ids don't uniquely support - they repeat per tile) to attempt this for real.</t>
+          <t>Automated: confirmed live that CommCare's own in-app language switch does NOT change Android's real system layout direction (home tile bounds stayed byte-identical to English) - what genuinely causes RTL mirroring is the device's actual system locale, set via UiAutomator2's standard language/locale Appium capabilities (scripts/appium_browserstack_client.py's start_session(device_language="ar", device_locale="SA")), confirmed live to mirror the home screen's tiles (Sync moves left, Start+Logout move right) while leaving CommCare's own string content in English - so this never needs to match Arabic text at all, sidestepping the Unicode round-trip bug a prior Maestro attempt hit. See scripts/appium_rtl_scenarios.py's own module docstring for the full citation. Verified passing live 2026-09-15.</t>
         </is>
       </c>
       <c r="F23" s="410" t="n"/>
       <c r="G23" s="410" t="n"/>
       <c r="H23" s="410" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I23" s="697" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J23" s="410" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J23" s="410" t="inlineStr">
+        <is>
+          <t>scripts/appium_rtl_scenarios.py + scripts/run_appium_rtl_suite.py</t>
+        </is>
+      </c>
       <c r="K23" s="410" t="n"/>
       <c r="L23" s="410" t="n"/>
     </row>
@@ -19809,22 +19813,26 @@
       <c r="D36" s="399" t="n"/>
       <c r="E36" s="410" t="inlineStr">
         <is>
-          <t>Registration button text-alignment + arrow direction: the CHEVRON's mirrored position (icon_chevron_right_attnpos, which does carry a real rotationY RTL-mirror flag in source) is a genuine, checkable element-to-element position claim - but the button LABEL's own alignment is The claim is text alignment/gravity WITHIN a single widget (e.g. a TextView's own text starting from its right edge) - Maestro's position selectors (leftOf/rightOf/above/below) only compare the bounding boxes of two DISTINCT elements, not a property of one element's internal rendering. There is no Maestro primitive for intra-widget text alignment, so this can't be asserted regardless of effort. Not attempted this round given the mixed feasibility and this app's own confirmed Arabic-translation risk for the label text (EntityActionViewUtils displays app-config text, not a hardcoded string, so its real rendered value/language isn't known without live HQ inspection).</t>
+          <t>Partial-in-practice, automated where feasible: of this row's 3 claims, 2 are now automated via the same device-level Arabic locale mechanism as Home Screen 8 (scripts/appium_rtl_scenarios.py) - (1) the case-list action button's own label genuinely reads Arabic text ("تسجيل") unconditionally, checked via an Arabic-Unicode-range regex on the read-back string value, never as a tap selector; (2) the button's arrow/chevron container (right_aligned_container) is confirmed live to sit at the RIGHT edge under English/LTR (x:[838,1018] of 1080) and the LEFT edge under the device-level Arabic locale (x:[62,242]) - a genuine, checkable element-position mirror. The 3rd claim ("the text is right aligned" - intra-widget text gravity) stays confirmed Not automatable, same as this tab's other intra-widget-alignment gaps (Question Types 1/3/7) - no Maestro/Appium primitive compares a single element's own internal text alignment. Verified passing live 2026-09-15.</t>
         </is>
       </c>
       <c r="F36" s="410" t="n"/>
       <c r="G36" s="410" t="n"/>
       <c r="H36" s="410" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I36" s="697" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J36" s="410" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J36" s="410" t="inlineStr">
+        <is>
+          <t>scripts/appium_rtl_scenarios.py + scripts/run_appium_rtl_suite.py</t>
+        </is>
+      </c>
       <c r="K36" s="410" t="n"/>
       <c r="L36" s="410" t="n"/>
     </row>
@@ -26496,7 +26504,7 @@
       <c r="D57" s="485" t="n"/>
       <c r="E57" s="493" t="inlineStr">
         <is>
-          <t>Partial in principle, not yet reachable: the precondition (custom property cc-auto-form-save-on-pause=yes) could be verified via HQ's get_custom_properties, the same pattern already proven for Support Menus' own precondition check. Simulating an actual app crash/force-stop and verifying draft recovery afterward is blocked by this repo's own confirmed dead end on terminateApp/backgroundApp/adb_shell-style forced termination on BrowserStack - Maestro's stop/kill primitives don't reproduce a genuine crash the way this row's own steps need.</t>
+          <t>Partial (unchanged status, gap now documented and actively monitored): the row's own on-device steps (force-stop the app mid-form, relaunch, confirm the draft is restored) stay Not automatable - confirmed dead end on terminateApp/backgroundApp/adb_shell-style forced termination on BrowserStack, Maestro's stop/kill primitives don't reproduce a genuine crash. The row's own PRECONDITION (custom property cc-auto-form-save-on-pause=yes, name verified against commcare-android source: MainConfigurablePreferences.AUTO_SAVE_FORM_ON_PAUSE) IS a plain, automatable HQ read - scripts/run_graceful_session_pause_precondition_check.py, same pattern as Support Menus' own precondition check - but confirmed live 2026-09-15 that [Master] Basic Tests genuinely has NO such property set at all (get_custom_properties returns no cc-auto-form-save-on-pause key). This is a REAL, currently-unmet precondition, not a broken check - per direct user instruction, left as-is (not fixed by setting the property ourselves) and wired into CI (continue-on-error) so the gap stays visible in every run's report rather than silently undocumented.</t>
         </is>
       </c>
       <c r="F57" s="494" t="n"/>
@@ -26508,6 +26516,11 @@
       <c r="J57" s="0" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>scripts/run_graceful_session_pause_precondition_check.py</t>
         </is>
       </c>
     </row>
@@ -26627,7 +26640,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="K60" s="0" t="inlineStr">
         <is>
           <t>scripts/appium_user_activation_scenarios.py + scripts/run_appium_user_activation_suite.py</t>
         </is>
@@ -26669,7 +26682,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="K61" s="0" t="inlineStr">
         <is>
           <t>scripts/appium_user_activation_scenarios.py + scripts/run_appium_user_activation_suite.py</t>
         </is>
@@ -26712,7 +26725,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="K62" s="0" t="inlineStr">
         <is>
           <t>scripts/appium_user_activation_scenarios.py + scripts/run_appium_user_activation_suite.py</t>
         </is>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -8489,7 +8489,7 @@
       <c r="D12" s="387" t="n"/>
       <c r="E12" s="249" t="inlineStr">
         <is>
-          <t>Not automatable (currently paused pending a real multimedia zip/CCZ file): requires manually connecting the device to a computer, moving a specific file within the app's media directory via a file manager, and toggling network/uninstall state - genuinely reachable via Appium's real file-push capability (already proven for CCZ files elsewhere in this program), but blocked on obtaining the right multimedia zip asset. Explicitly paused per direct user instruction this session ('it will need a ccz file... I will get the ccz file') - not a hard technical dead end.</t>
+          <t>Not automatable (confirmed live 2026-09-15, superseding the earlier 'pending a ccz file' framing - that blocker is resolved as of MM1/2/3, but MM5/6 have a genuinely different, still-real one): unlike MM1/2/3 (which detect missing media during a fresh no-media INSTALL, before login), MM5/6's own premise is a file going missing from an ALREADY-successfully-installed, already-logged-in session while it keeps running - this requires actually deleting a real on-device file, not repairing a pre-login-detected one. Confirmed no working deletion mechanism exists on this BrowserStack Appium/UiAutomator2 driver: `mobile: shell` is blocked (adb_shell insecure feature disabled, same limitation cited for MM1-3), and `mobile: delete` - despite being listed in this driver's own 'Only shell,...,delete' unsupported-command error text - throws its own 'Unknown mobile command "delete"' error when actually invoked (tested live with several parameter shapes). Also confirmed there is no bypass/skip option on the pre-login CommCareVerificationActivity screen (its own overflow menu has only 'Install Multimedia') that would let a no-media install reach a normal logged-in home screen with media still missing, so MM1's own technique can't be adapted to reach MM5's required starting state either. A real on-device delete capability (or a different BrowserStack driver/feature exposing one) would be needed before this is revisited.</t>
         </is>
       </c>
       <c r="F12" s="249" t="n"/>
@@ -8544,7 +8544,7 @@
       <c r="D13" s="387" t="n"/>
       <c r="E13" s="249" t="inlineStr">
         <is>
-          <t>Not automatable (currently paused pending a real multimedia zip/CCZ file): requires manually connecting the device to a computer, moving a specific file within the app's media directory via a file manager, and toggling network/uninstall state - genuinely reachable via Appium's real file-push capability (already proven for CCZ files elsewhere in this program), but blocked on obtaining the right multimedia zip asset. Explicitly paused per direct user instruction this session ('it will need a ccz file... I will get the ccz file') - not a hard technical dead end.</t>
+          <t>Not automatable (confirmed live 2026-09-15, superseding the earlier 'pending a ccz file' framing - that blocker is resolved as of MM1/2/3, but MM5/6 have a genuinely different, still-real one): unlike MM1/2/3 (which detect missing media during a fresh no-media INSTALL, before login), MM5/6's own premise is a file going missing from an ALREADY-successfully-installed, already-logged-in session while it keeps running - this requires actually deleting a real on-device file, not repairing a pre-login-detected one. Confirmed no working deletion mechanism exists on this BrowserStack Appium/UiAutomator2 driver: `mobile: shell` is blocked (adb_shell insecure feature disabled, same limitation cited for MM1-3), and `mobile: delete` - despite being listed in this driver's own 'Only shell,...,delete' unsupported-command error text - throws its own 'Unknown mobile command "delete"' error when actually invoked (tested live with several parameter shapes). Also confirmed there is no bypass/skip option on the pre-login CommCareVerificationActivity screen (its own overflow menu has only 'Install Multimedia') that would let a no-media install reach a normal logged-in home screen with media still missing, so MM1's own technique can't be adapted to reach MM5's required starting state either. A real on-device delete capability (or a different BrowserStack driver/feature exposing one) would be needed before this is revisited.</t>
         </is>
       </c>
       <c r="F13" s="249" t="n"/>
@@ -26518,7 +26518,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="K57" s="0" t="inlineStr">
         <is>
           <t>scripts/run_graceful_session_pause_precondition_check.py</t>
         </is>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -19054,22 +19054,26 @@
       <c r="D16" s="399" t="n"/>
       <c r="E16" s="410" t="inlineStr">
         <is>
-          <t>Home header: same toolbar/overflow-button claim as Login 1 - No stable Maestro selector exists for the control in question, confirmed via commcare-android source: the toolbar's overflow ('More options') button and the app-name title are rendered by the platform AppCompat/Toolbar with no custom resource id or app-owned string (the title falls back to a per-flavor build value).</t>
+          <t>Automated: same device-level Arabic locale mechanism as Home Screen 8 (scripts/appium_rtl_scenarios.py's run_home_screen_1) - confirmed live the toolbar's nav-drawer icon (x:[0,168]-&gt;x:[912,1080]) and overflow icon (x:[960,1080]-&gt;x:[0,120]) mirror exactly like the home tiles do, identified by class/structure scoped to the toolbar's own stable resource-id, never by content-desc text (which itself changes under a real device-locale change - confirmed "More options" becomes "مزيد من الخيارات"). The app title's own position claim needed a real fix: a first attempt asserted the title sat right-of-center, which failed live for this app's longer title ("Right to Left Tests!") even though the mirroring was genuinely correct - confirmed via a second real screen (the login screen's shorter "CommCare" title) that both share an identical right edge (864) and identical ~48px gap to the drawer icon, proving the title is anchored adjacent to the drawer icon wherever it currently sits, not pinned to an absolute half-screen threshold. Verified passing live 2026-09-15 after that fix. NOTE: "Login 1" (row 12) makes the same toolbar-position claim but its own wording expects the options button on the RIGHT under RTL - confirmed live this contradicts the real, correct behavior (options button mirrors to the LEFT on the login screen too, identically to the home screen) - flagged to the user as a likely error in the sheet's own wording rather than encoded as a wrong assertion; left Not automatable pending that decision.</t>
         </is>
       </c>
       <c r="F16" s="410" t="n"/>
       <c r="G16" s="410" t="n"/>
       <c r="H16" s="410" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I16" s="697" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J16" s="410" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J16" s="410" t="inlineStr">
+        <is>
+          <t>scripts/appium_rtl_scenarios.py + scripts/run_appium_rtl_suite.py</t>
+        </is>
+      </c>
       <c r="K16" s="410" t="n"/>
       <c r="L16" s="410" t="n"/>
     </row>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -26430,18 +26430,23 @@
       <c r="D55" s="485" t="n"/>
       <c r="E55" s="486" t="inlineStr">
         <is>
-          <t>Not automatable (not yet wired up): configuring a Case Search property's checkbox/multi-select format lives in HQ's App Builder Case List UI, backed by the app's module/case_details XML - a materially more complex structure than the simple custom_properties key/value toggles hq_client.py already wraps (mark_build_status/set_custom_properties/etc.), so no existing action covers it.</t>
+          <t>Automated: per direct user instruction with exact App Builder steps, HQClient.set_module_search_properties() (scripts/hq_client.py, real edit_module_detail_screens endpoint found by reading commcare-hq source) adds a real Genre Case Search property in checkbox format against the Genre lookup table, on the "casesearch" domain's "[Mobile_Tests] Case Search and Claim" app's "Songs (See More)" module (app_registry.py's CASE_SEARCH_AND_CLAIM). Reads the module's CURRENT search_config fresh every run (never a hardcoded snapshot) - confirmed live this app is also edited manually by a colleague, so a stale snapshot would risk clobbering a real concurrent change. Verified live 2026-09-16, then reverted (confirmed via a fresh API read the property was removed and the other 4 properties were untouched).</t>
         </is>
       </c>
       <c r="F55" s="484" t="n"/>
       <c r="I55" s="0" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="J55" s="0" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>scripts/appium_casesearch_scenarios.py + scripts/run_casesearch_checkbox_suite.py</t>
         </is>
       </c>
     </row>
@@ -26469,18 +26474,23 @@
       <c r="D56" s="485" t="n"/>
       <c r="E56" s="486" t="inlineStr">
         <is>
-          <t>Not automatable: depends on Casesearch Checkbox 1's own App Builder configuration existing first.</t>
+          <t>Automated: builds a real app version from Casesearch Checkbox 1's own change and verifies on-device - confirmed live (BrowserStack sessions 47228751e72702f090c0f8b3775ef7bd221c2e53 + b0b51c0031a06edcb9c49c0c7a80d47d94856f5e) the Genre field renders as 4 real, independently-clickable android.widget.CheckBox elements (Hip Hop, Latin music, Metal, Pop music); selecting Hip Hop AND Metal simultaneously showed both checked=true (genuine multi-select, not radio-button behavior), and submitting the query returned real matching results with no error. The "SEARCH ALL CASES" button sits at the end of this case list's many existing cases, requiring a scroll to reach - a fixed tap-without-scroll attempt timed out before this was found. Wired as a repeatable CI step per direct user instruction, with the revert step retried up to 3 times after a real run hit a transient network error on the first attempt. See scripts/appium_casesearch_scenarios.py's own module docstring for the full citation.</t>
         </is>
       </c>
       <c r="F56" s="484" t="n"/>
       <c r="I56" s="0" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="J56" s="0" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>scripts/appium_casesearch_scenarios.py + scripts/run_casesearch_checkbox_suite.py</t>
         </is>
       </c>
     </row>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -14728,18 +14728,23 @@
       <c r="D19" s="564" t="n"/>
       <c r="E19" s="497" t="inlineStr">
         <is>
-          <t>Many of the feature built by USH (like input-search,) are not yet available to mobile yet, so the app might crash on searching the cases.</t>
+          <t>RESOLVED (2026-09-16): the referenced "Case Search and Claim" app genuinely exists (domain casesearch, app_id 414ea62a6610470eb8582a13954515ea) - confirmed via a direct user-supplied app link. MODULE PIVOT: this row's own steps reference "Songs (Search First)", which has date_opened configured, but live testing confirmed that module's own Case Search config returns zero results for the test1 account no matter what (not a scenario-code bug) - "Songs (See More)" (same app, also used by Form Submissions' Casesearch Checkbox 1/2 for an unrelated row) returns real results on a blank query and also has date_opened configured as a daterange property, so this scenario targets that module instead; no HQ config change needed. A hardcoded search date can't be relied on to match real, changeable test data, so the scenario reads a real date_opened value off an actually-listed case first, then re-searches using that exact date. Confirmed live the Date Opened field's calendar icon opens a Material date-range picker with a "Switch to text input mode" toggle - setting both start/end fields to the same date and tapping SAVE collapses the field to "&lt;date&gt; to &lt;date&gt;", matching this row's own "end date autopopulated" language. See scripts/appium_case_search_claim_scenarios.py's own module docstring for the full citation. Verified passing live locally (two clean consecutive runs) before being wired into CI.</t>
         </is>
       </c>
       <c r="F19" s="497" t="n"/>
       <c r="I19" s="0" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="J19" s="0" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>scripts/appium_case_search_claim_scenarios.py, scripts/run_case_search_claim_suite.py</t>
         </is>
       </c>
     </row>
@@ -26444,7 +26449,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="K55" s="0" t="inlineStr">
         <is>
           <t>scripts/appium_casesearch_scenarios.py + scripts/run_casesearch_checkbox_suite.py</t>
         </is>
@@ -26488,7 +26493,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="K56" s="0" t="inlineStr">
         <is>
           <t>scripts/appium_casesearch_scenarios.py + scripts/run_casesearch_checkbox_suite.py</t>
         </is>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -14742,7 +14742,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K19" s="0" t="inlineStr">
         <is>
           <t>scripts/appium_case_search_claim_scenarios.py, scripts/run_case_search_claim_suite.py</t>
         </is>
@@ -26035,7 +26035,7 @@
       <c r="D46" s="564" t="n"/>
       <c r="E46" s="477" t="inlineStr">
         <is>
-          <t>This property will not update for user for App Updates (we don’t want to change the user experience on maps on App Updates).</t>
+          <t>This property will not update for user for App Updates (we don’t want to change the user experience on maps on App Updates). UPDATE (2026-09-16), investigated in depth (not just re-asserted), same category as Case Filters' own Case Lists 1/2 device-dependent visual-confirmation precedent: the tileset IS writable via a real HQ endpoint (cc-maps-default-layer, a named CommCare Profile Setting under app.profile.properties - a new write path would be needed since hq_client.py's existing set_custom_properties() targets a different dict), but on-device, the SELECTED tileset has no accessibility-tree signal anywhere (confirmed via commcare-android source: GeoPointMapActivity/EntityMapActivity just call GoogleMap.setMapType() with no Log/content-desc/resource-id exposing the active layer), and the SharedPreferences key that holds it is unreadable on this harness (adb_shell is disabled on BrowserStack's managed Appium server). A real map view IS already reached (unasserted) by the existing Partial appearance_attributes_page_through_and_submit.yaml flow. Given the actual tileset check has no reliable observable signal, the 3x publish/install/uninstall cycle against Basic Tests (the most shared app in this repo) isn't worth the blast radius for zero incremental confidence. See coverage/coverage_matrix.csv's Geoservice 1 row for the full citation. Stays Not automatable.</t>
         </is>
       </c>
       <c r="F46" s="204" t="n"/>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -19406,22 +19406,26 @@
       <c r="D25" s="399" t="n"/>
       <c r="E25" s="410" t="inlineStr">
         <is>
-          <t>Form/menu list alignment with icon on the right: the row_img/row_txt ORDER is a real, checkable element-to-element position claim (confirmed via menu_list_item_modern.xml/MenuAdapter.java source), but the sheet's own 'text right aligned within its box' half is The claim is text alignment/gravity WITHIN a single widget (e.g. a TextView's own text starting from its right edge) - Maestro's position selectors (leftOf/rightOf/above/below) only compare the bounding boxes of two DISTINCT elements, not a property of one element's internal rendering. There is no Maestro primitive for intra-widget text alignment, so this can't be asserted regardless of effort.</t>
+          <t>Partial-in-practice, automated where feasible: of this row's 2 claims, 1 is now automated via the same device-level Arabic locale mechanism as Case list 4/Home Screen 8 (scripts/appium_rtl_scenarios.py, run_question_types_1) - on the Start screen's real form/menu list (confirmed live to have exactly 2 rows, "Survey" and "Case List"), each row's icon (row_img) is confirmed live to sit to the RIGHT of its own text (row_txt) under the device-level Arabic locale (row 0: row_img x:[882,1056] vs row_txt x:[72,834], screen width 1080) - a genuine, checkable element-to-element position claim, consistent with the row_img/row_txt order already established via menu_list_item_modern.xml/MenuAdapter.java source. The 2nd claim ("text right aligned within its box" - intra-widget text gravity) stays confirmed Not automatable, same as this tab's other intra-widget-alignment gaps (Case list 2/3, Question Types 3/7) - no Maestro/Appium primitive compares a single element's own internal text alignment. Verified passing live 2026-09-16 (2 runs).</t>
         </is>
       </c>
       <c r="F25" s="410" t="n"/>
       <c r="G25" s="410" t="n"/>
       <c r="H25" s="410" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I25" s="697" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J25" s="410" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J25" s="410" t="inlineStr">
+        <is>
+          <t>scripts/appium_rtl_scenarios.py (run_question_types_1) + scripts/run_appium_rtl_suite.py</t>
+        </is>
+      </c>
       <c r="K25" s="410" t="n"/>
       <c r="L25" s="410" t="n"/>
     </row>
@@ -19484,22 +19488,26 @@
       <c r="D27" s="399" t="n"/>
       <c r="E27" s="410" t="inlineStr">
         <is>
-          <t>Swipe direction inversion IS behaviorally testable (perform a swipe, check whether it advanced); the progress-bar-direction half is not - The claim is an animation/rendering DIRECTION (progress bar fill direction, spinner rotation direction) sampled over time - Maestro has no angular-rotation or fill-direction assertion primitive at all, independent of whether the element has a stable id. Not attempted this round given the mixed feasibility and the Arabic-text dependency noted in Question Types 2's sibling rows.</t>
+          <t>Partial-in-practice, automated where feasible: of this row's 2 claims, 1 is now automated (scripts/appium_rtl_scenarios.py, run_question_types_3) - a prior Maestro attempt (question_types_02_open_first_form.yaml's own header) had concluded swipe had no observable effect on this form, based on checking a resource id ("nav_btn_back") confirmed live NOT to exist in this app at all (the real id is nav_btn_prev) - a false negative from a wrong selector, not real evidence against swipe navigation. Re-tested live with a safe, non-edge-hugging swipe (an earlier edge-to-edge attempt instead triggered Android's own system back gesture, landing on CommCare's "Exit Form?" dialog - a false positive for an unrelated reason): on the form's first real question, a right-to-left finger swipe genuinely navigates BACKWARD and a left-to-right finger swipe genuinely navigates FORWARD - a real, working, objectively checkable (via the visible question text changing) swipe gesture whose forward direction is exactly "left to right", matching this row's own literal wording. The 2nd claim (progress-bar fill direction - an animation/rendering direction sampled over time) stays confirmed Not automatable, same as already established - no Maestro/Appium primitive for angular-rotation or fill-direction assertions. Verified passing live 2026-09-16.</t>
         </is>
       </c>
       <c r="F27" s="410" t="n"/>
       <c r="G27" s="410" t="n"/>
       <c r="H27" s="410" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I27" s="697" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J27" s="410" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J27" s="410" t="inlineStr">
+        <is>
+          <t>scripts/appium_rtl_scenarios.py (run_question_types_3) + scripts/run_appium_rtl_suite.py</t>
+        </is>
+      </c>
       <c r="K27" s="410" t="n"/>
       <c r="L27" s="410" t="n"/>
     </row>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -14474,12 +14474,12 @@
       <c r="F13" s="497" t="n"/>
       <c r="I13" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Not automatable</t>
         </is>
       </c>
       <c r="J13" s="0" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -14511,12 +14511,12 @@
       <c r="F14" s="331" t="n"/>
       <c r="I14" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Not automatable</t>
         </is>
       </c>
       <c r="J14" s="0" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -36621,12 +36621,12 @@
       <c r="G16" s="150" t="n"/>
       <c r="H16" s="124" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Not automatable</t>
         </is>
       </c>
       <c r="I16" s="664" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -36814,12 +36814,12 @@
       <c r="G21" s="139" t="n"/>
       <c r="H21" s="124" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Not automatable</t>
         </is>
       </c>
       <c r="I21" s="664" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -26043,7 +26043,7 @@
       <c r="D46" s="564" t="n"/>
       <c r="E46" s="477" t="inlineStr">
         <is>
-          <t>This property will not update for user for App Updates (we don’t want to change the user experience on maps on App Updates). UPDATE (2026-09-16), investigated in depth (not just re-asserted), same category as Case Filters' own Case Lists 1/2 device-dependent visual-confirmation precedent: the tileset IS writable via a real HQ endpoint (cc-maps-default-layer, a named CommCare Profile Setting under app.profile.properties - a new write path would be needed since hq_client.py's existing set_custom_properties() targets a different dict), but on-device, the SELECTED tileset has no accessibility-tree signal anywhere (confirmed via commcare-android source: GeoPointMapActivity/EntityMapActivity just call GoogleMap.setMapType() with no Log/content-desc/resource-id exposing the active layer), and the SharedPreferences key that holds it is unreadable on this harness (adb_shell is disabled on BrowserStack's managed Appium server). A real map view IS already reached (unasserted) by the existing Partial appearance_attributes_page_through_and_submit.yaml flow. Given the actual tileset check has no reliable observable signal, the 3x publish/install/uninstall cycle against Basic Tests (the most shared app in this repo) isn't worth the blast radius for zero incremental confidence. See coverage/coverage_matrix.csv's Geoservice 1 row for the full citation. Stays Not automatable.</t>
+          <t>This property will not update for user for App Updates (we don’t want to change the user experience on maps on App Updates). UPDATE (2026-09-16), investigated in depth (not just re-asserted), same category as Case Filters' own Case Lists 1/2 device-dependent visual-confirmation precedent: the tileset IS writable via a real HQ endpoint (cc-maps-default-layer, a named CommCare Profile Setting under app.profile.properties - a new write path would be needed since hq_client.py's existing set_custom_properties() targets a different dict), but on-device, the SELECTED tileset has no accessibility-tree signal anywhere (confirmed via commcare-android source: GeoPointMapActivity/EntityMapActivity just call GoogleMap.setMapType() with no Log/content-desc/resource-id exposing the active layer), and the SharedPreferences key that holds it is unreadable on this harness (adb_shell is disabled on BrowserStack's managed Appium server). A real map view IS already reached (unasserted) by the existing Partial appearance_attributes_page_through_and_submit.yaml flow. Given the actual tileset check has no reliable observable signal, the 3x publish/install/uninstall cycle against Basic Tests (the most shared app in this repo) isn't worth the blast radius for zero incremental confidence. See coverage/coverage_matrix.csv's Geoservice 1 row for the full citation. Stays Not automatable. UPDATE (2026-09-17), per direct user-supplied screenshots: re-scoped to the lower-blast-radius [Master] Basic Tests NS Copy!!! app instead of the main shared Basic Tests app. Built and verified live a real HQClient.set_app_properties()/get_app_properties() pair for the actual HQ endpoint (profile.properties, a true per-key merge - distinct from custom_properties, which replaces the whole dict; a bug in an early version silently wiped this app's custom_properties by omitting that key from the POST body, found and fixed, app state restored and independently re-verified). Confirmed NS Copy has the same appearance="maps" geopoint question ([Mobile] Appearance Attributes) as the main app, and verified the full write -&gt; new build -&gt; app-code install -&gt; login -&gt; open map pipeline end-to-end for one tileset (Terrain): map screen loads with no crash. This is real, useful verification tooling (scripts/appium_geoservice1_scenarios.py + scripts/run_geoservice1_suite.py) but NOT wired into CI - the core gap (no way to assert WHICH tileset is actually rendering) is unchanged and still genuinely unautomatable. Default Map Tileset restored to its original value (satellite) after testing.</t>
         </is>
       </c>
       <c r="F46" s="204" t="n"/>
@@ -26531,7 +26531,7 @@
       <c r="D57" s="485" t="n"/>
       <c r="E57" s="493" t="inlineStr">
         <is>
-          <t>Partial (unchanged status, gap now documented and actively monitored): the row's own on-device steps (force-stop the app mid-form, relaunch, confirm the draft is restored) stay Not automatable - confirmed dead end on terminateApp/backgroundApp/adb_shell-style forced termination on BrowserStack, Maestro's stop/kill primitives don't reproduce a genuine crash. The row's own PRECONDITION (custom property cc-auto-form-save-on-pause=yes, name verified against commcare-android source: MainConfigurablePreferences.AUTO_SAVE_FORM_ON_PAUSE) IS a plain, automatable HQ read - scripts/run_graceful_session_pause_precondition_check.py, same pattern as Support Menus' own precondition check - but confirmed live 2026-09-15 that [Master] Basic Tests genuinely has NO such property set at all (get_custom_properties returns no cc-auto-form-save-on-pause key). This is a REAL, currently-unmet precondition, not a broken check - per direct user instruction, left as-is (not fixed by setting the property ourselves) and wired into CI (continue-on-error) so the gap stays visible in every run's report rather than silently undocumented.</t>
+          <t>Partial: this row's own on-device steps (force-stop the app mid-form, relaunch, confirm the draft is restored) were genuinely re-tried live (2026-09-17) against a correctly-configured app - installed [Master] Basic Tests NS Copy!!! fresh via app-code, logged in, navigated Start &gt; Basic_Form_Tests &gt; Question_Types!, answered a question, then called Appium's driver.terminate_app("org.commcare.dalvik") (mobile: terminateApp - the correct non-adb_shell, non-Maestro-killApp primitive this needs). Result: a genuine UnknownMethodException whose own exhaustive supported-command list for this BrowserStack Appium driver build confirms none of terminateApp/activateApp/backgroundApp are supported at all; "shell" is nominally listed but BrowserStack separately confirmed to disable the underlying adb_shell feature account-wide (same finding as the MM5/MM6 multimedia investigation), so a real force-stop isn't reachable that way either. This is now a concrete, evidence-based dead end tied to the specific flow and the correct app/primitive, not an overgeneralized carryover. The row's own PRECONDITION (custom property cc-auto-form-save-on-pause=yes, verified against commcare-android source: MainConfigurablePreferences.AUTO_SAVE_FORM_ON_PAUSE) IS automatable and now passing: scripts/run_graceful_session_pause_precondition_check.py was found pointed at the WRONG app ([Master] Basic Tests, which genuinely lacks the property) - re-pointed at [Master] Basic Tests NS Copy!!! (APP_REGISTRY["BASIC_TESTS_NS_COPY"]), confirmed live to have cc-auto-form-save-on-pause=yes. Wired into CI (continue-on-error, non-gating). See coverage/coverage_matrix.csv's own Graceful Session Pause row for the full citation.</t>
         </is>
       </c>
       <c r="F57" s="494" t="n"/>
@@ -26542,7 +26542,7 @@
       </c>
       <c r="J57" s="0" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K57" s="0" t="inlineStr">

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -14728,7 +14728,7 @@
       <c r="D19" s="564" t="n"/>
       <c r="E19" s="497" t="inlineStr">
         <is>
-          <t>RESOLVED (2026-09-16): the referenced "Case Search and Claim" app genuinely exists (domain casesearch, app_id 414ea62a6610470eb8582a13954515ea) - confirmed via a direct user-supplied app link. MODULE PIVOT: this row's own steps reference "Songs (Search First)", which has date_opened configured, but live testing confirmed that module's own Case Search config returns zero results for the test1 account no matter what (not a scenario-code bug) - "Songs (See More)" (same app, also used by Form Submissions' Casesearch Checkbox 1/2 for an unrelated row) returns real results on a blank query and also has date_opened configured as a daterange property, so this scenario targets that module instead; no HQ config change needed. A hardcoded search date can't be relied on to match real, changeable test data, so the scenario reads a real date_opened value off an actually-listed case first, then re-searches using that exact date. Confirmed live the Date Opened field's calendar icon opens a Material date-range picker with a "Switch to text input mode" toggle - setting both start/end fields to the same date and tapping SAVE collapses the field to "&lt;date&gt; to &lt;date&gt;", matching this row's own "end date autopopulated" language. See scripts/appium_case_search_claim_scenarios.py's own module docstring for the full citation. Verified passing live locally (two clean consecutive runs) before being wired into CI.</t>
+          <t>RESOLVED (2026-09-16): the referenced "Case Search and Claim" app genuinely exists (domain casesearch, app_id 414ea62a6610470eb8582a13954515ea) - confirmed via a direct user-supplied app link. REWRITTEN (2026-09-17), per direct user instruction after reviewing a real device recording: targets "Songs (Search First)" - the module this row's own steps literally name - rather than an earlier "Songs (See More)" pivot that existed only because an earlier version required real matching data to prove the date filter works. Search First's own pre-filled defaults (Song Name="Default Song", Rating=*****) make every query return zero matches regardless of date - the user's own recording confirmed this "Query response had no results" outcome is normal and acceptable here, not a failure, so the scenario no longer needs a real matching case at all: it verifies the Date Opened field is present, that entering a single date (today's date) in the calendar picker's start/end fields genuinely collapses the field to "&lt;date&gt; to &lt;date&gt;", then submits the query and accepts EITHER a real results screen OR a clean "no results" toast as a pass. See scripts/appium_case_search_claim_scenarios.py's own module docstring for the full citation. Verified passing live locally (two clean consecutive runs) before being wired into CI.</t>
         </is>
       </c>
       <c r="F19" s="497" t="n"/>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -14773,18 +14773,23 @@
       <c r="D20" s="564" t="n"/>
       <c r="E20" s="497" t="inlineStr">
         <is>
-          <t>Step 6 explicitly requires verifying functionality 'on webapps' - a different platform/surface than this repo's mobile-only Maestro framework covers.</t>
+          <t>RESOLVED to PARTIAL (2026-09-17), same app as Case Search &amp; Claim 1 (row 19) - domain casesearch, app_id 414ea62a6610470eb8582a13954515ea. Steps 1-4 (open Songs (Search First), select a song, open Shows, Search Again/open the search form) are real, live-confirmed navigation and are automated. BLOCKER CONFIRMED LIVE: the Shows module's own "Show Date" search property (when_is_the_show, input_="date") genuinely never renders as a query prompt at all - a UI rendering gap on this app's currently installed CommCare client, not a data problem (the only input_="date" field across this app's modules; every other date field, including row 19's own, uses the working input_="daterange" widget). RESOLVED, per direct user instruction after reviewing a real device recording: a NEW property was added to this module - "Date Opened" (input_="daterange", confirmed live) - which renders and works. This scenario uses that field (not literally "Show Date", but the row's practical "search by date" intent) the same way row 19 uses its own Date Opened field: enters today's date, verifies the field collapses to "&lt;date&gt; to &lt;date&gt;", submits the query, and accepts EITHER a real results screen OR a clean "no results" toast as a pass. Step 6 ("functional on webapps") stays out of scope for this mobile-only repo; step 7 against the ORIGINAL "Show Date" widget specifically stays not automatable since that field still doesn't render. Also benefits from a shared fix: this device's date picker's expected text-entry order (mm/dd/y vs dd/mm/y) varies by BrowserStack session, so the scenario now detects the correct order live via a validation hint rather than assuming one. See scripts/appium_case_search_claim_2_scenarios.py's own module docstring for the full citation. Verified passing live locally (multiple clean consecutive runs) before being wired into CI.</t>
         </is>
       </c>
       <c r="F20" s="497" t="n"/>
       <c r="I20" s="0" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="J20" s="0" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K20" s="0" t="inlineStr">
+        <is>
+          <t>scripts/appium_case_search_claim_2_scenarios.py, scripts/run_case_search_claim_2_suite.py</t>
         </is>
       </c>
     </row>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -8909,7 +8909,7 @@
       <c r="G19" s="60" t="n"/>
       <c r="H19" s="60" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I19" s="709" t="inlineStr">
@@ -9214,7 +9214,7 @@
       <c r="G24" s="60" t="n"/>
       <c r="H24" s="60" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I24" s="709" t="inlineStr">
@@ -9516,7 +9516,7 @@
       <c r="G29" s="60" t="n"/>
       <c r="H29" s="60" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I29" s="709" t="inlineStr">
@@ -9818,7 +9818,7 @@
       <c r="G34" s="60" t="n"/>
       <c r="H34" s="60" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I34" s="709" t="inlineStr">

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -6233,12 +6233,15 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.29" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="30.29" customWidth="1" style="629" min="2" max="2"/>
     <col width="50.43" customWidth="1" style="629" min="3" max="3"/>
     <col width="21.86" customWidth="1" style="629" min="5" max="6"/>
+    <col width="18" customWidth="1" style="629" min="9" max="9"/>
+    <col width="13" customWidth="1" style="629" min="10" max="10"/>
+    <col width="60" customWidth="1" style="629" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6366,6 +6369,21 @@
           <t>Ticket ID</t>
         </is>
       </c>
+      <c r="I7" s="140" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="479" t="inlineStr">
@@ -6387,6 +6405,21 @@
       <c r="D8" s="137" t="n"/>
       <c r="E8" s="479" t="n"/>
       <c r="F8" s="479" t="n"/>
+      <c r="I8" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/wifi_direct/wifi_01_change_modes_dialog.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="479" t="inlineStr">
@@ -6424,6 +6457,21 @@
         </is>
       </c>
       <c r="F9" s="497" t="n"/>
+      <c r="I9" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/wifi_direct/wifi_01_change_modes_dialog.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="479" t="inlineStr">
@@ -6452,6 +6500,17 @@
       <c r="D10" s="137" t="n"/>
       <c r="E10" s="479" t="n"/>
       <c r="F10" s="479" t="n"/>
+      <c r="I10" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="479" t="inlineStr">
@@ -6477,6 +6536,17 @@
       <c r="D11" s="137" t="n"/>
       <c r="E11" s="497" t="n"/>
       <c r="F11" s="497" t="n"/>
+      <c r="I11" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="479" t="inlineStr">
@@ -6511,6 +6581,17 @@
         </is>
       </c>
       <c r="F12" s="497" t="n"/>
+      <c r="I12" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="479" t="inlineStr">
@@ -6533,6 +6614,17 @@
       <c r="D13" s="137" t="n"/>
       <c r="E13" s="479" t="n"/>
       <c r="F13" s="479" t="n"/>
+      <c r="I13" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="0" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="479" t="inlineStr">
@@ -6555,6 +6647,17 @@
       <c r="D14" s="137" t="n"/>
       <c r="E14" s="479" t="n"/>
       <c r="F14" s="479" t="n"/>
+      <c r="I14" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" s="0" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="479" t="inlineStr">
@@ -6578,6 +6681,17 @@
       <c r="D15" s="137" t="n"/>
       <c r="E15" s="479" t="n"/>
       <c r="F15" s="479" t="n"/>
+      <c r="I15" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K15" s="0" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="479" t="inlineStr">
@@ -6602,6 +6716,17 @@
       <c r="D16" s="137" t="n"/>
       <c r="E16" s="479" t="n"/>
       <c r="F16" s="479" t="n"/>
+      <c r="I16" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" s="0" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -12305,12 +12430,15 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.29" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="18.71" customWidth="1" style="629" min="1" max="1"/>
     <col width="39.29" customWidth="1" style="629" min="2" max="2"/>
     <col width="52" customWidth="1" style="629" min="3" max="3"/>
+    <col width="18" customWidth="1" style="629" min="9" max="9"/>
+    <col width="13" customWidth="1" style="629" min="10" max="10"/>
+    <col width="60" customWidth="1" style="629" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12461,8 +12589,21 @@
         </is>
       </c>
       <c r="H7" s="166" t="n"/>
-      <c r="I7" s="166" t="n"/>
-      <c r="J7" s="166" t="n"/>
+      <c r="I7" s="140" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="455" t="inlineStr">
@@ -12498,8 +12639,21 @@
       <c r="F8" s="249" t="n"/>
       <c r="G8" s="249" t="n"/>
       <c r="H8" s="166" t="n"/>
-      <c r="I8" s="166" t="n"/>
-      <c r="J8" s="166" t="n"/>
+      <c r="I8" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/developer_options/do_01_enable_developer_options.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="455" t="inlineStr">
@@ -12527,8 +12681,21 @@
       <c r="F9" s="249" t="n"/>
       <c r="G9" s="249" t="n"/>
       <c r="H9" s="166" t="n"/>
-      <c r="I9" s="166" t="n"/>
-      <c r="J9" s="166" t="n"/>
+      <c r="I9" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/developer_options/do_01_enable_developer_options.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="455" t="inlineStr">
@@ -12562,8 +12729,21 @@
       <c r="F10" s="249" t="n"/>
       <c r="G10" s="249" t="n"/>
       <c r="H10" s="166" t="n"/>
-      <c r="I10" s="166" t="n"/>
-      <c r="J10" s="166" t="n"/>
+      <c r="I10" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/developer_options/do_01_enable_developer_options.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="455" t="inlineStr">
@@ -12586,8 +12766,21 @@
       <c r="F11" s="249" t="n"/>
       <c r="G11" s="249" t="n"/>
       <c r="H11" s="166" t="n"/>
-      <c r="I11" s="166" t="n"/>
-      <c r="J11" s="166" t="n"/>
+      <c r="I11" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="inlineStr">
+        <is>
+          <t>(covered by the Update tab's flows)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="455" t="inlineStr">
@@ -12615,8 +12808,21 @@
       <c r="F12" s="249" t="n"/>
       <c r="G12" s="249" t="n"/>
       <c r="H12" s="166" t="n"/>
-      <c r="I12" s="166" t="n"/>
-      <c r="J12" s="166" t="n"/>
+      <c r="I12" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/developer_options/do_03_image_above_text_enabled.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="455" t="inlineStr">
@@ -12645,8 +12851,21 @@
       <c r="F13" s="249" t="n"/>
       <c r="G13" s="249" t="n"/>
       <c r="H13" s="166" t="n"/>
-      <c r="I13" s="166" t="n"/>
-      <c r="J13" s="166" t="n"/>
+      <c r="I13" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K13" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/developer_options/do_04_image_above_text_disabled.yaml</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -12685,12 +12904,15 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.29" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="19.86" customWidth="1" style="629" min="1" max="1"/>
     <col width="21.14" customWidth="1" style="629" min="2" max="2"/>
     <col width="93.70999999999999" customWidth="1" style="629" min="3" max="3"/>
+    <col width="18" customWidth="1" style="629" min="9" max="9"/>
+    <col width="13" customWidth="1" style="629" min="10" max="10"/>
+    <col width="60" customWidth="1" style="629" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12811,6 +13033,21 @@
         </is>
       </c>
       <c r="G7" s="494" t="n"/>
+      <c r="I7" s="140" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="284" t="inlineStr">
@@ -12832,6 +13069,21 @@
       <c r="E8" s="468" t="n"/>
       <c r="F8" s="468" t="n"/>
       <c r="G8" s="494" t="n"/>
+      <c r="I8" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/printing/form_printing_01_04_print_from_form.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="284" t="inlineStr">
@@ -12855,6 +13107,21 @@
       <c r="E9" s="468" t="n"/>
       <c r="F9" s="468" t="n"/>
       <c r="G9" s="494" t="n"/>
+      <c r="I9" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/printing/form_printing_01_04_print_from_form.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="284" t="inlineStr">
@@ -12876,6 +13143,21 @@
       <c r="E10" s="468" t="n"/>
       <c r="F10" s="468" t="n"/>
       <c r="G10" s="494" t="n"/>
+      <c r="I10" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/printing/form_printing_01_04_print_from_form.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="284" t="inlineStr">
@@ -12898,6 +13180,21 @@
       <c r="E11" s="468" t="n"/>
       <c r="F11" s="468" t="n"/>
       <c r="G11" s="494" t="n"/>
+      <c r="I11" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/printing/form_printing_01_04_print_from_form.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="284" t="inlineStr">
@@ -12920,6 +13217,17 @@
       <c r="E12" s="468" t="n"/>
       <c r="F12" s="468" t="n"/>
       <c r="G12" s="494" t="n"/>
+      <c r="I12" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="284" t="inlineStr">
@@ -12941,6 +13249,21 @@
       <c r="E13" s="468" t="n"/>
       <c r="F13" s="468" t="n"/>
       <c r="G13" s="494" t="n"/>
+      <c r="I13" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K13" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/printing/print_from_detail_01_02_case_detail_values.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="284" t="inlineStr">
@@ -12962,6 +13285,21 @@
       <c r="E14" s="468" t="n"/>
       <c r="F14" s="468" t="n"/>
       <c r="G14" s="494" t="n"/>
+      <c r="I14" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K14" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/printing/print_from_detail_01_02_case_detail_values.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="284" t="inlineStr">
@@ -12983,6 +13321,21 @@
       <c r="E15" s="468" t="n"/>
       <c r="F15" s="468" t="n"/>
       <c r="G15" s="494" t="n"/>
+      <c r="I15" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K15" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/printing/print_from_detail_03_print_case_detail.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="387" t="inlineStr">
@@ -13005,6 +13358,17 @@
       <c r="E16" s="387" t="n"/>
       <c r="F16" s="387" t="n"/>
       <c r="G16" s="494" t="n"/>
+      <c r="I16" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" s="0" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -13045,10 +13409,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.29" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="108.71" customWidth="1" style="629" min="3" max="3"/>
+    <col width="18" customWidth="1" style="629" min="9" max="9"/>
+    <col width="13" customWidth="1" style="629" min="10" max="10"/>
+    <col width="60" customWidth="1" style="629" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13191,7 +13558,21 @@
       </c>
       <c r="G7" s="494" t="n"/>
       <c r="H7" s="494" t="n"/>
-      <c r="I7" s="494" t="n"/>
+      <c r="I7" s="140" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="284" t="inlineStr">
@@ -13214,7 +13595,21 @@
       <c r="F8" s="468" t="n"/>
       <c r="G8" s="494" t="n"/>
       <c r="H8" s="494" t="n"/>
-      <c r="I8" s="494" t="n"/>
+      <c r="I8" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/graphing/graphing_01_05_19_create_case_points_view_and_remove.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="284" t="inlineStr">
@@ -13240,7 +13635,21 @@
       <c r="F9" s="468" t="n"/>
       <c r="G9" s="494" t="n"/>
       <c r="H9" s="494" t="n"/>
-      <c r="I9" s="494" t="n"/>
+      <c r="I9" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/graphing/graphing_01_05_19_create_case_points_view_and_remove.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="284" t="inlineStr">
@@ -13265,7 +13674,21 @@
       <c r="F10" s="468" t="n"/>
       <c r="G10" s="494" t="n"/>
       <c r="H10" s="494" t="n"/>
-      <c r="I10" s="494" t="n"/>
+      <c r="I10" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/graphing/graphing_01_05_19_create_case_points_view_and_remove.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="284" t="inlineStr">
@@ -13288,7 +13711,21 @@
       <c r="F11" s="468" t="n"/>
       <c r="G11" s="494" t="n"/>
       <c r="H11" s="494" t="n"/>
-      <c r="I11" s="494" t="n"/>
+      <c r="I11" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/graphing/graphing_01_05_19_create_case_points_view_and_remove.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="284" t="inlineStr">
@@ -13314,7 +13751,21 @@
       <c r="F12" s="468" t="n"/>
       <c r="G12" s="494" t="n"/>
       <c r="H12" s="494" t="n"/>
-      <c r="I12" s="494" t="n"/>
+      <c r="I12" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/graphing/graphing_01_05_19_create_case_points_view_and_remove.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="284" t="inlineStr">
@@ -13340,7 +13791,21 @@
       <c r="F13" s="468" t="n"/>
       <c r="G13" s="494" t="n"/>
       <c r="H13" s="494" t="n"/>
-      <c r="I13" s="494" t="n"/>
+      <c r="I13" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K13" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/graphing/graphing_01_05_19_create_case_points_view_and_remove.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="284" t="inlineStr">
@@ -13369,7 +13834,21 @@
       <c r="F14" s="468" t="n"/>
       <c r="G14" s="494" t="n"/>
       <c r="H14" s="494" t="n"/>
-      <c r="I14" s="494" t="n"/>
+      <c r="I14" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K14" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/graphing/graphing_06_xy_axis_labels.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="284" t="inlineStr">
@@ -13398,7 +13877,21 @@
       <c r="F15" s="468" t="n"/>
       <c r="G15" s="494" t="n"/>
       <c r="H15" s="494" t="n"/>
-      <c r="I15" s="494" t="n"/>
+      <c r="I15" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K15" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/graphing/graphing_07_11_graph_tabs_text.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="284" t="inlineStr">
@@ -13426,7 +13919,21 @@
       <c r="F16" s="468" t="n"/>
       <c r="G16" s="494" t="n"/>
       <c r="H16" s="494" t="n"/>
-      <c r="I16" s="494" t="n"/>
+      <c r="I16" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K16" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/graphing/graphing_07_11_graph_tabs_text.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="284" t="inlineStr">
@@ -13454,7 +13961,21 @@
       <c r="F17" s="468" t="n"/>
       <c r="G17" s="494" t="n"/>
       <c r="H17" s="494" t="n"/>
-      <c r="I17" s="494" t="n"/>
+      <c r="I17" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K17" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/graphing/graphing_07_11_graph_tabs_text.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="284" t="inlineStr">
@@ -13482,7 +14003,21 @@
       <c r="F18" s="468" t="n"/>
       <c r="G18" s="494" t="n"/>
       <c r="H18" s="494" t="n"/>
-      <c r="I18" s="494" t="n"/>
+      <c r="I18" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K18" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/graphing/graphing_07_11_graph_tabs_text.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="284" t="inlineStr">
@@ -13508,7 +14043,21 @@
       <c r="F19" s="468" t="n"/>
       <c r="G19" s="494" t="n"/>
       <c r="H19" s="494" t="n"/>
-      <c r="I19" s="494" t="n"/>
+      <c r="I19" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K19" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/graphing/graphing_07_11_graph_tabs_text.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="284" t="inlineStr">
@@ -13537,7 +14086,21 @@
       <c r="F20" s="468" t="n"/>
       <c r="G20" s="494" t="n"/>
       <c r="H20" s="494" t="n"/>
-      <c r="I20" s="494" t="n"/>
+      <c r="I20" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K20" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/graphing/graphing_12_double_tap_full_screen.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="284" t="inlineStr">
@@ -13562,7 +14125,17 @@
       <c r="F21" s="468" t="n"/>
       <c r="G21" s="494" t="n"/>
       <c r="H21" s="494" t="n"/>
-      <c r="I21" s="494" t="n"/>
+      <c r="I21" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J21" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K21" s="0" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="284" t="inlineStr">
@@ -13587,7 +14160,17 @@
       <c r="F22" s="468" t="n"/>
       <c r="G22" s="494" t="n"/>
       <c r="H22" s="494" t="n"/>
-      <c r="I22" s="494" t="n"/>
+      <c r="I22" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J22" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K22" s="0" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="284" t="inlineStr">
@@ -13612,7 +14195,17 @@
       <c r="F23" s="468" t="n"/>
       <c r="G23" s="494" t="n"/>
       <c r="H23" s="494" t="n"/>
-      <c r="I23" s="494" t="n"/>
+      <c r="I23" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J23" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" s="0" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="284" t="inlineStr">
@@ -13637,7 +14230,17 @@
       <c r="F24" s="468" t="n"/>
       <c r="G24" s="494" t="n"/>
       <c r="H24" s="494" t="n"/>
-      <c r="I24" s="494" t="n"/>
+      <c r="I24" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J24" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K24" s="0" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="284" t="inlineStr">
@@ -13662,7 +14265,17 @@
       <c r="F25" s="468" t="n"/>
       <c r="G25" s="494" t="n"/>
       <c r="H25" s="494" t="n"/>
-      <c r="I25" s="494" t="n"/>
+      <c r="I25" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J25" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K25" s="0" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="284" t="inlineStr">
@@ -13690,7 +14303,21 @@
       <c r="F26" s="468" t="n"/>
       <c r="G26" s="494" t="n"/>
       <c r="H26" s="494" t="n"/>
-      <c r="I26" s="494" t="n"/>
+      <c r="I26" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J26" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K26" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/graphing/graphing_18_remove_point_list.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="284" t="inlineStr">
@@ -13716,7 +14343,21 @@
       <c r="F27" s="468" t="n"/>
       <c r="G27" s="494" t="n"/>
       <c r="H27" s="494" t="n"/>
-      <c r="I27" s="494" t="n"/>
+      <c r="I27" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J27" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K27" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/graphing/graphing_01_05_19_create_case_points_view_and_remove.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="284" t="inlineStr">
@@ -13745,7 +14386,21 @@
       <c r="F28" s="468" t="n"/>
       <c r="G28" s="494" t="n"/>
       <c r="H28" s="494" t="n"/>
-      <c r="I28" s="494" t="n"/>
+      <c r="I28" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J28" s="0" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K28" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/graphing/graphing_20_22_user_info_report_graphs.yaml (blocked: app's mobile reports fixture not restored on HQ)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="284" t="inlineStr">
@@ -13770,7 +14425,17 @@
       <c r="F29" s="468" t="n"/>
       <c r="G29" s="494" t="n"/>
       <c r="H29" s="494" t="n"/>
-      <c r="I29" s="494" t="n"/>
+      <c r="I29" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J29" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K29" s="0" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="284" t="inlineStr">
@@ -13795,7 +14460,21 @@
       <c r="F30" s="468" t="n"/>
       <c r="G30" s="494" t="n"/>
       <c r="H30" s="494" t="n"/>
-      <c r="I30" s="494" t="n"/>
+      <c r="I30" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J30" s="0" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K30" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/graphing/graphing_20_22_user_info_report_graphs.yaml (blocked: app's mobile reports fixture not restored on HQ)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -26822,6 +27501,9 @@
     <col width="40" customWidth="1" style="629" min="2" max="2"/>
     <col width="82.70999999999999" customWidth="1" style="629" min="3" max="3"/>
     <col width="26.14" customWidth="1" style="629" min="6" max="6"/>
+    <col width="18" customWidth="1" style="629" min="9" max="9"/>
+    <col width="13" customWidth="1" style="629" min="10" max="10"/>
+    <col width="60" customWidth="1" style="629" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27057,9 +27739,21 @@
       </c>
       <c r="G7" s="507" t="n"/>
       <c r="H7" s="507" t="n"/>
-      <c r="I7" s="507" t="n"/>
-      <c r="J7" s="507" t="n"/>
-      <c r="K7" s="507" t="n"/>
+      <c r="I7" s="140" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
+        </is>
+      </c>
       <c r="L7" s="507" t="n"/>
       <c r="M7" s="507" t="n"/>
       <c r="N7" s="507" t="n"/>
@@ -27097,9 +27791,17 @@
       <c r="F8" s="526" t="n"/>
       <c r="G8" s="507" t="n"/>
       <c r="H8" s="507" t="n"/>
-      <c r="I8" s="507" t="n"/>
-      <c r="J8" s="507" t="n"/>
-      <c r="K8" s="507" t="n"/>
+      <c r="I8" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="n"/>
       <c r="L8" s="507" t="n"/>
       <c r="M8" s="507" t="n"/>
       <c r="N8" s="507" t="n"/>
@@ -27137,9 +27839,17 @@
       <c r="F9" s="526" t="n"/>
       <c r="G9" s="507" t="n"/>
       <c r="H9" s="507" t="n"/>
-      <c r="I9" s="507" t="n"/>
-      <c r="J9" s="507" t="n"/>
-      <c r="K9" s="529" t="inlineStr">
+      <c r="I9" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">       </t>
         </is>
@@ -27183,9 +27893,17 @@
       <c r="F10" s="526" t="n"/>
       <c r="G10" s="507" t="n"/>
       <c r="H10" s="507" t="n"/>
-      <c r="I10" s="507" t="n"/>
-      <c r="J10" s="507" t="n"/>
-      <c r="K10" s="507" t="n"/>
+      <c r="I10" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="n"/>
       <c r="L10" s="507" t="n"/>
       <c r="M10" s="507" t="n"/>
       <c r="N10" s="507" t="n"/>
@@ -27226,9 +27944,17 @@
       <c r="F11" s="526" t="n"/>
       <c r="G11" s="507" t="n"/>
       <c r="H11" s="507" t="n"/>
-      <c r="I11" s="507" t="n"/>
-      <c r="J11" s="507" t="n"/>
-      <c r="K11" s="507" t="n"/>
+      <c r="I11" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="n"/>
       <c r="L11" s="507" t="n"/>
       <c r="M11" s="507" t="n"/>
       <c r="N11" s="507" t="n"/>
@@ -27268,9 +27994,17 @@
       <c r="F12" s="526" t="n"/>
       <c r="G12" s="507" t="n"/>
       <c r="H12" s="507" t="n"/>
-      <c r="I12" s="507" t="n"/>
-      <c r="J12" s="507" t="n"/>
-      <c r="K12" s="507" t="n"/>
+      <c r="I12" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="n"/>
       <c r="L12" s="507" t="n"/>
       <c r="M12" s="507" t="n"/>
       <c r="N12" s="507" t="n"/>
@@ -27311,9 +28045,17 @@
       <c r="F13" s="526" t="n"/>
       <c r="G13" s="507" t="n"/>
       <c r="H13" s="507" t="n"/>
-      <c r="I13" s="507" t="n"/>
-      <c r="J13" s="507" t="n"/>
-      <c r="K13" s="507" t="n"/>
+      <c r="I13" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="0" t="n"/>
       <c r="L13" s="507" t="n"/>
       <c r="M13" s="507" t="n"/>
       <c r="N13" s="507" t="n"/>
@@ -27354,9 +28096,17 @@
       <c r="F14" s="526" t="n"/>
       <c r="G14" s="507" t="n"/>
       <c r="H14" s="507" t="n"/>
-      <c r="I14" s="507" t="n"/>
-      <c r="J14" s="507" t="n"/>
-      <c r="K14" s="507" t="n"/>
+      <c r="I14" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" s="0" t="n"/>
       <c r="L14" s="507" t="n"/>
       <c r="M14" s="507" t="n"/>
       <c r="N14" s="507" t="n"/>
@@ -27397,9 +28147,17 @@
       <c r="F15" s="526" t="n"/>
       <c r="G15" s="507" t="n"/>
       <c r="H15" s="507" t="n"/>
-      <c r="I15" s="507" t="n"/>
-      <c r="J15" s="507" t="n"/>
-      <c r="K15" s="507" t="n"/>
+      <c r="I15" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K15" s="0" t="n"/>
       <c r="L15" s="507" t="n"/>
       <c r="M15" s="507" t="n"/>
       <c r="N15" s="507" t="n"/>
@@ -27440,9 +28198,17 @@
       <c r="F16" s="526" t="n"/>
       <c r="G16" s="507" t="n"/>
       <c r="H16" s="507" t="n"/>
-      <c r="I16" s="507" t="n"/>
-      <c r="J16" s="507" t="n"/>
-      <c r="K16" s="507" t="n"/>
+      <c r="I16" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" s="0" t="n"/>
       <c r="L16" s="507" t="n"/>
       <c r="M16" s="507" t="n"/>
       <c r="N16" s="507" t="n"/>
@@ -27485,9 +28251,17 @@
       <c r="F17" s="526" t="n"/>
       <c r="G17" s="507" t="n"/>
       <c r="H17" s="507" t="n"/>
-      <c r="I17" s="507" t="n"/>
-      <c r="J17" s="507" t="n"/>
-      <c r="K17" s="507" t="n"/>
+      <c r="I17" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K17" s="0" t="n"/>
       <c r="L17" s="507" t="n"/>
       <c r="M17" s="507" t="n"/>
       <c r="N17" s="507" t="n"/>
@@ -27527,9 +28301,17 @@
       <c r="F18" s="526" t="n"/>
       <c r="G18" s="507" t="n"/>
       <c r="H18" s="507" t="n"/>
-      <c r="I18" s="507" t="n"/>
-      <c r="J18" s="507" t="n"/>
-      <c r="K18" s="507" t="n"/>
+      <c r="I18" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" s="0" t="n"/>
       <c r="L18" s="507" t="n"/>
       <c r="M18" s="507" t="n"/>
       <c r="N18" s="507" t="n"/>
@@ -27573,9 +28355,17 @@
       <c r="F19" s="526" t="n"/>
       <c r="G19" s="507" t="n"/>
       <c r="H19" s="507" t="n"/>
-      <c r="I19" s="507" t="n"/>
-      <c r="J19" s="507" t="n"/>
-      <c r="K19" s="507" t="n"/>
+      <c r="I19" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K19" s="0" t="n"/>
       <c r="L19" s="507" t="n"/>
       <c r="M19" s="507" t="n"/>
       <c r="N19" s="507" t="n"/>
@@ -27616,9 +28406,17 @@
       <c r="F20" s="526" t="n"/>
       <c r="G20" s="507" t="n"/>
       <c r="H20" s="507" t="n"/>
-      <c r="I20" s="507" t="n"/>
-      <c r="J20" s="507" t="n"/>
-      <c r="K20" s="507" t="n"/>
+      <c r="I20" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K20" s="0" t="n"/>
       <c r="L20" s="507" t="n"/>
       <c r="M20" s="507" t="n"/>
       <c r="N20" s="507" t="n"/>
@@ -27661,9 +28459,17 @@
       <c r="F21" s="198" t="n"/>
       <c r="G21" s="507" t="n"/>
       <c r="H21" s="507" t="n"/>
-      <c r="I21" s="507" t="n"/>
-      <c r="J21" s="507" t="n"/>
-      <c r="K21" s="507" t="n"/>
+      <c r="I21" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J21" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K21" s="0" t="n"/>
       <c r="L21" s="507" t="n"/>
       <c r="M21" s="507" t="n"/>
       <c r="N21" s="507" t="n"/>
@@ -27713,9 +28519,17 @@
       <c r="F22" s="198" t="n"/>
       <c r="G22" s="507" t="n"/>
       <c r="H22" s="507" t="n"/>
-      <c r="I22" s="507" t="n"/>
-      <c r="J22" s="507" t="n"/>
-      <c r="K22" s="507" t="n"/>
+      <c r="I22" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J22" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K22" s="0" t="n"/>
       <c r="L22" s="507" t="n"/>
       <c r="M22" s="507" t="n"/>
       <c r="N22" s="507" t="n"/>
@@ -27765,9 +28579,17 @@
       <c r="F23" s="198" t="n"/>
       <c r="G23" s="507" t="n"/>
       <c r="H23" s="507" t="n"/>
-      <c r="I23" s="507" t="n"/>
-      <c r="J23" s="507" t="n"/>
-      <c r="K23" s="507" t="n"/>
+      <c r="I23" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J23" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" s="0" t="n"/>
       <c r="L23" s="507" t="n"/>
       <c r="M23" s="507" t="n"/>
       <c r="N23" s="507" t="n"/>
@@ -30467,7 +31289,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.29" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="17.71" customWidth="1" style="629" min="1" max="1"/>
@@ -30476,6 +31298,9 @@
     <col width="21.57" customWidth="1" style="629" min="4" max="4"/>
     <col width="42.14" customWidth="1" style="629" min="5" max="5"/>
     <col width="43.57" customWidth="1" style="629" min="6" max="6"/>
+    <col width="18" customWidth="1" style="629" min="9" max="9"/>
+    <col width="13" customWidth="1" style="629" min="10" max="10"/>
+    <col width="60" customWidth="1" style="629" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30595,6 +31420,21 @@
         </is>
       </c>
       <c r="F7" s="204" t="n"/>
+      <c r="I7" s="140" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="521" t="inlineStr">
@@ -30621,6 +31461,17 @@
         </is>
       </c>
       <c r="F8" s="204" t="n"/>
+      <c r="I8" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="521" t="inlineStr">
@@ -30643,6 +31494,17 @@
       <c r="D9" s="564" t="n"/>
       <c r="E9" s="539" t="n"/>
       <c r="F9" s="204" t="n"/>
+      <c r="I9" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="521" t="inlineStr">
@@ -30671,6 +31533,17 @@
         </is>
       </c>
       <c r="F10" s="204" t="n"/>
+      <c r="I10" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="548" t="n"/>
@@ -30701,6 +31574,17 @@
         </is>
       </c>
       <c r="F12" s="204" t="n"/>
+      <c r="I12" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="521" t="inlineStr">
@@ -30719,6 +31603,17 @@
       <c r="D13" s="564" t="n"/>
       <c r="E13" s="349" t="n"/>
       <c r="F13" s="204" t="n"/>
+      <c r="I13" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="0" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="521" t="inlineStr">
@@ -30740,6 +31635,17 @@
       <c r="D14" s="564" t="n"/>
       <c r="E14" s="387" t="n"/>
       <c r="F14" s="204" t="n"/>
+      <c r="I14" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" s="0" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -30782,7 +31688,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.29" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="17.71" customWidth="1" style="629" min="1" max="1"/>
@@ -30791,6 +31697,9 @@
     <col width="21.57" customWidth="1" style="629" min="4" max="4"/>
     <col width="42.14" customWidth="1" style="629" min="5" max="5"/>
     <col width="43.57" customWidth="1" style="629" min="6" max="6"/>
+    <col width="18" customWidth="1" style="629" min="9" max="9"/>
+    <col width="13" customWidth="1" style="629" min="10" max="10"/>
+    <col width="60" customWidth="1" style="629" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30902,6 +31811,21 @@
       <c r="D7" s="537" t="n"/>
       <c r="E7" s="536" t="n"/>
       <c r="F7" s="204" t="n"/>
+      <c r="I7" s="140" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="387" t="inlineStr">
@@ -30927,6 +31851,21 @@
       <c r="D8" s="564" t="n"/>
       <c r="E8" s="539" t="n"/>
       <c r="F8" s="204" t="n"/>
+      <c r="I8" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/mapbox/mapbox_01_05_gps_capture_and_case_list.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="387" t="inlineStr">
@@ -30955,6 +31894,17 @@
       <c r="D9" s="564" t="n"/>
       <c r="E9" s="539" t="n"/>
       <c r="F9" s="204" t="n"/>
+      <c r="I9" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="387" t="inlineStr">
@@ -30978,6 +31928,17 @@
       <c r="D10" s="564" t="n"/>
       <c r="E10" s="539" t="n"/>
       <c r="F10" s="204" t="n"/>
+      <c r="I10" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="387" t="inlineStr">
@@ -31001,6 +31962,21 @@
       <c r="D11" s="564" t="n"/>
       <c r="E11" s="539" t="n"/>
       <c r="F11" s="204" t="n"/>
+      <c r="I11" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/mapbox/mapbox_04_location_permission_denied.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="387" t="inlineStr">
@@ -31021,6 +31997,21 @@
       <c r="D12" s="564" t="n"/>
       <c r="E12" s="539" t="n"/>
       <c r="F12" s="204" t="n"/>
+      <c r="I12" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/mapbox/mapbox_01_05_gps_capture_and_case_list.yaml</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -31062,13 +32053,16 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.29" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="27.86" customWidth="1" style="629" min="1" max="1"/>
     <col width="28" customWidth="1" style="629" min="2" max="2"/>
     <col width="66.29000000000001" customWidth="1" style="629" min="3" max="3"/>
     <col width="24.57" customWidth="1" style="629" min="6" max="6"/>
+    <col width="18" customWidth="1" style="629" min="9" max="9"/>
+    <col width="13" customWidth="1" style="629" min="10" max="10"/>
+    <col width="60" customWidth="1" style="629" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31179,6 +32173,21 @@
         </is>
       </c>
       <c r="G6" s="535" t="n"/>
+      <c r="I6" s="140" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J6" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K6" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="556" t="inlineStr">
@@ -31217,6 +32226,21 @@
       <c r="E8" s="564" t="n"/>
       <c r="F8" s="564" t="n"/>
       <c r="G8" s="382" t="n"/>
+      <c r="I8" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/text_to_speech/tts_01_02_enable_and_audio_button.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="387" t="inlineStr">
@@ -31242,6 +32266,21 @@
       <c r="E9" s="564" t="n"/>
       <c r="F9" s="564" t="n"/>
       <c r="G9" s="382" t="n"/>
+      <c r="I9" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/text_to_speech/tts_01_02_enable_and_audio_button.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="387" t="inlineStr">
@@ -31268,6 +32307,21 @@
       <c r="E10" s="564" t="n"/>
       <c r="F10" s="564" t="n"/>
       <c r="G10" s="382" t="n"/>
+      <c r="I10" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/text_to_speech/tts_03_form_language_change.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="387" t="inlineStr">
@@ -31293,6 +32347,21 @@
       <c r="E11" s="564" t="n"/>
       <c r="F11" s="564" t="n"/>
       <c r="G11" s="382" t="n"/>
+      <c r="I11" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/text_to_speech/tts_04_app_language_change.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="387" t="inlineStr">
@@ -31328,6 +32397,17 @@
         </is>
       </c>
       <c r="G12" s="382" t="n"/>
+      <c r="I12" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="575" t="inlineStr">
@@ -31353,6 +32433,17 @@
       <c r="E13" s="578" t="n"/>
       <c r="F13" s="578" t="n"/>
       <c r="G13" s="382" t="n"/>
+      <c r="I13" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="0" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -31393,13 +32484,16 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.29" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="27.86" customWidth="1" style="629" min="1" max="1"/>
     <col width="28" customWidth="1" style="629" min="2" max="2"/>
     <col width="66.29000000000001" customWidth="1" style="629" min="3" max="3"/>
     <col width="24.57" customWidth="1" style="629" min="6" max="6"/>
+    <col width="18" customWidth="1" style="629" min="9" max="9"/>
+    <col width="13" customWidth="1" style="629" min="10" max="10"/>
+    <col width="60" customWidth="1" style="629" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31510,6 +32604,21 @@
         </is>
       </c>
       <c r="G6" s="535" t="n"/>
+      <c r="I6" s="140" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J6" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K6" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="561" t="inlineStr">
@@ -31546,6 +32655,17 @@
       <c r="E8" s="564" t="n"/>
       <c r="F8" s="564" t="n"/>
       <c r="G8" s="382" t="n"/>
+      <c r="I8" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="387" t="inlineStr">
@@ -31568,6 +32688,21 @@
       <c r="E9" s="564" t="n"/>
       <c r="F9" s="564" t="n"/>
       <c r="G9" s="382" t="n"/>
+      <c r="I9" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/third_party_scanner/scanner_02_06_intent_callout_setting.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="387" t="inlineStr">
@@ -31594,6 +32729,17 @@
       <c r="E10" s="564" t="n"/>
       <c r="F10" s="564" t="n"/>
       <c r="G10" s="382" t="n"/>
+      <c r="I10" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="387" t="inlineStr">
@@ -31616,6 +32762,17 @@
       <c r="E11" s="564" t="n"/>
       <c r="F11" s="564" t="n"/>
       <c r="G11" s="382" t="n"/>
+      <c r="I11" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="387" t="inlineStr">
@@ -31641,6 +32798,17 @@
       <c r="E12" s="564" t="n"/>
       <c r="F12" s="564" t="n"/>
       <c r="G12" s="382" t="n"/>
+      <c r="I12" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="387" t="inlineStr">
@@ -31665,6 +32833,21 @@
       <c r="E13" s="564" t="n"/>
       <c r="F13" s="564" t="n"/>
       <c r="G13" s="382" t="n"/>
+      <c r="I13" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K13" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/third_party_scanner/scanner_02_06_intent_callout_setting.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="387" t="inlineStr">
@@ -31690,6 +32873,17 @@
       <c r="E14" s="564" t="n"/>
       <c r="F14" s="564" t="n"/>
       <c r="G14" s="382" t="n"/>
+      <c r="I14" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" s="0" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -31731,7 +32925,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.29" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="25" customWidth="1" style="629" min="1" max="1"/>
@@ -31739,6 +32933,9 @@
     <col width="73" customWidth="1" style="629" min="3" max="3"/>
     <col width="20.43" customWidth="1" style="629" min="4" max="4"/>
     <col width="17.14" customWidth="1" style="629" min="5" max="6"/>
+    <col width="18" customWidth="1" style="629" min="9" max="9"/>
+    <col width="13" customWidth="1" style="629" min="10" max="10"/>
+    <col width="60" customWidth="1" style="629" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31844,6 +33041,21 @@
       <c r="F6" s="568" t="inlineStr">
         <is>
           <t>Notes</t>
+        </is>
+      </c>
+      <c r="I6" s="140" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J6" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K6" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
         </is>
       </c>
     </row>
@@ -31886,6 +33098,21 @@
       <c r="D8" s="477" t="n"/>
       <c r="E8" s="625" t="n"/>
       <c r="F8" s="625" t="n"/>
+      <c r="I8" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/advanced_settings/custom_properties_01_offer_pin_for_login.yaml (written; awaiting a passing run)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="477" t="inlineStr">
@@ -31911,6 +33138,21 @@
       <c r="D9" s="477" t="n"/>
       <c r="E9" s="625" t="n"/>
       <c r="F9" s="625" t="n"/>
+      <c r="I9" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/advanced_settings/custom_properties_02_home_report.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="477" t="inlineStr">
@@ -31935,6 +33177,17 @@
       <c r="D10" s="477" t="n"/>
       <c r="E10" s="625" t="n"/>
       <c r="F10" s="625" t="n"/>
+      <c r="I10" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="477" t="inlineStr">
@@ -31962,6 +33215,21 @@
       <c r="D11" s="477" t="n"/>
       <c r="E11" s="625" t="n"/>
       <c r="F11" s="625" t="n"/>
+      <c r="I11" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/advanced_settings/custom_properties_04_superuser_developer_options.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="477" t="inlineStr">
@@ -31986,6 +33254,21 @@
       <c r="D12" s="477" t="n"/>
       <c r="E12" s="625" t="n"/>
       <c r="F12" s="625" t="n"/>
+      <c r="I12" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/advanced_settings/custom_properties_05_show_update_target_options.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="477" t="inlineStr">
@@ -32008,6 +33291,21 @@
       <c r="D13" s="477" t="n"/>
       <c r="E13" s="625" t="n"/>
       <c r="F13" s="625" t="n"/>
+      <c r="I13" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K13" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/advanced_settings/custom_properties_06_hide_issue_report.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="477" t="inlineStr">
@@ -32034,6 +33332,21 @@
       <c r="D14" s="477" t="n"/>
       <c r="E14" s="625" t="n"/>
       <c r="F14" s="625" t="n"/>
+      <c r="I14" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K14" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/advanced_settings/custom_properties_07_no_space_in_select_choices.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="477" t="inlineStr">
@@ -32059,6 +33372,21 @@
       <c r="D15" s="477" t="n"/>
       <c r="E15" s="625" t="n"/>
       <c r="F15" s="625" t="n"/>
+      <c r="I15" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K15" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/advanced_settings/custom_properties_08_alternate_question_text_format.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="477" t="inlineStr">
@@ -32084,6 +33412,21 @@
       <c r="D16" s="477" t="n"/>
       <c r="E16" s="625" t="n"/>
       <c r="F16" s="625" t="n"/>
+      <c r="I16" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K16" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/advanced_settings/custom_properties_09_detail_final_swipe_disabled.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="477" t="inlineStr">
@@ -32107,6 +33450,21 @@
       <c r="D17" s="477" t="n"/>
       <c r="E17" s="625" t="n"/>
       <c r="F17" s="625" t="n"/>
+      <c r="I17" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K17" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/advanced_settings/custom_properties_10_list_refresh.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="477" t="inlineStr">
@@ -32136,6 +33494,21 @@
       <c r="D18" s="477" t="n"/>
       <c r="E18" s="625" t="n"/>
       <c r="F18" s="625" t="n"/>
+      <c r="I18" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K18" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/advanced_settings/custom_properties_11_update_target_release.yaml (run via scripts/run_targeted_updates_check.py; awaiting a passing run)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="477" t="inlineStr">
@@ -32163,6 +33536,21 @@
       <c r="D19" s="477" t="n"/>
       <c r="E19" s="625" t="n"/>
       <c r="F19" s="625" t="n"/>
+      <c r="I19" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K19" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/advanced_settings/custom_properties_12_update_target_build.yaml (run via scripts/run_targeted_updates_check.py; awaiting a passing run)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="477" t="inlineStr">
@@ -32191,6 +33579,21 @@
       <c r="D20" s="477" t="n"/>
       <c r="E20" s="625" t="n"/>
       <c r="F20" s="625" t="n"/>
+      <c r="I20" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K20" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/advanced_settings/custom_properties_13_update_target_save.yaml (run via scripts/run_targeted_updates_check.py; awaiting a passing run)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="477" t="inlineStr">
@@ -32218,6 +33621,21 @@
       <c r="D21" s="477" t="n"/>
       <c r="E21" s="625" t="n"/>
       <c r="F21" s="625" t="n"/>
+      <c r="I21" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J21" s="0" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K21" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/advanced_settings/custom_properties_14_pre_update_sync_needed.yaml (run via scripts/run_targeted_updates_check.py; awaiting a passing run)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="477" t="inlineStr">
@@ -32254,6 +33672,21 @@
         <is>
           <t>Note: 
 Here the Incomplete Forms are not shown directly. Its seen under option 'Saved Forms' and filter update to 'Only Incomplete Forms'  then will show the incomplete forms.</t>
+        </is>
+      </c>
+      <c r="I22" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J22" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K22" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/advanced_settings/custom_properties_15_root_menu_as_home_screen.yaml</t>
         </is>
       </c>
     </row>
@@ -32290,6 +33723,17 @@
       <c r="D23" s="477" t="n"/>
       <c r="E23" s="625" t="n"/>
       <c r="F23" s="625" t="n"/>
+      <c r="I23" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J23" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" s="0" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="628" t="inlineStr">
@@ -32326,6 +33770,21 @@
       <c r="D25" s="477" t="n"/>
       <c r="E25" s="625" t="n"/>
       <c r="F25" s="625" t="n"/>
+      <c r="I25" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J25" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K25" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/advanced_settings/settings_01_grid_menu_display.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="477" t="inlineStr">
@@ -32352,6 +33811,17 @@
       <c r="D26" s="477" t="n"/>
       <c r="E26" s="625" t="n"/>
       <c r="F26" s="625" t="n"/>
+      <c r="I26" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J26" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K26" s="0" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="477" t="inlineStr">
@@ -32377,6 +33847,17 @@
       <c r="D27" s="477" t="n"/>
       <c r="E27" s="625" t="n"/>
       <c r="F27" s="625" t="n"/>
+      <c r="I27" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J27" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K27" s="0" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="477" t="inlineStr">
@@ -32399,6 +33880,21 @@
       <c r="D28" s="477" t="n"/>
       <c r="E28" s="625" t="n"/>
       <c r="F28" s="625" t="n"/>
+      <c r="I28" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J28" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K28" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/advanced_settings/settings_04_asterisk_on_required_question.yaml</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -32445,13 +33941,16 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.29" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="34.43" customWidth="1" style="629" min="2" max="2"/>
     <col width="75.29000000000001" customWidth="1" style="629" min="3" max="3"/>
     <col width="24.14" customWidth="1" style="629" min="4" max="4"/>
     <col width="21.14" customWidth="1" style="629" min="5" max="5"/>
+    <col width="18" customWidth="1" style="629" min="9" max="9"/>
+    <col width="13" customWidth="1" style="629" min="10" max="10"/>
+    <col width="60" customWidth="1" style="629" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32547,6 +34046,21 @@
           <t>Notes/Ticket ID</t>
         </is>
       </c>
+      <c r="I6" s="140" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J6" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K6" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="580" t="inlineStr">
@@ -32569,6 +34083,21 @@
       </c>
       <c r="D7" s="580" t="n"/>
       <c r="E7" s="590" t="n"/>
+      <c r="I7" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>scripts/run_appium_non_core_upgrade_suite.py --scenario performance_upgrade (awaiting a live run)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="580" t="inlineStr">
@@ -32590,6 +34119,21 @@
       </c>
       <c r="D8" s="580" t="n"/>
       <c r="E8" s="590" t="n"/>
+      <c r="I8" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>scripts/run_appium_non_core_upgrade_suite.py --scenario performance_upgrade (awaiting a live run)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="591" t="inlineStr">
@@ -32615,6 +34159,21 @@
       <c r="E9" s="591" t="inlineStr">
         <is>
           <t>Comments (if any)</t>
+        </is>
+      </c>
+      <c r="I9" s="140" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
         </is>
       </c>
     </row>
@@ -32637,6 +34196,21 @@
       </c>
       <c r="D10" s="596" t="n"/>
       <c r="E10" s="596" t="n"/>
+      <c r="I10" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/performance_tests/perf_rows_01_02_login_screen_and_home_load.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="600" t="n">
@@ -32656,6 +34230,21 @@
       </c>
       <c r="D11" s="596" t="n"/>
       <c r="E11" s="596" t="n"/>
+      <c r="I11" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/performance_tests/perf_rows_01_02_login_screen_and_home_load.yaml</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -32697,13 +34286,16 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.29" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="34.43" customWidth="1" style="629" min="2" max="2"/>
     <col width="75.29000000000001" customWidth="1" style="629" min="3" max="3"/>
     <col width="24.14" customWidth="1" style="629" min="4" max="4"/>
     <col width="21.14" customWidth="1" style="629" min="5" max="6"/>
+    <col width="18" customWidth="1" style="629" min="9" max="9"/>
+    <col width="13" customWidth="1" style="629" min="10" max="10"/>
+    <col width="60" customWidth="1" style="629" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32840,6 +34432,21 @@
           <t>Ticket ID</t>
         </is>
       </c>
+      <c r="I8" s="140" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="198" t="inlineStr">
@@ -32863,6 +34470,21 @@
       <c r="D9" s="622" t="n"/>
       <c r="E9" s="622" t="n"/>
       <c r="F9" s="622" t="n"/>
+      <c r="I9" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/case_list_optimization/cache_index_01_02_sorting_and_filter_sorting.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="198" t="inlineStr">
@@ -32886,6 +34508,21 @@
       <c r="D10" s="622" t="n"/>
       <c r="E10" s="622" t="n"/>
       <c r="F10" s="622" t="n"/>
+      <c r="I10" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/case_list_optimization/cache_index_01_02_sorting_and_filter_sorting.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="198" t="inlineStr">
@@ -32908,6 +34545,21 @@
       <c r="D11" s="622" t="n"/>
       <c r="E11" s="622" t="n"/>
       <c r="F11" s="622" t="n"/>
+      <c r="I11" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/case_list_optimization/cache_index_01_02_sorting_and_filter_sorting.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="198" t="inlineStr">
@@ -32930,6 +34582,21 @@
       <c r="D12" s="622" t="n"/>
       <c r="E12" s="622" t="n"/>
       <c r="F12" s="622" t="n"/>
+      <c r="I12" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/case_list_optimization/cache_index_01_02_sorting_and_filter_sorting.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="622" t="n"/>
@@ -32969,6 +34636,21 @@
       <c r="D15" s="622" t="n"/>
       <c r="E15" s="622" t="n"/>
       <c r="F15" s="622" t="n"/>
+      <c r="I15" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K15" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/case_list_optimization/load_time_01_optimization_disabled.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="198" t="inlineStr">
@@ -32993,6 +34675,21 @@
       <c r="D16" s="622" t="n"/>
       <c r="E16" s="622" t="n"/>
       <c r="F16" s="622" t="n"/>
+      <c r="I16" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K16" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/case_list_optimization/load_time_01_optimization_disabled.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="198" t="inlineStr">
@@ -33016,6 +34713,21 @@
       <c r="D17" s="622" t="n"/>
       <c r="E17" s="622" t="n"/>
       <c r="F17" s="622" t="n"/>
+      <c r="I17" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K17" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/case_list_optimization/load_time_02_cache.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="198" t="inlineStr">
@@ -33039,6 +34751,21 @@
       <c r="D18" s="622" t="n"/>
       <c r="E18" s="622" t="n"/>
       <c r="F18" s="622" t="n"/>
+      <c r="I18" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K18" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/case_list_optimization/load_time_03_lazy_load.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="198" t="inlineStr">
@@ -33063,6 +34790,21 @@
       <c r="D19" s="622" t="n"/>
       <c r="E19" s="622" t="n"/>
       <c r="F19" s="622" t="n"/>
+      <c r="I19" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K19" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/case_list_optimization/load_time_04_cache_and_lazy_load.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="198" t="inlineStr">
@@ -33087,6 +34829,21 @@
       <c r="D20" s="622" t="n"/>
       <c r="E20" s="622" t="n"/>
       <c r="F20" s="622" t="n"/>
+      <c r="I20" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K20" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/case_list_optimization/load_time_05_all_mix.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="198" t="inlineStr">
@@ -33110,6 +34867,21 @@
       <c r="D21" s="622" t="n"/>
       <c r="E21" s="622" t="n"/>
       <c r="F21" s="622" t="n"/>
+      <c r="I21" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J21" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K21" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/case_list_optimization/load_time_06_after_clear_app_data.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="198" t="inlineStr">
@@ -33133,6 +34905,21 @@
       <c r="D22" s="622" t="n"/>
       <c r="E22" s="622" t="n"/>
       <c r="F22" s="622" t="n"/>
+      <c r="I22" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J22" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K22" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/case_list_optimization/load_time_07_after_force_stop.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="198" t="inlineStr">
@@ -33156,6 +34943,21 @@
       <c r="D23" s="622" t="n"/>
       <c r="E23" s="622" t="n"/>
       <c r="F23" s="622" t="n"/>
+      <c r="I23" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J23" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K23" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/case_list_optimization/load_time_08_second_login.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="622" t="inlineStr">
@@ -33176,6 +34978,17 @@
       <c r="D24" s="622" t="n"/>
       <c r="E24" s="622" t="n"/>
       <c r="F24" s="622" t="n"/>
+      <c r="I24" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J24" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K24" s="0" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -33214,13 +35027,16 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.29" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="48.71" customWidth="1" style="629" min="2" max="2"/>
     <col hidden="1" width="75.29000000000001" customWidth="1" style="629" min="3" max="3"/>
     <col width="61" customWidth="1" style="629" min="4" max="4"/>
     <col width="21.14" customWidth="1" style="629" min="5" max="7"/>
+    <col width="18" customWidth="1" style="629" min="9" max="9"/>
+    <col width="13" customWidth="1" style="629" min="10" max="10"/>
+    <col width="60" customWidth="1" style="629" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -33259,6 +35075,21 @@
           <t>Comments</t>
         </is>
       </c>
+      <c r="I1" s="140" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K1" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="603" t="inlineStr">
@@ -33280,6 +35111,17 @@
       <c r="E2" s="608" t="n"/>
       <c r="F2" s="609" t="n"/>
       <c r="G2" s="609" t="n"/>
+      <c r="I2" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J2" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K2" s="0" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="603" t="inlineStr">
@@ -33302,6 +35144,17 @@
       <c r="E3" s="608" t="n"/>
       <c r="F3" s="609" t="n"/>
       <c r="G3" s="609" t="n"/>
+      <c r="I3" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J3" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K3" s="0" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="603" t="inlineStr">
@@ -33323,6 +35176,17 @@
       <c r="E4" s="608" t="n"/>
       <c r="F4" s="609" t="n"/>
       <c r="G4" s="616" t="n"/>
+      <c r="I4" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J4" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K4" s="0" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="603" t="inlineStr">
@@ -33344,6 +35208,21 @@
       <c r="E5" s="608" t="n"/>
       <c r="F5" s="616" t="n"/>
       <c r="G5" s="616" t="n"/>
+      <c r="I5" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J5" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K5" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/personal_id/tc_04_sign_up_menu_option.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="603" t="inlineStr">
@@ -33370,6 +35249,17 @@
       <c r="E6" s="618" t="n"/>
       <c r="F6" s="616" t="n"/>
       <c r="G6" s="616" t="n"/>
+      <c r="I6" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J6" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" s="0" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="603" t="inlineStr">
@@ -33394,6 +35284,17 @@
       <c r="E7" s="618" t="n"/>
       <c r="F7" s="616" t="n"/>
       <c r="G7" s="616" t="n"/>
+      <c r="I7" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="603" t="inlineStr">
@@ -33415,6 +35316,17 @@
       <c r="E8" s="618" t="n"/>
       <c r="F8" s="616" t="n"/>
       <c r="G8" s="616" t="n"/>
+      <c r="I8" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="603" t="inlineStr">
@@ -33437,6 +35349,17 @@
       <c r="E9" s="618" t="n"/>
       <c r="F9" s="616" t="n"/>
       <c r="G9" s="616" t="n"/>
+      <c r="I9" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="603" t="inlineStr">
@@ -33458,6 +35381,17 @@
       <c r="E10" s="618" t="n"/>
       <c r="F10" s="616" t="n"/>
       <c r="G10" s="616" t="n"/>
+      <c r="I10" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="603" t="inlineStr">
@@ -33480,6 +35414,17 @@
       <c r="E11" s="618" t="n"/>
       <c r="F11" s="616" t="n"/>
       <c r="G11" s="616" t="n"/>
+      <c r="I11" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="603" t="inlineStr">
@@ -33503,6 +35448,17 @@
       <c r="E12" s="618" t="n"/>
       <c r="F12" s="618" t="n"/>
       <c r="G12" s="616" t="n"/>
+      <c r="I12" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="603" t="inlineStr">
@@ -33525,6 +35481,17 @@
       <c r="E13" s="618" t="n"/>
       <c r="F13" s="618" t="n"/>
       <c r="G13" s="616" t="n"/>
+      <c r="I13" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="0" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="603" t="inlineStr">
@@ -33546,6 +35513,17 @@
       <c r="E14" s="618" t="n"/>
       <c r="F14" s="616" t="n"/>
       <c r="G14" s="616" t="n"/>
+      <c r="I14" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" s="0" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="603" t="inlineStr">
@@ -33568,6 +35546,17 @@
       <c r="E15" s="618" t="n"/>
       <c r="F15" s="616" t="n"/>
       <c r="G15" s="616" t="n"/>
+      <c r="I15" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K15" s="0" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="603" t="inlineStr">
@@ -33589,6 +35578,17 @@
       <c r="E16" s="618" t="n"/>
       <c r="F16" s="616" t="n"/>
       <c r="G16" s="616" t="n"/>
+      <c r="I16" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" s="0" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="603" t="inlineStr">
@@ -33611,6 +35611,17 @@
       <c r="E17" s="618" t="n"/>
       <c r="F17" s="616" t="n"/>
       <c r="G17" s="616" t="n"/>
+      <c r="I17" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K17" s="0" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="603" t="inlineStr">
@@ -33633,6 +35644,17 @@
       <c r="E18" s="618" t="n"/>
       <c r="F18" s="616" t="n"/>
       <c r="G18" s="616" t="n"/>
+      <c r="I18" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" s="0" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="603" t="inlineStr">
@@ -33655,6 +35677,17 @@
       <c r="E19" s="618" t="n"/>
       <c r="F19" s="616" t="n"/>
       <c r="G19" s="616" t="n"/>
+      <c r="I19" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K19" s="0" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="603" t="inlineStr">
@@ -33678,6 +35711,17 @@
       <c r="E20" s="618" t="n"/>
       <c r="F20" s="616" t="n"/>
       <c r="G20" s="616" t="n"/>
+      <c r="I20" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K20" s="0" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="603" t="inlineStr">
@@ -33702,6 +35746,17 @@
       <c r="E21" s="618" t="n"/>
       <c r="F21" s="616" t="n"/>
       <c r="G21" s="616" t="n"/>
+      <c r="I21" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J21" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K21" s="0" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="603" t="inlineStr">
@@ -33724,6 +35779,17 @@
       <c r="E22" s="618" t="n"/>
       <c r="F22" s="616" t="n"/>
       <c r="G22" s="616" t="n"/>
+      <c r="I22" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J22" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K22" s="0" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="603" t="inlineStr">
@@ -33746,6 +35812,17 @@
       <c r="E23" s="618" t="n"/>
       <c r="F23" s="616" t="n"/>
       <c r="G23" s="616" t="n"/>
+      <c r="I23" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J23" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" s="0" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="603" t="inlineStr">
@@ -33769,6 +35846,17 @@
       <c r="E24" s="618" t="n"/>
       <c r="F24" s="616" t="n"/>
       <c r="G24" s="616" t="n"/>
+      <c r="I24" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J24" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K24" s="0" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="603" t="inlineStr">
@@ -33792,6 +35880,17 @@
       <c r="E25" s="618" t="n"/>
       <c r="F25" s="616" t="n"/>
       <c r="G25" s="616" t="n"/>
+      <c r="I25" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J25" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K25" s="0" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="603" t="inlineStr">
@@ -33814,6 +35913,17 @@
       <c r="E26" s="618" t="n"/>
       <c r="F26" s="616" t="n"/>
       <c r="G26" s="616" t="n"/>
+      <c r="I26" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J26" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K26" s="0" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="603" t="inlineStr">
@@ -33837,6 +35947,17 @@
       <c r="E27" s="618" t="n"/>
       <c r="F27" s="616" t="n"/>
       <c r="G27" s="616" t="n"/>
+      <c r="I27" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J27" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K27" s="0" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="603" t="inlineStr">
@@ -33859,6 +35980,17 @@
       <c r="E28" s="618" t="n"/>
       <c r="F28" s="616" t="n"/>
       <c r="G28" s="616" t="n"/>
+      <c r="I28" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J28" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K28" s="0" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="603" t="inlineStr">
@@ -33881,6 +36013,17 @@
       <c r="E29" s="618" t="n"/>
       <c r="F29" s="616" t="n"/>
       <c r="G29" s="616" t="n"/>
+      <c r="I29" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J29" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K29" s="0" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="603" t="inlineStr">
@@ -33904,6 +36047,17 @@
       <c r="E30" s="618" t="n"/>
       <c r="F30" s="616" t="n"/>
       <c r="G30" s="616" t="n"/>
+      <c r="I30" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J30" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K30" s="0" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="603" t="inlineStr">
@@ -33927,6 +36081,17 @@
       <c r="E31" s="618" t="n"/>
       <c r="F31" s="616" t="n"/>
       <c r="G31" s="616" t="n"/>
+      <c r="I31" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J31" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K31" s="0" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="603" t="inlineStr">
@@ -33949,6 +36114,17 @@
       <c r="E32" s="618" t="n"/>
       <c r="F32" s="616" t="n"/>
       <c r="G32" s="616" t="n"/>
+      <c r="I32" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J32" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K32" s="0" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="603" t="inlineStr">
@@ -33970,6 +36146,17 @@
       <c r="E33" s="618" t="n"/>
       <c r="F33" s="616" t="n"/>
       <c r="G33" s="616" t="n"/>
+      <c r="I33" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J33" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K33" s="0" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="603" t="inlineStr">
@@ -33991,6 +36178,17 @@
       <c r="E34" s="618" t="n"/>
       <c r="F34" s="616" t="n"/>
       <c r="G34" s="616" t="n"/>
+      <c r="I34" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J34" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K34" s="0" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="603" t="inlineStr">
@@ -34013,6 +36211,17 @@
       <c r="E35" s="618" t="n"/>
       <c r="F35" s="616" t="n"/>
       <c r="G35" s="616" t="n"/>
+      <c r="I35" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J35" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K35" s="0" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="603" t="inlineStr">
@@ -34039,6 +36248,17 @@
       <c r="E36" s="618" t="n"/>
       <c r="F36" s="616" t="n"/>
       <c r="G36" s="616" t="n"/>
+      <c r="I36" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J36" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K36" s="0" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="603" t="inlineStr">
@@ -34061,6 +36281,17 @@
       <c r="E37" s="618" t="n"/>
       <c r="F37" s="616" t="n"/>
       <c r="G37" s="616" t="n"/>
+      <c r="I37" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J37" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K37" s="0" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="603" t="inlineStr">
@@ -34085,6 +36316,17 @@
       <c r="E38" s="618" t="n"/>
       <c r="F38" s="616" t="n"/>
       <c r="G38" s="616" t="n"/>
+      <c r="I38" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J38" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K38" s="0" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="603" t="inlineStr">
@@ -34108,6 +36350,17 @@
       <c r="E39" s="618" t="n"/>
       <c r="F39" s="616" t="n"/>
       <c r="G39" s="616" t="n"/>
+      <c r="I39" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J39" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K39" s="0" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="603" t="inlineStr">
@@ -34130,6 +36383,17 @@
       <c r="E40" s="618" t="n"/>
       <c r="F40" s="616" t="n"/>
       <c r="G40" s="616" t="n"/>
+      <c r="I40" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J40" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K40" s="0" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="603" t="inlineStr">
@@ -34155,6 +36419,17 @@
       <c r="E41" s="618" t="n"/>
       <c r="F41" s="616" t="n"/>
       <c r="G41" s="616" t="n"/>
+      <c r="I41" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J41" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K41" s="0" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="603" t="inlineStr">
@@ -34177,6 +36452,17 @@
       <c r="E42" s="618" t="n"/>
       <c r="F42" s="616" t="n"/>
       <c r="G42" s="616" t="n"/>
+      <c r="I42" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J42" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K42" s="0" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="603" t="inlineStr">
@@ -34198,6 +36484,17 @@
       <c r="E43" s="618" t="n"/>
       <c r="F43" s="616" t="n"/>
       <c r="G43" s="616" t="n"/>
+      <c r="I43" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J43" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K43" s="0" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="603" t="inlineStr">
@@ -34222,6 +36519,17 @@
       <c r="E44" s="618" t="n"/>
       <c r="F44" s="616" t="n"/>
       <c r="G44" s="616" t="n"/>
+      <c r="I44" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J44" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K44" s="0" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="603" t="inlineStr">
@@ -34243,6 +36551,17 @@
       <c r="E45" s="618" t="n"/>
       <c r="F45" s="616" t="n"/>
       <c r="G45" s="616" t="n"/>
+      <c r="I45" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J45" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K45" s="0" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="603" t="inlineStr">
@@ -34266,6 +36585,17 @@
       <c r="E46" s="618" t="n"/>
       <c r="F46" s="616" t="n"/>
       <c r="G46" s="616" t="n"/>
+      <c r="I46" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J46" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K46" s="0" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="603" t="inlineStr">
@@ -34289,6 +36619,17 @@
       <c r="E47" s="618" t="n"/>
       <c r="F47" s="616" t="n"/>
       <c r="G47" s="616" t="n"/>
+      <c r="I47" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J47" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K47" s="0" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="603" t="inlineStr">
@@ -34310,6 +36651,17 @@
       <c r="E48" s="618" t="n"/>
       <c r="F48" s="616" t="n"/>
       <c r="G48" s="616" t="n"/>
+      <c r="I48" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J48" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K48" s="0" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -36879,6 +39231,9 @@
     <col width="17.43" customWidth="1" style="629" min="5" max="5"/>
     <col width="24" customWidth="1" style="629" min="6" max="7"/>
     <col width="32.14" customWidth="1" style="629" min="8" max="8"/>
+    <col width="18" customWidth="1" style="629" min="9" max="9"/>
+    <col width="13" customWidth="1" style="629" min="10" max="10"/>
+    <col width="60" customWidth="1" style="629" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37050,9 +39405,21 @@
         </is>
       </c>
       <c r="H7" s="159" t="n"/>
-      <c r="I7" s="45" t="n"/>
-      <c r="J7" s="45" t="n"/>
-      <c r="K7" s="45" t="n"/>
+      <c r="I7" s="140" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
+        </is>
+      </c>
       <c r="L7" s="45" t="n"/>
     </row>
     <row r="8">
@@ -37082,9 +39449,21 @@
       <c r="F8" s="521" t="n"/>
       <c r="G8" s="521" t="n"/>
       <c r="H8" s="166" t="n"/>
-      <c r="I8" s="166" t="n"/>
-      <c r="J8" s="166" t="n"/>
-      <c r="K8" s="166" t="n"/>
+      <c r="I8" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>scripts/run_appium_non_core_upgrade_suite.py --scenario database_change_upgrade (awaiting a live run)</t>
+        </is>
+      </c>
       <c r="L8" s="166" t="n"/>
     </row>
     <row r="9">
@@ -37120,9 +39499,21 @@
       <c r="F9" s="521" t="n"/>
       <c r="G9" s="521" t="n"/>
       <c r="H9" s="166" t="n"/>
-      <c r="I9" s="166" t="n"/>
-      <c r="J9" s="166" t="n"/>
-      <c r="K9" s="166" t="n"/>
+      <c r="I9" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/database_change/database_change_10_12_change_logs.yaml</t>
+        </is>
+      </c>
       <c r="L9" s="166" t="n"/>
     </row>
     <row r="10">
@@ -37151,9 +39542,21 @@
       <c r="F10" s="521" t="n"/>
       <c r="G10" s="521" t="n"/>
       <c r="H10" s="166" t="n"/>
-      <c r="I10" s="166" t="n"/>
-      <c r="J10" s="166" t="n"/>
-      <c r="K10" s="166" t="n"/>
+      <c r="I10" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/database_change/database_change_10_12_change_logs.yaml</t>
+        </is>
+      </c>
       <c r="L10" s="166" t="n"/>
     </row>
     <row r="11">
@@ -37184,9 +39587,17 @@
       <c r="F11" s="521" t="n"/>
       <c r="G11" s="521" t="n"/>
       <c r="H11" s="166" t="n"/>
-      <c r="I11" s="166" t="n"/>
-      <c r="J11" s="166" t="n"/>
-      <c r="K11" s="166" t="n"/>
+      <c r="I11" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="n"/>
       <c r="L11" s="166" t="n"/>
     </row>
     <row r="12">
@@ -37269,9 +39680,17 @@
       <c r="F14" s="521" t="n"/>
       <c r="G14" s="521" t="n"/>
       <c r="H14" s="166" t="n"/>
-      <c r="I14" s="166" t="n"/>
-      <c r="J14" s="166" t="n"/>
-      <c r="K14" s="166" t="n"/>
+      <c r="I14" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" s="0" t="n"/>
       <c r="L14" s="166" t="n"/>
     </row>
     <row r="15">
@@ -37306,9 +39725,21 @@
       <c r="F15" s="521" t="n"/>
       <c r="G15" s="521" t="n"/>
       <c r="H15" s="166" t="n"/>
-      <c r="I15" s="166" t="n"/>
-      <c r="J15" s="166" t="n"/>
-      <c r="K15" s="166" t="n"/>
+      <c r="I15" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K15" s="0" t="inlineStr">
+        <is>
+          <t>scripts/run_appium_non_core_upgrade_suite.py --scenario database_change_upgrade (awaiting a live run)</t>
+        </is>
+      </c>
       <c r="L15" s="166" t="n"/>
     </row>
     <row r="16">
@@ -37343,9 +39774,17 @@
       <c r="F16" s="521" t="n"/>
       <c r="G16" s="521" t="n"/>
       <c r="H16" s="166" t="n"/>
-      <c r="I16" s="166" t="n"/>
-      <c r="J16" s="166" t="n"/>
-      <c r="K16" s="166" t="n"/>
+      <c r="I16" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" s="0" t="n"/>
       <c r="L16" s="166" t="n"/>
     </row>
     <row r="17">
@@ -37379,9 +39818,17 @@
       <c r="F17" s="521" t="n"/>
       <c r="G17" s="521" t="n"/>
       <c r="H17" s="166" t="n"/>
-      <c r="I17" s="166" t="n"/>
-      <c r="J17" s="166" t="n"/>
-      <c r="K17" s="166" t="n"/>
+      <c r="I17" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K17" s="0" t="n"/>
       <c r="L17" s="166" t="n"/>
     </row>
     <row r="18">
@@ -37415,9 +39862,17 @@
       <c r="F18" s="521" t="n"/>
       <c r="G18" s="521" t="n"/>
       <c r="H18" s="166" t="n"/>
-      <c r="I18" s="166" t="n"/>
-      <c r="J18" s="166" t="n"/>
-      <c r="K18" s="166" t="n"/>
+      <c r="I18" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" s="0" t="n"/>
       <c r="L18" s="166" t="n"/>
     </row>
     <row r="19">
@@ -37456,9 +39911,17 @@
         </is>
       </c>
       <c r="H19" s="166" t="n"/>
-      <c r="I19" s="166" t="n"/>
-      <c r="J19" s="166" t="n"/>
-      <c r="K19" s="166" t="n"/>
+      <c r="I19" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K19" s="0" t="n"/>
       <c r="L19" s="166" t="n"/>
     </row>
     <row r="20">
@@ -37515,9 +39978,21 @@
       <c r="F21" s="521" t="n"/>
       <c r="G21" s="521" t="n"/>
       <c r="H21" s="166" t="n"/>
-      <c r="I21" s="166" t="n"/>
-      <c r="J21" s="166" t="n"/>
-      <c r="K21" s="166" t="n"/>
+      <c r="I21" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J21" s="0" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K21" s="0" t="inlineStr">
+        <is>
+          <t>scripts/run_appium_non_core_upgrade_suite.py --scenario database_change_upgrade (awaiting a live run)</t>
+        </is>
+      </c>
       <c r="L21" s="166" t="n"/>
     </row>
     <row r="22">
@@ -37544,9 +40019,21 @@
       <c r="F22" s="521" t="n"/>
       <c r="G22" s="521" t="n"/>
       <c r="H22" s="166" t="n"/>
-      <c r="I22" s="166" t="n"/>
-      <c r="J22" s="166" t="n"/>
-      <c r="K22" s="166" t="n"/>
+      <c r="I22" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J22" s="0" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K22" s="0" t="inlineStr">
+        <is>
+          <t>scripts/run_appium_non_core_upgrade_suite.py --scenario database_change_upgrade (awaiting a live run)</t>
+        </is>
+      </c>
       <c r="L22" s="166" t="n"/>
     </row>
     <row r="23">
@@ -37572,9 +40059,17 @@
       <c r="F23" s="521" t="n"/>
       <c r="G23" s="521" t="n"/>
       <c r="H23" s="166" t="n"/>
-      <c r="I23" s="166" t="n"/>
-      <c r="J23" s="166" t="n"/>
-      <c r="K23" s="166" t="n"/>
+      <c r="I23" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J23" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" s="0" t="n"/>
       <c r="L23" s="166" t="n"/>
     </row>
     <row r="24">
@@ -37600,9 +40095,17 @@
       <c r="F24" s="521" t="n"/>
       <c r="G24" s="521" t="n"/>
       <c r="H24" s="166" t="n"/>
-      <c r="I24" s="166" t="n"/>
-      <c r="J24" s="166" t="n"/>
-      <c r="K24" s="166" t="n"/>
+      <c r="I24" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J24" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K24" s="0" t="n"/>
       <c r="L24" s="166" t="n"/>
     </row>
     <row r="25">
@@ -37683,9 +40186,21 @@
       <c r="F27" s="521" t="n"/>
       <c r="G27" s="521" t="n"/>
       <c r="H27" s="166" t="n"/>
-      <c r="I27" s="166" t="n"/>
-      <c r="J27" s="166" t="n"/>
-      <c r="K27" s="166" t="n"/>
+      <c r="I27" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J27" s="0" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K27" s="0" t="inlineStr">
+        <is>
+          <t>scripts/run_appium_non_core_upgrade_suite.py --scenario database_change_upgrade (awaiting a live run)</t>
+        </is>
+      </c>
       <c r="L27" s="166" t="n"/>
     </row>
     <row r="28">
@@ -37727,9 +40242,17 @@
       <c r="F28" s="195" t="n"/>
       <c r="G28" s="195" t="n"/>
       <c r="H28" s="166" t="n"/>
-      <c r="I28" s="166" t="n"/>
-      <c r="J28" s="166" t="n"/>
-      <c r="K28" s="166" t="n"/>
+      <c r="I28" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J28" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K28" s="0" t="n"/>
       <c r="L28" s="166" t="n"/>
     </row>
     <row r="29">
@@ -37769,9 +40292,21 @@
       <c r="F29" s="195" t="n"/>
       <c r="G29" s="195" t="n"/>
       <c r="H29" s="166" t="n"/>
-      <c r="I29" s="166" t="n"/>
-      <c r="J29" s="166" t="n"/>
-      <c r="K29" s="166" t="n"/>
+      <c r="I29" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J29" s="0" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K29" s="0" t="inlineStr">
+        <is>
+          <t>scripts/run_appium_non_core_upgrade_suite.py --scenario database_change_upgrade (awaiting a live run)</t>
+        </is>
+      </c>
       <c r="L29" s="166" t="n"/>
     </row>
     <row r="30">
@@ -37848,9 +40383,21 @@
         </is>
       </c>
       <c r="H32" s="166" t="n"/>
-      <c r="I32" s="166" t="n"/>
-      <c r="J32" s="166" t="n"/>
-      <c r="K32" s="166" t="n"/>
+      <c r="I32" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J32" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K32" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/database_change/database_change_10_12_change_logs.yaml</t>
+        </is>
+      </c>
       <c r="L32" s="166" t="n"/>
     </row>
     <row r="33">
@@ -37886,9 +40433,21 @@
         </is>
       </c>
       <c r="H33" s="166" t="n"/>
-      <c r="I33" s="166" t="n"/>
-      <c r="J33" s="166" t="n"/>
-      <c r="K33" s="166" t="n"/>
+      <c r="I33" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J33" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K33" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/database_change/database_change_10_12_change_logs.yaml</t>
+        </is>
+      </c>
       <c r="L33" s="166" t="n"/>
     </row>
     <row r="34">
@@ -37921,9 +40480,21 @@
       <c r="F34" s="204" t="n"/>
       <c r="G34" s="204" t="n"/>
       <c r="H34" s="166" t="n"/>
-      <c r="I34" s="166" t="n"/>
-      <c r="J34" s="166" t="n"/>
-      <c r="K34" s="166" t="n"/>
+      <c r="I34" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J34" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K34" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/database_change/database_change_10_12_change_logs.yaml</t>
+        </is>
+      </c>
       <c r="L34" s="166" t="n"/>
     </row>
     <row r="35">
@@ -37953,9 +40524,17 @@
       <c r="F35" s="204" t="n"/>
       <c r="G35" s="204" t="n"/>
       <c r="H35" s="166" t="n"/>
-      <c r="I35" s="166" t="n"/>
-      <c r="J35" s="166" t="n"/>
-      <c r="K35" s="166" t="n"/>
+      <c r="I35" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J35" s="0" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K35" s="0" t="n"/>
       <c r="L35" s="166" t="n"/>
     </row>
   </sheetData>
@@ -38011,7 +40590,9 @@
     <col width="30.71" customWidth="1" style="629" min="6" max="6"/>
     <col width="19" customWidth="1" style="629" min="7" max="7"/>
     <col width="29.43" customWidth="1" style="629" min="8" max="8"/>
-    <col width="8.710000000000001" customWidth="1" style="629" min="9" max="14"/>
+    <col width="18" customWidth="1" style="629" min="9" max="14"/>
+    <col width="13" customWidth="1" style="629" min="10" max="10"/>
+    <col width="60" customWidth="1" style="629" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1" s="629">
@@ -38192,9 +40773,21 @@
       </c>
       <c r="G7" s="183" t="n"/>
       <c r="H7" s="175" t="n"/>
-      <c r="I7" s="175" t="n"/>
-      <c r="J7" s="175" t="n"/>
-      <c r="K7" s="175" t="n"/>
+      <c r="I7" s="140" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
+        </is>
+      </c>
       <c r="L7" s="175" t="n"/>
       <c r="M7" s="175" t="n"/>
       <c r="N7" s="175" t="n"/>
@@ -38224,9 +40817,21 @@
       <c r="F8" s="353" t="n"/>
       <c r="G8" s="175" t="n"/>
       <c r="H8" s="175" t="n"/>
-      <c r="I8" s="175" t="n"/>
-      <c r="J8" s="175" t="n"/>
-      <c r="K8" s="175" t="n"/>
+      <c r="I8" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/sd_card_dump/sd_card_01_manage_sd_warning.yaml</t>
+        </is>
+      </c>
       <c r="L8" s="175" t="n"/>
       <c r="M8" s="175" t="n"/>
       <c r="N8" s="175" t="n"/>
@@ -38253,9 +40858,17 @@
       <c r="F9" s="353" t="n"/>
       <c r="G9" s="175" t="n"/>
       <c r="H9" s="175" t="n"/>
-      <c r="I9" s="175" t="n"/>
-      <c r="J9" s="175" t="n"/>
-      <c r="K9" s="175" t="n"/>
+      <c r="I9" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="n"/>
       <c r="L9" s="175" t="n"/>
       <c r="M9" s="175" t="n"/>
       <c r="N9" s="175" t="n"/>
@@ -38283,9 +40896,17 @@
       <c r="F10" s="353" t="n"/>
       <c r="G10" s="175" t="n"/>
       <c r="H10" s="175" t="n"/>
-      <c r="I10" s="175" t="n"/>
-      <c r="J10" s="175" t="n"/>
-      <c r="K10" s="175" t="n"/>
+      <c r="I10" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="n"/>
       <c r="L10" s="175" t="n"/>
       <c r="M10" s="175" t="n"/>
       <c r="N10" s="175" t="n"/>
@@ -38314,9 +40935,17 @@
       <c r="F11" s="353" t="n"/>
       <c r="G11" s="175" t="n"/>
       <c r="H11" s="175" t="n"/>
-      <c r="I11" s="175" t="n"/>
-      <c r="J11" s="175" t="n"/>
-      <c r="K11" s="175" t="n"/>
+      <c r="I11" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="n"/>
       <c r="L11" s="175" t="n"/>
       <c r="M11" s="175" t="n"/>
       <c r="N11" s="175" t="n"/>
@@ -38346,9 +40975,17 @@
       <c r="F12" s="353" t="n"/>
       <c r="G12" s="175" t="n"/>
       <c r="H12" s="175" t="n"/>
-      <c r="I12" s="175" t="n"/>
-      <c r="J12" s="175" t="n"/>
-      <c r="K12" s="175" t="n"/>
+      <c r="I12" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="n"/>
       <c r="L12" s="175" t="n"/>
       <c r="M12" s="175" t="n"/>
       <c r="N12" s="175" t="n"/>
@@ -38379,9 +41016,17 @@
       <c r="F13" s="198" t="n"/>
       <c r="G13" s="175" t="n"/>
       <c r="H13" s="175" t="n"/>
-      <c r="I13" s="175" t="n"/>
-      <c r="J13" s="175" t="n"/>
-      <c r="K13" s="175" t="n"/>
+      <c r="I13" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="0" t="n"/>
       <c r="L13" s="175" t="n"/>
       <c r="M13" s="175" t="n"/>
       <c r="N13" s="175" t="n"/>
@@ -38409,9 +41054,17 @@
       <c r="F14" s="353" t="n"/>
       <c r="G14" s="175" t="n"/>
       <c r="H14" s="175" t="n"/>
-      <c r="I14" s="175" t="n"/>
-      <c r="J14" s="175" t="n"/>
-      <c r="K14" s="175" t="n"/>
+      <c r="I14" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" s="0" t="n"/>
       <c r="L14" s="175" t="n"/>
       <c r="M14" s="175" t="n"/>
       <c r="N14" s="175" t="n"/>
@@ -38439,9 +41092,17 @@
       <c r="F15" s="353" t="n"/>
       <c r="G15" s="175" t="n"/>
       <c r="H15" s="175" t="n"/>
-      <c r="I15" s="175" t="n"/>
-      <c r="J15" s="175" t="n"/>
-      <c r="K15" s="175" t="n"/>
+      <c r="I15" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K15" s="0" t="n"/>
       <c r="L15" s="175" t="n"/>
       <c r="M15" s="175" t="n"/>
       <c r="N15" s="175" t="n"/>
@@ -38469,9 +41130,17 @@
       <c r="F16" s="353" t="n"/>
       <c r="G16" s="175" t="n"/>
       <c r="H16" s="175" t="n"/>
-      <c r="I16" s="175" t="n"/>
-      <c r="J16" s="175" t="n"/>
-      <c r="K16" s="175" t="n"/>
+      <c r="I16" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" s="0" t="n"/>
       <c r="L16" s="175" t="n"/>
       <c r="M16" s="175" t="n"/>
       <c r="N16" s="175" t="n"/>
@@ -38500,9 +41169,17 @@
       <c r="F17" s="353" t="n"/>
       <c r="G17" s="175" t="n"/>
       <c r="H17" s="175" t="n"/>
-      <c r="I17" s="175" t="n"/>
-      <c r="J17" s="175" t="n"/>
-      <c r="K17" s="175" t="n"/>
+      <c r="I17" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K17" s="0" t="n"/>
       <c r="L17" s="175" t="n"/>
       <c r="M17" s="175" t="n"/>
       <c r="N17" s="175" t="n"/>
@@ -38533,9 +41210,17 @@
       <c r="F18" s="353" t="n"/>
       <c r="G18" s="175" t="n"/>
       <c r="H18" s="175" t="n"/>
-      <c r="I18" s="175" t="n"/>
-      <c r="J18" s="175" t="n"/>
-      <c r="K18" s="175" t="n"/>
+      <c r="I18" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" s="0" t="n"/>
       <c r="L18" s="175" t="n"/>
       <c r="M18" s="175" t="n"/>
       <c r="N18" s="175" t="n"/>
@@ -38564,9 +41249,17 @@
       <c r="F19" s="353" t="n"/>
       <c r="G19" s="175" t="n"/>
       <c r="H19" s="175" t="n"/>
-      <c r="I19" s="175" t="n"/>
-      <c r="J19" s="175" t="n"/>
-      <c r="K19" s="175" t="n"/>
+      <c r="I19" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K19" s="0" t="n"/>
       <c r="L19" s="175" t="n"/>
       <c r="M19" s="175" t="n"/>
       <c r="N19" s="175" t="n"/>
@@ -38595,9 +41288,17 @@
       <c r="F20" s="198" t="n"/>
       <c r="G20" s="175" t="n"/>
       <c r="H20" s="175" t="n"/>
-      <c r="I20" s="175" t="n"/>
-      <c r="J20" s="175" t="n"/>
-      <c r="K20" s="175" t="n"/>
+      <c r="I20" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K20" s="0" t="n"/>
       <c r="L20" s="175" t="n"/>
       <c r="M20" s="175" t="n"/>
       <c r="N20" s="175" t="n"/>
@@ -38633,9 +41334,17 @@
       <c r="F21" s="206" t="n"/>
       <c r="G21" s="175" t="n"/>
       <c r="H21" s="175" t="n"/>
-      <c r="I21" s="175" t="n"/>
-      <c r="J21" s="175" t="n"/>
-      <c r="K21" s="175" t="n"/>
+      <c r="I21" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J21" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K21" s="0" t="n"/>
       <c r="L21" s="175" t="n"/>
       <c r="M21" s="175" t="n"/>
       <c r="N21" s="175" t="n"/>
@@ -38663,9 +41372,17 @@
       <c r="F22" s="353" t="n"/>
       <c r="G22" s="175" t="n"/>
       <c r="H22" s="175" t="n"/>
-      <c r="I22" s="175" t="n"/>
-      <c r="J22" s="175" t="n"/>
-      <c r="K22" s="175" t="n"/>
+      <c r="I22" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J22" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K22" s="0" t="n"/>
       <c r="L22" s="175" t="n"/>
       <c r="M22" s="175" t="n"/>
       <c r="N22" s="175" t="n"/>
@@ -38695,9 +41412,17 @@
       <c r="F23" s="208" t="n"/>
       <c r="G23" s="175" t="n"/>
       <c r="H23" s="175" t="n"/>
-      <c r="I23" s="175" t="n"/>
-      <c r="J23" s="175" t="n"/>
-      <c r="K23" s="175" t="n"/>
+      <c r="I23" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J23" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" s="0" t="n"/>
       <c r="L23" s="175" t="n"/>
       <c r="M23" s="175" t="n"/>
       <c r="N23" s="175" t="n"/>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -33105,12 +33105,12 @@
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t>flows_non_core/advanced_settings/custom_properties_01_offer_pin_for_login.yaml (written; awaiting a passing run)</t>
+          <t>flows_non_core/advanced_settings/custom_properties_01_offer_pin_for_login.yaml</t>
         </is>
       </c>
     </row>
@@ -33686,7 +33686,7 @@
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t>flows_non_core/advanced_settings/custom_properties_15_root_menu_as_home_screen.yaml</t>
+          <t>flows_non_core/advanced_settings/custom_properties_15_root_menu_as_home_screen.yaml (CommCare 2.64 and earlier; skipped on 2.65+, which removed root-menu-as-home-screen)</t>
         </is>
       </c>
     </row>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -13251,17 +13251,17 @@
       <c r="G13" s="494" t="n"/>
       <c r="I13" s="140" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J13" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K13" s="0" t="inlineStr">
         <is>
-          <t>flows_non_core/printing/print_from_detail_01_02_case_detail_values.yaml</t>
+          <t>(Print from case detail is deprecated - confirmed 2026-10-23)</t>
         </is>
       </c>
     </row>
@@ -13287,17 +13287,17 @@
       <c r="G14" s="494" t="n"/>
       <c r="I14" s="140" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J14" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K14" s="0" t="inlineStr">
         <is>
-          <t>flows_non_core/printing/print_from_detail_01_02_case_detail_values.yaml</t>
+          <t>(Print from case detail is deprecated - confirmed 2026-10-23)</t>
         </is>
       </c>
     </row>
@@ -13323,17 +13323,17 @@
       <c r="G15" s="494" t="n"/>
       <c r="I15" s="140" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J15" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K15" s="0" t="inlineStr">
         <is>
-          <t>flows_non_core/printing/print_from_detail_03_print_case_detail.yaml</t>
+          <t>(Print from case detail is deprecated - confirmed 2026-10-23)</t>
         </is>
       </c>
     </row>
@@ -13360,7 +13360,7 @@
       <c r="G16" s="494" t="n"/>
       <c r="I16" s="140" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J16" s="0" t="inlineStr">
@@ -13368,7 +13368,11 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K16" s="0" t="n"/>
+      <c r="K16" s="0" t="inlineStr">
+        <is>
+          <t>(Print from case detail is deprecated - confirmed 2026-10-23)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -14398,7 +14402,7 @@
       </c>
       <c r="K28" s="0" t="inlineStr">
         <is>
-          <t>flows_non_core/graphing/graphing_20_22_user_info_report_graphs.yaml (blocked: app's mobile reports fixture not restored on HQ)</t>
+          <t>flows_non_core/graphing/graphing_20_22_user_info_report_graphs.yaml (blocked: app configuration issue on HQ, confirmed 2026-10-23 - needs the app fixed)</t>
         </is>
       </c>
     </row>
@@ -14472,7 +14476,7 @@
       </c>
       <c r="K30" s="0" t="inlineStr">
         <is>
-          <t>flows_non_core/graphing/graphing_20_22_user_info_report_graphs.yaml (blocked: app's mobile reports fixture not restored on HQ)</t>
+          <t>flows_non_core/graphing/graphing_20_22_user_info_report_graphs.yaml (blocked: app configuration issue on HQ, confirmed 2026-10-23 - needs the app fixed)</t>
         </is>
       </c>
     </row>
@@ -31896,7 +31900,7 @@
       <c r="F9" s="204" t="n"/>
       <c r="I9" s="140" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J9" s="0" t="inlineStr">
@@ -31904,7 +31908,11 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K9" s="0" t="n"/>
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>(Mapbox removed from CommCare in 2.59.0 - confirmed N/A 2026-10-23)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="387" t="inlineStr">
@@ -35121,7 +35129,11 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K2" s="0" t="n"/>
+      <c r="K2" s="0" t="inlineStr">
+        <is>
+          <t>(needs an SMS OTP - no test number receives one, confirmed 2026-10-23)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="603" t="inlineStr">
@@ -35154,7 +35166,11 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K3" s="0" t="n"/>
+      <c r="K3" s="0" t="inlineStr">
+        <is>
+          <t>(needs an SMS OTP - no test number receives one, confirmed 2026-10-23)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="603" t="inlineStr">
@@ -35186,7 +35202,11 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K4" s="0" t="n"/>
+      <c r="K4" s="0" t="inlineStr">
+        <is>
+          <t>(needs an SMS OTP - no test number receives one, confirmed 2026-10-23)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="603" t="inlineStr">
@@ -36326,7 +36346,11 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K38" s="0" t="n"/>
+      <c r="K38" s="0" t="inlineStr">
+        <is>
+          <t>(needs fingerprint enrollment - confirmed 2026-10-23)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="603" t="inlineStr">
@@ -36360,7 +36384,11 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K39" s="0" t="n"/>
+      <c r="K39" s="0" t="inlineStr">
+        <is>
+          <t>(needs fingerprint enrollment - confirmed 2026-10-23)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="603" t="inlineStr">
@@ -36393,7 +36421,11 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K40" s="0" t="n"/>
+      <c r="K40" s="0" t="inlineStr">
+        <is>
+          <t>(needs fingerprint enrollment - confirmed 2026-10-23)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="603" t="inlineStr">
@@ -36429,7 +36461,11 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K41" s="0" t="n"/>
+      <c r="K41" s="0" t="inlineStr">
+        <is>
+          <t>(needs fingerprint enrollment - confirmed 2026-10-23)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="603" t="inlineStr">
@@ -36462,7 +36498,11 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K42" s="0" t="n"/>
+      <c r="K42" s="0" t="inlineStr">
+        <is>
+          <t>(needs fingerprint enrollment - confirmed 2026-10-23)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="603" t="inlineStr">
@@ -36494,7 +36534,11 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K43" s="0" t="n"/>
+      <c r="K43" s="0" t="inlineStr">
+        <is>
+          <t>(needs fingerprint enrollment - confirmed 2026-10-23)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="603" t="inlineStr">

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -33509,12 +33509,12 @@
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t>flows_non_core/advanced_settings/custom_properties_11_update_target_release.yaml (run via scripts/run_targeted_updates_check.py; awaiting a passing run)</t>
+          <t>flows_non_core/advanced_settings/custom_properties_11_update_target_release.yaml (run via scripts/run_targeted_updates_check.py)</t>
         </is>
       </c>
     </row>
@@ -33551,12 +33551,12 @@
       </c>
       <c r="J19" s="0" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K19" s="0" t="inlineStr">
         <is>
-          <t>flows_non_core/advanced_settings/custom_properties_12_update_target_build.yaml (run via scripts/run_targeted_updates_check.py; awaiting a passing run)</t>
+          <t>flows_non_core/advanced_settings/custom_properties_12_update_target_build.yaml (run via scripts/run_targeted_updates_check.py)</t>
         </is>
       </c>
     </row>
@@ -33594,12 +33594,12 @@
       </c>
       <c r="J20" s="0" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K20" s="0" t="inlineStr">
         <is>
-          <t>flows_non_core/advanced_settings/custom_properties_13_update_target_save.yaml (run via scripts/run_targeted_updates_check.py; awaiting a passing run)</t>
+          <t>flows_non_core/advanced_settings/custom_properties_13_update_target_save.yaml (run via scripts/run_targeted_updates_check.py)</t>
         </is>
       </c>
     </row>
@@ -33636,12 +33636,12 @@
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t>flows_non_core/advanced_settings/custom_properties_14_pre_update_sync_needed.yaml (run via scripts/run_targeted_updates_check.py; awaiting a passing run)</t>
+          <t>flows_non_core/advanced_settings/custom_properties_14_pre_update_sync_needed.yaml (run via scripts/run_targeted_updates_check.py)</t>
         </is>
       </c>
     </row>
@@ -34098,12 +34098,12 @@
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t>scripts/run_appium_non_core_upgrade_suite.py --scenario performance_upgrade (awaiting a live run)</t>
+          <t>scripts/run_appium_non_core_upgrade_suite.py --scenario performance_upgrade (CommCare 2.45 -&gt; release, mid-session upgrade)</t>
         </is>
       </c>
     </row>
@@ -34134,12 +34134,12 @@
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t>scripts/run_appium_non_core_upgrade_suite.py --scenario performance_upgrade (awaiting a live run)</t>
+          <t>scripts/run_appium_non_core_upgrade_suite.py --scenario performance_upgrade (CommCare 2.45 -&gt; release, mid-session upgrade)</t>
         </is>
       </c>
     </row>
@@ -39500,12 +39500,12 @@
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t>scripts/run_appium_non_core_upgrade_suite.py --scenario database_change_upgrade (awaiting a live run)</t>
+          <t>scripts/run_appium_non_core_upgrade_suite.py --scenario database_change_upgrade (CommCare 2.45 -&gt; release, mid-session upgrade)</t>
         </is>
       </c>
       <c r="L8" s="166" t="n"/>
@@ -39776,12 +39776,12 @@
       </c>
       <c r="J15" s="0" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K15" s="0" t="inlineStr">
         <is>
-          <t>scripts/run_appium_non_core_upgrade_suite.py --scenario database_change_upgrade (awaiting a live run)</t>
+          <t>scripts/run_appium_non_core_upgrade_suite.py --scenario database_change_upgrade (CommCare 2.45 -&gt; release, mid-session upgrade)</t>
         </is>
       </c>
       <c r="L15" s="166" t="n"/>
@@ -39962,10 +39962,14 @@
       </c>
       <c r="J19" s="0" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K19" s="0" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K19" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/database_change/database_06_multimedia_form_saved.yaml</t>
+        </is>
+      </c>
       <c r="L19" s="166" t="n"/>
     </row>
     <row r="20">
@@ -40029,12 +40033,12 @@
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t>scripts/run_appium_non_core_upgrade_suite.py --scenario database_change_upgrade (awaiting a live run)</t>
+          <t>scripts/run_appium_non_core_upgrade_suite.py --scenario database_change_upgrade (CommCare 2.45 -&gt; release, mid-session upgrade)</t>
         </is>
       </c>
       <c r="L21" s="166" t="n"/>
@@ -40070,12 +40074,12 @@
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t>scripts/run_appium_non_core_upgrade_suite.py --scenario database_change_upgrade (awaiting a live run)</t>
+          <t>scripts/run_appium_non_core_upgrade_suite.py --scenario database_change_upgrade (CommCare 2.45 -&gt; release, mid-session upgrade)</t>
         </is>
       </c>
       <c r="L22" s="166" t="n"/>
@@ -40237,12 +40241,12 @@
       </c>
       <c r="J27" s="0" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K27" s="0" t="inlineStr">
         <is>
-          <t>scripts/run_appium_non_core_upgrade_suite.py --scenario database_change_upgrade (awaiting a live run)</t>
+          <t>scripts/run_appium_non_core_upgrade_suite.py --scenario database_change_upgrade (CommCare 2.45 -&gt; release, mid-session upgrade)</t>
         </is>
       </c>
       <c r="L27" s="166" t="n"/>
@@ -40343,12 +40347,12 @@
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t>scripts/run_appium_non_core_upgrade_suite.py --scenario database_change_upgrade (awaiting a live run)</t>
+          <t>scripts/run_appium_non_core_upgrade_suite.py --scenario database_change_upgrade (CommCare 2.45 -&gt; release, mid-session upgrade)</t>
         </is>
       </c>
       <c r="L29" s="166" t="n"/>
@@ -40575,10 +40579,14 @@
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K35" s="0" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K35" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/database_change/database_change_13_share_logs_gmail.yaml</t>
+        </is>
+      </c>
       <c r="L35" s="166" t="n"/>
     </row>
   </sheetData>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -14397,12 +14397,12 @@
       </c>
       <c r="J28" s="0" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K28" s="0" t="inlineStr">
         <is>
-          <t>flows_non_core/graphing/graphing_20_22_user_info_report_graphs.yaml (blocked: app configuration issue on HQ, confirmed 2026-10-23 - needs the app fixed)</t>
+          <t>flows_non_core/graphing/graphing_20_22_user_info_report_graphs.yaml (on the 'Graphing - Maestro Reports [DO NOT DELETE]' copy - the original app's graphs read the removed v1 report fixture)</t>
         </is>
       </c>
     </row>
@@ -14471,12 +14471,12 @@
       </c>
       <c r="J30" s="0" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K30" s="0" t="inlineStr">
         <is>
-          <t>flows_non_core/graphing/graphing_20_22_user_info_report_graphs.yaml (blocked: app configuration issue on HQ, confirmed 2026-10-23 - needs the app fixed)</t>
+          <t>flows_non_core/graphing/graphing_20_22_user_info_report_graphs.yaml (on the 'Graphing - Maestro Reports [DO NOT DELETE]' copy - the original app's graphs read the removed v1 report fixture)</t>
         </is>
       </c>
     </row>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -33694,7 +33694,7 @@
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t>flows_non_core/advanced_settings/custom_properties_15_root_menu_as_home_screen.yaml (CommCare 2.64 and earlier; skipped on 2.65+, which removed root-menu-as-home-screen)</t>
+          <t>flows_non_core/advanced_settings/custom_properties_15_root_menu_as_home_screen.yaml (CommCare 2.64 and earlier only; skipped on 2.65+, which removed root-menu-as-home-screen - mobile dev confirmed 2026-10-27 it is gone for good, so retire this row when 2.64 is no longer tested)</t>
         </is>
       </c>
     </row>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -6233,12 +6233,15 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.29" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="30.29" customWidth="1" style="629" min="2" max="2"/>
     <col width="50.43" customWidth="1" style="629" min="3" max="3"/>
     <col width="21.86" customWidth="1" style="629" min="5" max="6"/>
+    <col width="18" customWidth="1" style="629" min="9" max="9"/>
+    <col width="13" customWidth="1" style="629" min="10" max="10"/>
+    <col width="60" customWidth="1" style="629" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6366,6 +6369,21 @@
           <t>Ticket ID</t>
         </is>
       </c>
+      <c r="I7" s="140" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="479" t="inlineStr">
@@ -6387,6 +6405,21 @@
       <c r="D8" s="137" t="n"/>
       <c r="E8" s="479" t="n"/>
       <c r="F8" s="479" t="n"/>
+      <c r="I8" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/wifi_direct/wifi_01_change_modes_dialog.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="479" t="inlineStr">
@@ -6424,6 +6457,21 @@
         </is>
       </c>
       <c r="F9" s="497" t="n"/>
+      <c r="I9" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/wifi_direct/wifi_01_change_modes_dialog.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="479" t="inlineStr">
@@ -6452,6 +6500,17 @@
       <c r="D10" s="137" t="n"/>
       <c r="E10" s="479" t="n"/>
       <c r="F10" s="479" t="n"/>
+      <c r="I10" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="479" t="inlineStr">
@@ -6477,6 +6536,17 @@
       <c r="D11" s="137" t="n"/>
       <c r="E11" s="497" t="n"/>
       <c r="F11" s="497" t="n"/>
+      <c r="I11" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="479" t="inlineStr">
@@ -6511,6 +6581,17 @@
         </is>
       </c>
       <c r="F12" s="497" t="n"/>
+      <c r="I12" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="479" t="inlineStr">
@@ -6533,6 +6614,17 @@
       <c r="D13" s="137" t="n"/>
       <c r="E13" s="479" t="n"/>
       <c r="F13" s="479" t="n"/>
+      <c r="I13" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="0" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="479" t="inlineStr">
@@ -6555,6 +6647,17 @@
       <c r="D14" s="137" t="n"/>
       <c r="E14" s="479" t="n"/>
       <c r="F14" s="479" t="n"/>
+      <c r="I14" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" s="0" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="479" t="inlineStr">
@@ -6578,6 +6681,17 @@
       <c r="D15" s="137" t="n"/>
       <c r="E15" s="479" t="n"/>
       <c r="F15" s="479" t="n"/>
+      <c r="I15" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K15" s="0" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="479" t="inlineStr">
@@ -6602,6 +6716,17 @@
       <c r="D16" s="137" t="n"/>
       <c r="E16" s="479" t="n"/>
       <c r="F16" s="479" t="n"/>
+      <c r="I16" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" s="0" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -12305,12 +12430,15 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.29" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="18.71" customWidth="1" style="629" min="1" max="1"/>
     <col width="39.29" customWidth="1" style="629" min="2" max="2"/>
     <col width="52" customWidth="1" style="629" min="3" max="3"/>
+    <col width="18" customWidth="1" style="629" min="9" max="9"/>
+    <col width="13" customWidth="1" style="629" min="10" max="10"/>
+    <col width="60" customWidth="1" style="629" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12461,8 +12589,21 @@
         </is>
       </c>
       <c r="H7" s="166" t="n"/>
-      <c r="I7" s="166" t="n"/>
-      <c r="J7" s="166" t="n"/>
+      <c r="I7" s="140" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="455" t="inlineStr">
@@ -12498,8 +12639,21 @@
       <c r="F8" s="249" t="n"/>
       <c r="G8" s="249" t="n"/>
       <c r="H8" s="166" t="n"/>
-      <c r="I8" s="166" t="n"/>
-      <c r="J8" s="166" t="n"/>
+      <c r="I8" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/developer_options/do_01_enable_developer_options.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="455" t="inlineStr">
@@ -12527,8 +12681,21 @@
       <c r="F9" s="249" t="n"/>
       <c r="G9" s="249" t="n"/>
       <c r="H9" s="166" t="n"/>
-      <c r="I9" s="166" t="n"/>
-      <c r="J9" s="166" t="n"/>
+      <c r="I9" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/developer_options/do_01_enable_developer_options.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="455" t="inlineStr">
@@ -12562,8 +12729,21 @@
       <c r="F10" s="249" t="n"/>
       <c r="G10" s="249" t="n"/>
       <c r="H10" s="166" t="n"/>
-      <c r="I10" s="166" t="n"/>
-      <c r="J10" s="166" t="n"/>
+      <c r="I10" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/developer_options/do_01_enable_developer_options.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="455" t="inlineStr">
@@ -12586,8 +12766,21 @@
       <c r="F11" s="249" t="n"/>
       <c r="G11" s="249" t="n"/>
       <c r="H11" s="166" t="n"/>
-      <c r="I11" s="166" t="n"/>
-      <c r="J11" s="166" t="n"/>
+      <c r="I11" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="inlineStr">
+        <is>
+          <t>(covered by the Update tab's flows)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="455" t="inlineStr">
@@ -12615,8 +12808,21 @@
       <c r="F12" s="249" t="n"/>
       <c r="G12" s="249" t="n"/>
       <c r="H12" s="166" t="n"/>
-      <c r="I12" s="166" t="n"/>
-      <c r="J12" s="166" t="n"/>
+      <c r="I12" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/developer_options/do_03_image_above_text_enabled.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="455" t="inlineStr">
@@ -12645,8 +12851,21 @@
       <c r="F13" s="249" t="n"/>
       <c r="G13" s="249" t="n"/>
       <c r="H13" s="166" t="n"/>
-      <c r="I13" s="166" t="n"/>
-      <c r="J13" s="166" t="n"/>
+      <c r="I13" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K13" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/developer_options/do_04_image_above_text_disabled.yaml</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -12685,12 +12904,15 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.29" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="19.86" customWidth="1" style="629" min="1" max="1"/>
     <col width="21.14" customWidth="1" style="629" min="2" max="2"/>
     <col width="93.70999999999999" customWidth="1" style="629" min="3" max="3"/>
+    <col width="18" customWidth="1" style="629" min="9" max="9"/>
+    <col width="13" customWidth="1" style="629" min="10" max="10"/>
+    <col width="60" customWidth="1" style="629" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12811,6 +13033,21 @@
         </is>
       </c>
       <c r="G7" s="494" t="n"/>
+      <c r="I7" s="140" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="284" t="inlineStr">
@@ -12832,6 +13069,21 @@
       <c r="E8" s="468" t="n"/>
       <c r="F8" s="468" t="n"/>
       <c r="G8" s="494" t="n"/>
+      <c r="I8" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/printing/form_printing_01_04_print_from_form.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="284" t="inlineStr">
@@ -12855,6 +13107,21 @@
       <c r="E9" s="468" t="n"/>
       <c r="F9" s="468" t="n"/>
       <c r="G9" s="494" t="n"/>
+      <c r="I9" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/printing/form_printing_01_04_print_from_form.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="284" t="inlineStr">
@@ -12876,6 +13143,21 @@
       <c r="E10" s="468" t="n"/>
       <c r="F10" s="468" t="n"/>
       <c r="G10" s="494" t="n"/>
+      <c r="I10" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/printing/form_printing_01_04_print_from_form.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="284" t="inlineStr">
@@ -12898,6 +13180,21 @@
       <c r="E11" s="468" t="n"/>
       <c r="F11" s="468" t="n"/>
       <c r="G11" s="494" t="n"/>
+      <c r="I11" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/printing/form_printing_01_04_print_from_form.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="284" t="inlineStr">
@@ -12920,6 +13217,17 @@
       <c r="E12" s="468" t="n"/>
       <c r="F12" s="468" t="n"/>
       <c r="G12" s="494" t="n"/>
+      <c r="I12" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="284" t="inlineStr">
@@ -12941,6 +13249,21 @@
       <c r="E13" s="468" t="n"/>
       <c r="F13" s="468" t="n"/>
       <c r="G13" s="494" t="n"/>
+      <c r="I13" s="140" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="0" t="inlineStr">
+        <is>
+          <t>(Print from case detail is deprecated - confirmed 2026-10-23)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="284" t="inlineStr">
@@ -12962,6 +13285,21 @@
       <c r="E14" s="468" t="n"/>
       <c r="F14" s="468" t="n"/>
       <c r="G14" s="494" t="n"/>
+      <c r="I14" s="140" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" s="0" t="inlineStr">
+        <is>
+          <t>(Print from case detail is deprecated - confirmed 2026-10-23)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="284" t="inlineStr">
@@ -12983,6 +13321,21 @@
       <c r="E15" s="468" t="n"/>
       <c r="F15" s="468" t="n"/>
       <c r="G15" s="494" t="n"/>
+      <c r="I15" s="140" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K15" s="0" t="inlineStr">
+        <is>
+          <t>(Print from case detail is deprecated - confirmed 2026-10-23)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="387" t="inlineStr">
@@ -13005,6 +13358,21 @@
       <c r="E16" s="387" t="n"/>
       <c r="F16" s="387" t="n"/>
       <c r="G16" s="494" t="n"/>
+      <c r="I16" s="140" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" s="0" t="inlineStr">
+        <is>
+          <t>(Print from case detail is deprecated - confirmed 2026-10-23)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -13045,10 +13413,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.29" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="108.71" customWidth="1" style="629" min="3" max="3"/>
+    <col width="18" customWidth="1" style="629" min="9" max="9"/>
+    <col width="13" customWidth="1" style="629" min="10" max="10"/>
+    <col width="60" customWidth="1" style="629" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13191,7 +13562,21 @@
       </c>
       <c r="G7" s="494" t="n"/>
       <c r="H7" s="494" t="n"/>
-      <c r="I7" s="494" t="n"/>
+      <c r="I7" s="140" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="284" t="inlineStr">
@@ -13214,7 +13599,21 @@
       <c r="F8" s="468" t="n"/>
       <c r="G8" s="494" t="n"/>
       <c r="H8" s="494" t="n"/>
-      <c r="I8" s="494" t="n"/>
+      <c r="I8" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/graphing/graphing_01_05_19_create_case_points_view_and_remove.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="284" t="inlineStr">
@@ -13240,7 +13639,21 @@
       <c r="F9" s="468" t="n"/>
       <c r="G9" s="494" t="n"/>
       <c r="H9" s="494" t="n"/>
-      <c r="I9" s="494" t="n"/>
+      <c r="I9" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/graphing/graphing_01_05_19_create_case_points_view_and_remove.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="284" t="inlineStr">
@@ -13265,7 +13678,21 @@
       <c r="F10" s="468" t="n"/>
       <c r="G10" s="494" t="n"/>
       <c r="H10" s="494" t="n"/>
-      <c r="I10" s="494" t="n"/>
+      <c r="I10" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/graphing/graphing_01_05_19_create_case_points_view_and_remove.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="284" t="inlineStr">
@@ -13288,7 +13715,21 @@
       <c r="F11" s="468" t="n"/>
       <c r="G11" s="494" t="n"/>
       <c r="H11" s="494" t="n"/>
-      <c r="I11" s="494" t="n"/>
+      <c r="I11" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/graphing/graphing_01_05_19_create_case_points_view_and_remove.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="284" t="inlineStr">
@@ -13314,7 +13755,21 @@
       <c r="F12" s="468" t="n"/>
       <c r="G12" s="494" t="n"/>
       <c r="H12" s="494" t="n"/>
-      <c r="I12" s="494" t="n"/>
+      <c r="I12" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/graphing/graphing_01_05_19_create_case_points_view_and_remove.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="284" t="inlineStr">
@@ -13340,7 +13795,21 @@
       <c r="F13" s="468" t="n"/>
       <c r="G13" s="494" t="n"/>
       <c r="H13" s="494" t="n"/>
-      <c r="I13" s="494" t="n"/>
+      <c r="I13" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K13" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/graphing/graphing_01_05_19_create_case_points_view_and_remove.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="284" t="inlineStr">
@@ -13369,7 +13838,21 @@
       <c r="F14" s="468" t="n"/>
       <c r="G14" s="494" t="n"/>
       <c r="H14" s="494" t="n"/>
-      <c r="I14" s="494" t="n"/>
+      <c r="I14" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K14" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/graphing/graphing_06_xy_axis_labels.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="284" t="inlineStr">
@@ -13398,7 +13881,21 @@
       <c r="F15" s="468" t="n"/>
       <c r="G15" s="494" t="n"/>
       <c r="H15" s="494" t="n"/>
-      <c r="I15" s="494" t="n"/>
+      <c r="I15" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K15" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/graphing/graphing_07_11_graph_tabs_text.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="284" t="inlineStr">
@@ -13426,7 +13923,21 @@
       <c r="F16" s="468" t="n"/>
       <c r="G16" s="494" t="n"/>
       <c r="H16" s="494" t="n"/>
-      <c r="I16" s="494" t="n"/>
+      <c r="I16" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K16" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/graphing/graphing_07_11_graph_tabs_text.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="284" t="inlineStr">
@@ -13454,7 +13965,21 @@
       <c r="F17" s="468" t="n"/>
       <c r="G17" s="494" t="n"/>
       <c r="H17" s="494" t="n"/>
-      <c r="I17" s="494" t="n"/>
+      <c r="I17" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K17" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/graphing/graphing_07_11_graph_tabs_text.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="284" t="inlineStr">
@@ -13482,7 +14007,21 @@
       <c r="F18" s="468" t="n"/>
       <c r="G18" s="494" t="n"/>
       <c r="H18" s="494" t="n"/>
-      <c r="I18" s="494" t="n"/>
+      <c r="I18" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K18" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/graphing/graphing_07_11_graph_tabs_text.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="284" t="inlineStr">
@@ -13508,7 +14047,21 @@
       <c r="F19" s="468" t="n"/>
       <c r="G19" s="494" t="n"/>
       <c r="H19" s="494" t="n"/>
-      <c r="I19" s="494" t="n"/>
+      <c r="I19" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K19" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/graphing/graphing_07_11_graph_tabs_text.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="284" t="inlineStr">
@@ -13537,7 +14090,21 @@
       <c r="F20" s="468" t="n"/>
       <c r="G20" s="494" t="n"/>
       <c r="H20" s="494" t="n"/>
-      <c r="I20" s="494" t="n"/>
+      <c r="I20" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K20" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/graphing/graphing_12_double_tap_full_screen.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="284" t="inlineStr">
@@ -13562,7 +14129,17 @@
       <c r="F21" s="468" t="n"/>
       <c r="G21" s="494" t="n"/>
       <c r="H21" s="494" t="n"/>
-      <c r="I21" s="494" t="n"/>
+      <c r="I21" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J21" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K21" s="0" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="284" t="inlineStr">
@@ -13587,7 +14164,17 @@
       <c r="F22" s="468" t="n"/>
       <c r="G22" s="494" t="n"/>
       <c r="H22" s="494" t="n"/>
-      <c r="I22" s="494" t="n"/>
+      <c r="I22" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J22" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K22" s="0" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="284" t="inlineStr">
@@ -13612,7 +14199,17 @@
       <c r="F23" s="468" t="n"/>
       <c r="G23" s="494" t="n"/>
       <c r="H23" s="494" t="n"/>
-      <c r="I23" s="494" t="n"/>
+      <c r="I23" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J23" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" s="0" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="284" t="inlineStr">
@@ -13637,7 +14234,17 @@
       <c r="F24" s="468" t="n"/>
       <c r="G24" s="494" t="n"/>
       <c r="H24" s="494" t="n"/>
-      <c r="I24" s="494" t="n"/>
+      <c r="I24" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J24" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K24" s="0" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="284" t="inlineStr">
@@ -13662,7 +14269,17 @@
       <c r="F25" s="468" t="n"/>
       <c r="G25" s="494" t="n"/>
       <c r="H25" s="494" t="n"/>
-      <c r="I25" s="494" t="n"/>
+      <c r="I25" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J25" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K25" s="0" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="284" t="inlineStr">
@@ -13690,7 +14307,21 @@
       <c r="F26" s="468" t="n"/>
       <c r="G26" s="494" t="n"/>
       <c r="H26" s="494" t="n"/>
-      <c r="I26" s="494" t="n"/>
+      <c r="I26" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J26" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K26" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/graphing/graphing_18_remove_point_list.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="284" t="inlineStr">
@@ -13716,7 +14347,21 @@
       <c r="F27" s="468" t="n"/>
       <c r="G27" s="494" t="n"/>
       <c r="H27" s="494" t="n"/>
-      <c r="I27" s="494" t="n"/>
+      <c r="I27" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J27" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K27" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/graphing/graphing_01_05_19_create_case_points_view_and_remove.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="284" t="inlineStr">
@@ -13745,7 +14390,21 @@
       <c r="F28" s="468" t="n"/>
       <c r="G28" s="494" t="n"/>
       <c r="H28" s="494" t="n"/>
-      <c r="I28" s="494" t="n"/>
+      <c r="I28" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J28" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K28" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/graphing/graphing_20_22_user_info_report_graphs.yaml (on the 'Graphing - Maestro Reports [DO NOT DELETE]' copy - the original app's graphs read the removed v1 report fixture)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="284" t="inlineStr">
@@ -13770,7 +14429,17 @@
       <c r="F29" s="468" t="n"/>
       <c r="G29" s="494" t="n"/>
       <c r="H29" s="494" t="n"/>
-      <c r="I29" s="494" t="n"/>
+      <c r="I29" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J29" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K29" s="0" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="284" t="inlineStr">
@@ -13795,7 +14464,21 @@
       <c r="F30" s="468" t="n"/>
       <c r="G30" s="494" t="n"/>
       <c r="H30" s="494" t="n"/>
-      <c r="I30" s="494" t="n"/>
+      <c r="I30" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J30" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K30" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/graphing/graphing_20_22_user_info_report_graphs.yaml (on the 'Graphing - Maestro Reports [DO NOT DELETE]' copy - the original app's graphs read the removed v1 report fixture)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -26822,6 +27505,9 @@
     <col width="40" customWidth="1" style="629" min="2" max="2"/>
     <col width="82.70999999999999" customWidth="1" style="629" min="3" max="3"/>
     <col width="26.14" customWidth="1" style="629" min="6" max="6"/>
+    <col width="18" customWidth="1" style="629" min="9" max="9"/>
+    <col width="13" customWidth="1" style="629" min="10" max="10"/>
+    <col width="60" customWidth="1" style="629" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27057,9 +27743,21 @@
       </c>
       <c r="G7" s="507" t="n"/>
       <c r="H7" s="507" t="n"/>
-      <c r="I7" s="507" t="n"/>
-      <c r="J7" s="507" t="n"/>
-      <c r="K7" s="507" t="n"/>
+      <c r="I7" s="140" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
+        </is>
+      </c>
       <c r="L7" s="507" t="n"/>
       <c r="M7" s="507" t="n"/>
       <c r="N7" s="507" t="n"/>
@@ -27097,9 +27795,17 @@
       <c r="F8" s="526" t="n"/>
       <c r="G8" s="507" t="n"/>
       <c r="H8" s="507" t="n"/>
-      <c r="I8" s="507" t="n"/>
-      <c r="J8" s="507" t="n"/>
-      <c r="K8" s="507" t="n"/>
+      <c r="I8" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="n"/>
       <c r="L8" s="507" t="n"/>
       <c r="M8" s="507" t="n"/>
       <c r="N8" s="507" t="n"/>
@@ -27137,9 +27843,17 @@
       <c r="F9" s="526" t="n"/>
       <c r="G9" s="507" t="n"/>
       <c r="H9" s="507" t="n"/>
-      <c r="I9" s="507" t="n"/>
-      <c r="J9" s="507" t="n"/>
-      <c r="K9" s="529" t="inlineStr">
+      <c r="I9" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">       </t>
         </is>
@@ -27183,9 +27897,17 @@
       <c r="F10" s="526" t="n"/>
       <c r="G10" s="507" t="n"/>
       <c r="H10" s="507" t="n"/>
-      <c r="I10" s="507" t="n"/>
-      <c r="J10" s="507" t="n"/>
-      <c r="K10" s="507" t="n"/>
+      <c r="I10" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="n"/>
       <c r="L10" s="507" t="n"/>
       <c r="M10" s="507" t="n"/>
       <c r="N10" s="507" t="n"/>
@@ -27226,9 +27948,17 @@
       <c r="F11" s="526" t="n"/>
       <c r="G11" s="507" t="n"/>
       <c r="H11" s="507" t="n"/>
-      <c r="I11" s="507" t="n"/>
-      <c r="J11" s="507" t="n"/>
-      <c r="K11" s="507" t="n"/>
+      <c r="I11" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="n"/>
       <c r="L11" s="507" t="n"/>
       <c r="M11" s="507" t="n"/>
       <c r="N11" s="507" t="n"/>
@@ -27268,9 +27998,17 @@
       <c r="F12" s="526" t="n"/>
       <c r="G12" s="507" t="n"/>
       <c r="H12" s="507" t="n"/>
-      <c r="I12" s="507" t="n"/>
-      <c r="J12" s="507" t="n"/>
-      <c r="K12" s="507" t="n"/>
+      <c r="I12" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="n"/>
       <c r="L12" s="507" t="n"/>
       <c r="M12" s="507" t="n"/>
       <c r="N12" s="507" t="n"/>
@@ -27311,9 +28049,17 @@
       <c r="F13" s="526" t="n"/>
       <c r="G13" s="507" t="n"/>
       <c r="H13" s="507" t="n"/>
-      <c r="I13" s="507" t="n"/>
-      <c r="J13" s="507" t="n"/>
-      <c r="K13" s="507" t="n"/>
+      <c r="I13" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="0" t="n"/>
       <c r="L13" s="507" t="n"/>
       <c r="M13" s="507" t="n"/>
       <c r="N13" s="507" t="n"/>
@@ -27354,9 +28100,17 @@
       <c r="F14" s="526" t="n"/>
       <c r="G14" s="507" t="n"/>
       <c r="H14" s="507" t="n"/>
-      <c r="I14" s="507" t="n"/>
-      <c r="J14" s="507" t="n"/>
-      <c r="K14" s="507" t="n"/>
+      <c r="I14" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" s="0" t="n"/>
       <c r="L14" s="507" t="n"/>
       <c r="M14" s="507" t="n"/>
       <c r="N14" s="507" t="n"/>
@@ -27397,9 +28151,17 @@
       <c r="F15" s="526" t="n"/>
       <c r="G15" s="507" t="n"/>
       <c r="H15" s="507" t="n"/>
-      <c r="I15" s="507" t="n"/>
-      <c r="J15" s="507" t="n"/>
-      <c r="K15" s="507" t="n"/>
+      <c r="I15" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K15" s="0" t="n"/>
       <c r="L15" s="507" t="n"/>
       <c r="M15" s="507" t="n"/>
       <c r="N15" s="507" t="n"/>
@@ -27440,9 +28202,17 @@
       <c r="F16" s="526" t="n"/>
       <c r="G16" s="507" t="n"/>
       <c r="H16" s="507" t="n"/>
-      <c r="I16" s="507" t="n"/>
-      <c r="J16" s="507" t="n"/>
-      <c r="K16" s="507" t="n"/>
+      <c r="I16" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" s="0" t="n"/>
       <c r="L16" s="507" t="n"/>
       <c r="M16" s="507" t="n"/>
       <c r="N16" s="507" t="n"/>
@@ -27485,9 +28255,17 @@
       <c r="F17" s="526" t="n"/>
       <c r="G17" s="507" t="n"/>
       <c r="H17" s="507" t="n"/>
-      <c r="I17" s="507" t="n"/>
-      <c r="J17" s="507" t="n"/>
-      <c r="K17" s="507" t="n"/>
+      <c r="I17" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K17" s="0" t="n"/>
       <c r="L17" s="507" t="n"/>
       <c r="M17" s="507" t="n"/>
       <c r="N17" s="507" t="n"/>
@@ -27527,9 +28305,17 @@
       <c r="F18" s="526" t="n"/>
       <c r="G18" s="507" t="n"/>
       <c r="H18" s="507" t="n"/>
-      <c r="I18" s="507" t="n"/>
-      <c r="J18" s="507" t="n"/>
-      <c r="K18" s="507" t="n"/>
+      <c r="I18" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" s="0" t="n"/>
       <c r="L18" s="507" t="n"/>
       <c r="M18" s="507" t="n"/>
       <c r="N18" s="507" t="n"/>
@@ -27573,9 +28359,17 @@
       <c r="F19" s="526" t="n"/>
       <c r="G19" s="507" t="n"/>
       <c r="H19" s="507" t="n"/>
-      <c r="I19" s="507" t="n"/>
-      <c r="J19" s="507" t="n"/>
-      <c r="K19" s="507" t="n"/>
+      <c r="I19" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K19" s="0" t="n"/>
       <c r="L19" s="507" t="n"/>
       <c r="M19" s="507" t="n"/>
       <c r="N19" s="507" t="n"/>
@@ -27616,9 +28410,17 @@
       <c r="F20" s="526" t="n"/>
       <c r="G20" s="507" t="n"/>
       <c r="H20" s="507" t="n"/>
-      <c r="I20" s="507" t="n"/>
-      <c r="J20" s="507" t="n"/>
-      <c r="K20" s="507" t="n"/>
+      <c r="I20" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K20" s="0" t="n"/>
       <c r="L20" s="507" t="n"/>
       <c r="M20" s="507" t="n"/>
       <c r="N20" s="507" t="n"/>
@@ -27661,9 +28463,17 @@
       <c r="F21" s="198" t="n"/>
       <c r="G21" s="507" t="n"/>
       <c r="H21" s="507" t="n"/>
-      <c r="I21" s="507" t="n"/>
-      <c r="J21" s="507" t="n"/>
-      <c r="K21" s="507" t="n"/>
+      <c r="I21" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J21" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K21" s="0" t="n"/>
       <c r="L21" s="507" t="n"/>
       <c r="M21" s="507" t="n"/>
       <c r="N21" s="507" t="n"/>
@@ -27713,9 +28523,17 @@
       <c r="F22" s="198" t="n"/>
       <c r="G22" s="507" t="n"/>
       <c r="H22" s="507" t="n"/>
-      <c r="I22" s="507" t="n"/>
-      <c r="J22" s="507" t="n"/>
-      <c r="K22" s="507" t="n"/>
+      <c r="I22" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J22" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K22" s="0" t="n"/>
       <c r="L22" s="507" t="n"/>
       <c r="M22" s="507" t="n"/>
       <c r="N22" s="507" t="n"/>
@@ -27765,9 +28583,17 @@
       <c r="F23" s="198" t="n"/>
       <c r="G23" s="507" t="n"/>
       <c r="H23" s="507" t="n"/>
-      <c r="I23" s="507" t="n"/>
-      <c r="J23" s="507" t="n"/>
-      <c r="K23" s="507" t="n"/>
+      <c r="I23" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J23" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" s="0" t="n"/>
       <c r="L23" s="507" t="n"/>
       <c r="M23" s="507" t="n"/>
       <c r="N23" s="507" t="n"/>
@@ -30467,7 +31293,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.29" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="17.71" customWidth="1" style="629" min="1" max="1"/>
@@ -30476,6 +31302,9 @@
     <col width="21.57" customWidth="1" style="629" min="4" max="4"/>
     <col width="42.14" customWidth="1" style="629" min="5" max="5"/>
     <col width="43.57" customWidth="1" style="629" min="6" max="6"/>
+    <col width="18" customWidth="1" style="629" min="9" max="9"/>
+    <col width="13" customWidth="1" style="629" min="10" max="10"/>
+    <col width="60" customWidth="1" style="629" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30595,6 +31424,21 @@
         </is>
       </c>
       <c r="F7" s="204" t="n"/>
+      <c r="I7" s="140" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="521" t="inlineStr">
@@ -30621,6 +31465,17 @@
         </is>
       </c>
       <c r="F8" s="204" t="n"/>
+      <c r="I8" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="521" t="inlineStr">
@@ -30643,6 +31498,17 @@
       <c r="D9" s="564" t="n"/>
       <c r="E9" s="539" t="n"/>
       <c r="F9" s="204" t="n"/>
+      <c r="I9" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="521" t="inlineStr">
@@ -30671,6 +31537,17 @@
         </is>
       </c>
       <c r="F10" s="204" t="n"/>
+      <c r="I10" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="548" t="n"/>
@@ -30701,6 +31578,17 @@
         </is>
       </c>
       <c r="F12" s="204" t="n"/>
+      <c r="I12" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="521" t="inlineStr">
@@ -30719,6 +31607,17 @@
       <c r="D13" s="564" t="n"/>
       <c r="E13" s="349" t="n"/>
       <c r="F13" s="204" t="n"/>
+      <c r="I13" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="0" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="521" t="inlineStr">
@@ -30740,6 +31639,17 @@
       <c r="D14" s="564" t="n"/>
       <c r="E14" s="387" t="n"/>
       <c r="F14" s="204" t="n"/>
+      <c r="I14" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" s="0" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -30782,7 +31692,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.29" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="17.71" customWidth="1" style="629" min="1" max="1"/>
@@ -30791,6 +31701,9 @@
     <col width="21.57" customWidth="1" style="629" min="4" max="4"/>
     <col width="42.14" customWidth="1" style="629" min="5" max="5"/>
     <col width="43.57" customWidth="1" style="629" min="6" max="6"/>
+    <col width="18" customWidth="1" style="629" min="9" max="9"/>
+    <col width="13" customWidth="1" style="629" min="10" max="10"/>
+    <col width="60" customWidth="1" style="629" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30902,6 +31815,21 @@
       <c r="D7" s="537" t="n"/>
       <c r="E7" s="536" t="n"/>
       <c r="F7" s="204" t="n"/>
+      <c r="I7" s="140" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="387" t="inlineStr">
@@ -30927,6 +31855,21 @@
       <c r="D8" s="564" t="n"/>
       <c r="E8" s="539" t="n"/>
       <c r="F8" s="204" t="n"/>
+      <c r="I8" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/mapbox/mapbox_01_05_gps_capture_and_case_list.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="387" t="inlineStr">
@@ -30955,6 +31898,21 @@
       <c r="D9" s="564" t="n"/>
       <c r="E9" s="539" t="n"/>
       <c r="F9" s="204" t="n"/>
+      <c r="I9" s="140" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>(Mapbox removed from CommCare in 2.59.0 - confirmed N/A 2026-10-23)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="387" t="inlineStr">
@@ -30978,6 +31936,17 @@
       <c r="D10" s="564" t="n"/>
       <c r="E10" s="539" t="n"/>
       <c r="F10" s="204" t="n"/>
+      <c r="I10" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="387" t="inlineStr">
@@ -31001,6 +31970,21 @@
       <c r="D11" s="564" t="n"/>
       <c r="E11" s="539" t="n"/>
       <c r="F11" s="204" t="n"/>
+      <c r="I11" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/mapbox/mapbox_04_location_permission_denied.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="387" t="inlineStr">
@@ -31021,6 +32005,21 @@
       <c r="D12" s="564" t="n"/>
       <c r="E12" s="539" t="n"/>
       <c r="F12" s="204" t="n"/>
+      <c r="I12" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/mapbox/mapbox_01_05_gps_capture_and_case_list.yaml</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -31062,13 +32061,16 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.29" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="27.86" customWidth="1" style="629" min="1" max="1"/>
     <col width="28" customWidth="1" style="629" min="2" max="2"/>
     <col width="66.29000000000001" customWidth="1" style="629" min="3" max="3"/>
     <col width="24.57" customWidth="1" style="629" min="6" max="6"/>
+    <col width="18" customWidth="1" style="629" min="9" max="9"/>
+    <col width="13" customWidth="1" style="629" min="10" max="10"/>
+    <col width="60" customWidth="1" style="629" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31179,6 +32181,21 @@
         </is>
       </c>
       <c r="G6" s="535" t="n"/>
+      <c r="I6" s="140" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J6" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K6" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="556" t="inlineStr">
@@ -31217,6 +32234,21 @@
       <c r="E8" s="564" t="n"/>
       <c r="F8" s="564" t="n"/>
       <c r="G8" s="382" t="n"/>
+      <c r="I8" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/text_to_speech/tts_01_02_enable_and_audio_button.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="387" t="inlineStr">
@@ -31242,6 +32274,21 @@
       <c r="E9" s="564" t="n"/>
       <c r="F9" s="564" t="n"/>
       <c r="G9" s="382" t="n"/>
+      <c r="I9" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/text_to_speech/tts_01_02_enable_and_audio_button.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="387" t="inlineStr">
@@ -31268,6 +32315,21 @@
       <c r="E10" s="564" t="n"/>
       <c r="F10" s="564" t="n"/>
       <c r="G10" s="382" t="n"/>
+      <c r="I10" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/text_to_speech/tts_03_form_language_change.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="387" t="inlineStr">
@@ -31293,6 +32355,21 @@
       <c r="E11" s="564" t="n"/>
       <c r="F11" s="564" t="n"/>
       <c r="G11" s="382" t="n"/>
+      <c r="I11" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/text_to_speech/tts_04_app_language_change.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="387" t="inlineStr">
@@ -31328,6 +32405,17 @@
         </is>
       </c>
       <c r="G12" s="382" t="n"/>
+      <c r="I12" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="575" t="inlineStr">
@@ -31353,6 +32441,17 @@
       <c r="E13" s="578" t="n"/>
       <c r="F13" s="578" t="n"/>
       <c r="G13" s="382" t="n"/>
+      <c r="I13" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="0" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -31393,13 +32492,16 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.29" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="27.86" customWidth="1" style="629" min="1" max="1"/>
     <col width="28" customWidth="1" style="629" min="2" max="2"/>
     <col width="66.29000000000001" customWidth="1" style="629" min="3" max="3"/>
     <col width="24.57" customWidth="1" style="629" min="6" max="6"/>
+    <col width="18" customWidth="1" style="629" min="9" max="9"/>
+    <col width="13" customWidth="1" style="629" min="10" max="10"/>
+    <col width="60" customWidth="1" style="629" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31510,6 +32612,21 @@
         </is>
       </c>
       <c r="G6" s="535" t="n"/>
+      <c r="I6" s="140" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J6" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K6" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="561" t="inlineStr">
@@ -31546,6 +32663,17 @@
       <c r="E8" s="564" t="n"/>
       <c r="F8" s="564" t="n"/>
       <c r="G8" s="382" t="n"/>
+      <c r="I8" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="387" t="inlineStr">
@@ -31568,6 +32696,21 @@
       <c r="E9" s="564" t="n"/>
       <c r="F9" s="564" t="n"/>
       <c r="G9" s="382" t="n"/>
+      <c r="I9" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/third_party_scanner/scanner_02_06_intent_callout_setting.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="387" t="inlineStr">
@@ -31594,6 +32737,17 @@
       <c r="E10" s="564" t="n"/>
       <c r="F10" s="564" t="n"/>
       <c r="G10" s="382" t="n"/>
+      <c r="I10" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="387" t="inlineStr">
@@ -31616,6 +32770,17 @@
       <c r="E11" s="564" t="n"/>
       <c r="F11" s="564" t="n"/>
       <c r="G11" s="382" t="n"/>
+      <c r="I11" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="387" t="inlineStr">
@@ -31641,6 +32806,17 @@
       <c r="E12" s="564" t="n"/>
       <c r="F12" s="564" t="n"/>
       <c r="G12" s="382" t="n"/>
+      <c r="I12" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="387" t="inlineStr">
@@ -31665,6 +32841,21 @@
       <c r="E13" s="564" t="n"/>
       <c r="F13" s="564" t="n"/>
       <c r="G13" s="382" t="n"/>
+      <c r="I13" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K13" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/third_party_scanner/scanner_02_06_intent_callout_setting.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="387" t="inlineStr">
@@ -31690,6 +32881,17 @@
       <c r="E14" s="564" t="n"/>
       <c r="F14" s="564" t="n"/>
       <c r="G14" s="382" t="n"/>
+      <c r="I14" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" s="0" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -31731,7 +32933,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.29" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="25" customWidth="1" style="629" min="1" max="1"/>
@@ -31739,6 +32941,9 @@
     <col width="73" customWidth="1" style="629" min="3" max="3"/>
     <col width="20.43" customWidth="1" style="629" min="4" max="4"/>
     <col width="17.14" customWidth="1" style="629" min="5" max="6"/>
+    <col width="18" customWidth="1" style="629" min="9" max="9"/>
+    <col width="13" customWidth="1" style="629" min="10" max="10"/>
+    <col width="60" customWidth="1" style="629" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31844,6 +33049,21 @@
       <c r="F6" s="568" t="inlineStr">
         <is>
           <t>Notes</t>
+        </is>
+      </c>
+      <c r="I6" s="140" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J6" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K6" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
         </is>
       </c>
     </row>
@@ -31886,6 +33106,21 @@
       <c r="D8" s="477" t="n"/>
       <c r="E8" s="625" t="n"/>
       <c r="F8" s="625" t="n"/>
+      <c r="I8" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/advanced_settings/custom_properties_01_offer_pin_for_login.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="477" t="inlineStr">
@@ -31911,6 +33146,21 @@
       <c r="D9" s="477" t="n"/>
       <c r="E9" s="625" t="n"/>
       <c r="F9" s="625" t="n"/>
+      <c r="I9" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/advanced_settings/custom_properties_02_home_report.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="477" t="inlineStr">
@@ -31935,6 +33185,17 @@
       <c r="D10" s="477" t="n"/>
       <c r="E10" s="625" t="n"/>
       <c r="F10" s="625" t="n"/>
+      <c r="I10" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="477" t="inlineStr">
@@ -31962,6 +33223,21 @@
       <c r="D11" s="477" t="n"/>
       <c r="E11" s="625" t="n"/>
       <c r="F11" s="625" t="n"/>
+      <c r="I11" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/advanced_settings/custom_properties_04_superuser_developer_options.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="477" t="inlineStr">
@@ -31986,6 +33262,21 @@
       <c r="D12" s="477" t="n"/>
       <c r="E12" s="625" t="n"/>
       <c r="F12" s="625" t="n"/>
+      <c r="I12" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/advanced_settings/custom_properties_05_show_update_target_options.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="477" t="inlineStr">
@@ -32008,6 +33299,21 @@
       <c r="D13" s="477" t="n"/>
       <c r="E13" s="625" t="n"/>
       <c r="F13" s="625" t="n"/>
+      <c r="I13" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K13" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/advanced_settings/custom_properties_06_hide_issue_report.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="477" t="inlineStr">
@@ -32034,6 +33340,21 @@
       <c r="D14" s="477" t="n"/>
       <c r="E14" s="625" t="n"/>
       <c r="F14" s="625" t="n"/>
+      <c r="I14" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K14" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/advanced_settings/custom_properties_07_no_space_in_select_choices.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="477" t="inlineStr">
@@ -32059,6 +33380,21 @@
       <c r="D15" s="477" t="n"/>
       <c r="E15" s="625" t="n"/>
       <c r="F15" s="625" t="n"/>
+      <c r="I15" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K15" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/advanced_settings/custom_properties_08_alternate_question_text_format.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="477" t="inlineStr">
@@ -32084,6 +33420,21 @@
       <c r="D16" s="477" t="n"/>
       <c r="E16" s="625" t="n"/>
       <c r="F16" s="625" t="n"/>
+      <c r="I16" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K16" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/advanced_settings/custom_properties_09_detail_final_swipe_disabled.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="477" t="inlineStr">
@@ -32107,6 +33458,21 @@
       <c r="D17" s="477" t="n"/>
       <c r="E17" s="625" t="n"/>
       <c r="F17" s="625" t="n"/>
+      <c r="I17" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K17" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/advanced_settings/custom_properties_10_list_refresh.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="477" t="inlineStr">
@@ -32136,6 +33502,21 @@
       <c r="D18" s="477" t="n"/>
       <c r="E18" s="625" t="n"/>
       <c r="F18" s="625" t="n"/>
+      <c r="I18" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K18" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/advanced_settings/custom_properties_11_update_target_release.yaml (run via scripts/run_targeted_updates_check.py)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="477" t="inlineStr">
@@ -32163,6 +33544,21 @@
       <c r="D19" s="477" t="n"/>
       <c r="E19" s="625" t="n"/>
       <c r="F19" s="625" t="n"/>
+      <c r="I19" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K19" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/advanced_settings/custom_properties_12_update_target_build.yaml (run via scripts/run_targeted_updates_check.py)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="477" t="inlineStr">
@@ -32191,6 +33587,21 @@
       <c r="D20" s="477" t="n"/>
       <c r="E20" s="625" t="n"/>
       <c r="F20" s="625" t="n"/>
+      <c r="I20" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K20" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/advanced_settings/custom_properties_13_update_target_save.yaml (run via scripts/run_targeted_updates_check.py)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="477" t="inlineStr">
@@ -32218,6 +33629,21 @@
       <c r="D21" s="477" t="n"/>
       <c r="E21" s="625" t="n"/>
       <c r="F21" s="625" t="n"/>
+      <c r="I21" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J21" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K21" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/advanced_settings/custom_properties_14_pre_update_sync_needed.yaml (run via scripts/run_targeted_updates_check.py)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="477" t="inlineStr">
@@ -32254,6 +33680,21 @@
         <is>
           <t>Note: 
 Here the Incomplete Forms are not shown directly. Its seen under option 'Saved Forms' and filter update to 'Only Incomplete Forms'  then will show the incomplete forms.</t>
+        </is>
+      </c>
+      <c r="I22" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J22" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K22" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/advanced_settings/custom_properties_15_root_menu_as_home_screen.yaml (CommCare 2.64 and earlier only; skipped on 2.65+, which removed root-menu-as-home-screen - mobile dev confirmed 2026-10-27 it is gone for good, so retire this row when 2.64 is no longer tested)</t>
         </is>
       </c>
     </row>
@@ -32290,6 +33731,17 @@
       <c r="D23" s="477" t="n"/>
       <c r="E23" s="625" t="n"/>
       <c r="F23" s="625" t="n"/>
+      <c r="I23" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J23" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" s="0" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="628" t="inlineStr">
@@ -32326,6 +33778,21 @@
       <c r="D25" s="477" t="n"/>
       <c r="E25" s="625" t="n"/>
       <c r="F25" s="625" t="n"/>
+      <c r="I25" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J25" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K25" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/advanced_settings/settings_01_grid_menu_display.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="477" t="inlineStr">
@@ -32352,6 +33819,17 @@
       <c r="D26" s="477" t="n"/>
       <c r="E26" s="625" t="n"/>
       <c r="F26" s="625" t="n"/>
+      <c r="I26" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J26" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K26" s="0" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="477" t="inlineStr">
@@ -32377,6 +33855,17 @@
       <c r="D27" s="477" t="n"/>
       <c r="E27" s="625" t="n"/>
       <c r="F27" s="625" t="n"/>
+      <c r="I27" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J27" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K27" s="0" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="477" t="inlineStr">
@@ -32399,6 +33888,21 @@
       <c r="D28" s="477" t="n"/>
       <c r="E28" s="625" t="n"/>
       <c r="F28" s="625" t="n"/>
+      <c r="I28" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J28" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K28" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/advanced_settings/settings_04_asterisk_on_required_question.yaml</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -32445,13 +33949,16 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.29" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="34.43" customWidth="1" style="629" min="2" max="2"/>
     <col width="75.29000000000001" customWidth="1" style="629" min="3" max="3"/>
     <col width="24.14" customWidth="1" style="629" min="4" max="4"/>
     <col width="21.14" customWidth="1" style="629" min="5" max="5"/>
+    <col width="18" customWidth="1" style="629" min="9" max="9"/>
+    <col width="13" customWidth="1" style="629" min="10" max="10"/>
+    <col width="60" customWidth="1" style="629" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32547,6 +34054,21 @@
           <t>Notes/Ticket ID</t>
         </is>
       </c>
+      <c r="I6" s="140" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J6" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K6" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="580" t="inlineStr">
@@ -32569,6 +34091,21 @@
       </c>
       <c r="D7" s="580" t="n"/>
       <c r="E7" s="590" t="n"/>
+      <c r="I7" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>scripts/run_appium_non_core_upgrade_suite.py --scenario performance_upgrade (CommCare 2.45 -&gt; release, mid-session upgrade)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="580" t="inlineStr">
@@ -32590,6 +34127,21 @@
       </c>
       <c r="D8" s="580" t="n"/>
       <c r="E8" s="590" t="n"/>
+      <c r="I8" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>scripts/run_appium_non_core_upgrade_suite.py --scenario performance_upgrade (CommCare 2.45 -&gt; release, mid-session upgrade)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="591" t="inlineStr">
@@ -32615,6 +34167,21 @@
       <c r="E9" s="591" t="inlineStr">
         <is>
           <t>Comments (if any)</t>
+        </is>
+      </c>
+      <c r="I9" s="140" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
         </is>
       </c>
     </row>
@@ -32637,6 +34204,21 @@
       </c>
       <c r="D10" s="596" t="n"/>
       <c r="E10" s="596" t="n"/>
+      <c r="I10" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/performance_tests/perf_rows_01_02_login_screen_and_home_load.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="600" t="n">
@@ -32656,6 +34238,21 @@
       </c>
       <c r="D11" s="596" t="n"/>
       <c r="E11" s="596" t="n"/>
+      <c r="I11" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/performance_tests/perf_rows_01_02_login_screen_and_home_load.yaml</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -32697,13 +34294,16 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.29" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="34.43" customWidth="1" style="629" min="2" max="2"/>
     <col width="75.29000000000001" customWidth="1" style="629" min="3" max="3"/>
     <col width="24.14" customWidth="1" style="629" min="4" max="4"/>
     <col width="21.14" customWidth="1" style="629" min="5" max="6"/>
+    <col width="18" customWidth="1" style="629" min="9" max="9"/>
+    <col width="13" customWidth="1" style="629" min="10" max="10"/>
+    <col width="60" customWidth="1" style="629" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32840,6 +34440,21 @@
           <t>Ticket ID</t>
         </is>
       </c>
+      <c r="I8" s="140" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="198" t="inlineStr">
@@ -32863,6 +34478,21 @@
       <c r="D9" s="622" t="n"/>
       <c r="E9" s="622" t="n"/>
       <c r="F9" s="622" t="n"/>
+      <c r="I9" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/case_list_optimization/cache_index_01_02_sorting_and_filter_sorting.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="198" t="inlineStr">
@@ -32886,6 +34516,21 @@
       <c r="D10" s="622" t="n"/>
       <c r="E10" s="622" t="n"/>
       <c r="F10" s="622" t="n"/>
+      <c r="I10" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/case_list_optimization/cache_index_01_02_sorting_and_filter_sorting.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="198" t="inlineStr">
@@ -32908,6 +34553,21 @@
       <c r="D11" s="622" t="n"/>
       <c r="E11" s="622" t="n"/>
       <c r="F11" s="622" t="n"/>
+      <c r="I11" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/case_list_optimization/cache_index_01_02_sorting_and_filter_sorting.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="198" t="inlineStr">
@@ -32930,6 +34590,21 @@
       <c r="D12" s="622" t="n"/>
       <c r="E12" s="622" t="n"/>
       <c r="F12" s="622" t="n"/>
+      <c r="I12" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/case_list_optimization/cache_index_01_02_sorting_and_filter_sorting.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="622" t="n"/>
@@ -32969,6 +34644,21 @@
       <c r="D15" s="622" t="n"/>
       <c r="E15" s="622" t="n"/>
       <c r="F15" s="622" t="n"/>
+      <c r="I15" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K15" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/case_list_optimization/load_time_01_optimization_disabled.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="198" t="inlineStr">
@@ -32993,6 +34683,21 @@
       <c r="D16" s="622" t="n"/>
       <c r="E16" s="622" t="n"/>
       <c r="F16" s="622" t="n"/>
+      <c r="I16" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K16" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/case_list_optimization/load_time_01_optimization_disabled.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="198" t="inlineStr">
@@ -33016,6 +34721,21 @@
       <c r="D17" s="622" t="n"/>
       <c r="E17" s="622" t="n"/>
       <c r="F17" s="622" t="n"/>
+      <c r="I17" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K17" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/case_list_optimization/load_time_02_cache.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="198" t="inlineStr">
@@ -33039,6 +34759,21 @@
       <c r="D18" s="622" t="n"/>
       <c r="E18" s="622" t="n"/>
       <c r="F18" s="622" t="n"/>
+      <c r="I18" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K18" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/case_list_optimization/load_time_03_lazy_load.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="198" t="inlineStr">
@@ -33063,6 +34798,21 @@
       <c r="D19" s="622" t="n"/>
       <c r="E19" s="622" t="n"/>
       <c r="F19" s="622" t="n"/>
+      <c r="I19" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K19" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/case_list_optimization/load_time_04_cache_and_lazy_load.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="198" t="inlineStr">
@@ -33087,6 +34837,21 @@
       <c r="D20" s="622" t="n"/>
       <c r="E20" s="622" t="n"/>
       <c r="F20" s="622" t="n"/>
+      <c r="I20" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K20" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/case_list_optimization/load_time_05_all_mix.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="198" t="inlineStr">
@@ -33110,6 +34875,21 @@
       <c r="D21" s="622" t="n"/>
       <c r="E21" s="622" t="n"/>
       <c r="F21" s="622" t="n"/>
+      <c r="I21" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J21" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K21" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/case_list_optimization/load_time_06_after_clear_app_data.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="198" t="inlineStr">
@@ -33133,6 +34913,21 @@
       <c r="D22" s="622" t="n"/>
       <c r="E22" s="622" t="n"/>
       <c r="F22" s="622" t="n"/>
+      <c r="I22" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J22" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K22" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/case_list_optimization/load_time_07_after_force_stop.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="198" t="inlineStr">
@@ -33156,6 +34951,21 @@
       <c r="D23" s="622" t="n"/>
       <c r="E23" s="622" t="n"/>
       <c r="F23" s="622" t="n"/>
+      <c r="I23" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J23" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K23" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/case_list_optimization/load_time_08_second_login.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="622" t="inlineStr">
@@ -33176,6 +34986,17 @@
       <c r="D24" s="622" t="n"/>
       <c r="E24" s="622" t="n"/>
       <c r="F24" s="622" t="n"/>
+      <c r="I24" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J24" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K24" s="0" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -33214,13 +35035,16 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.29" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="48.71" customWidth="1" style="629" min="2" max="2"/>
     <col hidden="1" width="75.29000000000001" customWidth="1" style="629" min="3" max="3"/>
     <col width="61" customWidth="1" style="629" min="4" max="4"/>
     <col width="21.14" customWidth="1" style="629" min="5" max="7"/>
+    <col width="18" customWidth="1" style="629" min="9" max="9"/>
+    <col width="13" customWidth="1" style="629" min="10" max="10"/>
+    <col width="60" customWidth="1" style="629" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -33259,6 +35083,21 @@
           <t>Comments</t>
         </is>
       </c>
+      <c r="I1" s="140" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K1" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="603" t="inlineStr">
@@ -33280,6 +35119,21 @@
       <c r="E2" s="608" t="n"/>
       <c r="F2" s="609" t="n"/>
       <c r="G2" s="609" t="n"/>
+      <c r="I2" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J2" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K2" s="0" t="inlineStr">
+        <is>
+          <t>(needs an SMS OTP - no test number receives one, confirmed 2026-10-23)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="603" t="inlineStr">
@@ -33302,6 +35156,21 @@
       <c r="E3" s="608" t="n"/>
       <c r="F3" s="609" t="n"/>
       <c r="G3" s="609" t="n"/>
+      <c r="I3" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J3" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K3" s="0" t="inlineStr">
+        <is>
+          <t>(needs an SMS OTP - no test number receives one, confirmed 2026-10-23)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="603" t="inlineStr">
@@ -33323,6 +35192,21 @@
       <c r="E4" s="608" t="n"/>
       <c r="F4" s="609" t="n"/>
       <c r="G4" s="616" t="n"/>
+      <c r="I4" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J4" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K4" s="0" t="inlineStr">
+        <is>
+          <t>(needs an SMS OTP - no test number receives one, confirmed 2026-10-23)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="603" t="inlineStr">
@@ -33344,6 +35228,21 @@
       <c r="E5" s="608" t="n"/>
       <c r="F5" s="616" t="n"/>
       <c r="G5" s="616" t="n"/>
+      <c r="I5" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J5" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K5" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/personal_id/tc_04_sign_up_menu_option.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="603" t="inlineStr">
@@ -33370,6 +35269,17 @@
       <c r="E6" s="618" t="n"/>
       <c r="F6" s="616" t="n"/>
       <c r="G6" s="616" t="n"/>
+      <c r="I6" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J6" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" s="0" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="603" t="inlineStr">
@@ -33394,6 +35304,17 @@
       <c r="E7" s="618" t="n"/>
       <c r="F7" s="616" t="n"/>
       <c r="G7" s="616" t="n"/>
+      <c r="I7" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="603" t="inlineStr">
@@ -33415,6 +35336,17 @@
       <c r="E8" s="618" t="n"/>
       <c r="F8" s="616" t="n"/>
       <c r="G8" s="616" t="n"/>
+      <c r="I8" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="603" t="inlineStr">
@@ -33437,6 +35369,17 @@
       <c r="E9" s="618" t="n"/>
       <c r="F9" s="616" t="n"/>
       <c r="G9" s="616" t="n"/>
+      <c r="I9" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="603" t="inlineStr">
@@ -33458,6 +35401,17 @@
       <c r="E10" s="618" t="n"/>
       <c r="F10" s="616" t="n"/>
       <c r="G10" s="616" t="n"/>
+      <c r="I10" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="603" t="inlineStr">
@@ -33480,6 +35434,17 @@
       <c r="E11" s="618" t="n"/>
       <c r="F11" s="616" t="n"/>
       <c r="G11" s="616" t="n"/>
+      <c r="I11" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="603" t="inlineStr">
@@ -33503,6 +35468,17 @@
       <c r="E12" s="618" t="n"/>
       <c r="F12" s="618" t="n"/>
       <c r="G12" s="616" t="n"/>
+      <c r="I12" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="603" t="inlineStr">
@@ -33525,6 +35501,17 @@
       <c r="E13" s="618" t="n"/>
       <c r="F13" s="618" t="n"/>
       <c r="G13" s="616" t="n"/>
+      <c r="I13" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="0" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="603" t="inlineStr">
@@ -33546,6 +35533,17 @@
       <c r="E14" s="618" t="n"/>
       <c r="F14" s="616" t="n"/>
       <c r="G14" s="616" t="n"/>
+      <c r="I14" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" s="0" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="603" t="inlineStr">
@@ -33568,6 +35566,17 @@
       <c r="E15" s="618" t="n"/>
       <c r="F15" s="616" t="n"/>
       <c r="G15" s="616" t="n"/>
+      <c r="I15" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K15" s="0" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="603" t="inlineStr">
@@ -33589,6 +35598,17 @@
       <c r="E16" s="618" t="n"/>
       <c r="F16" s="616" t="n"/>
       <c r="G16" s="616" t="n"/>
+      <c r="I16" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" s="0" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="603" t="inlineStr">
@@ -33611,6 +35631,17 @@
       <c r="E17" s="618" t="n"/>
       <c r="F17" s="616" t="n"/>
       <c r="G17" s="616" t="n"/>
+      <c r="I17" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K17" s="0" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="603" t="inlineStr">
@@ -33633,6 +35664,17 @@
       <c r="E18" s="618" t="n"/>
       <c r="F18" s="616" t="n"/>
       <c r="G18" s="616" t="n"/>
+      <c r="I18" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" s="0" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="603" t="inlineStr">
@@ -33655,6 +35697,17 @@
       <c r="E19" s="618" t="n"/>
       <c r="F19" s="616" t="n"/>
       <c r="G19" s="616" t="n"/>
+      <c r="I19" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K19" s="0" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="603" t="inlineStr">
@@ -33678,6 +35731,17 @@
       <c r="E20" s="618" t="n"/>
       <c r="F20" s="616" t="n"/>
       <c r="G20" s="616" t="n"/>
+      <c r="I20" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K20" s="0" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="603" t="inlineStr">
@@ -33702,6 +35766,17 @@
       <c r="E21" s="618" t="n"/>
       <c r="F21" s="616" t="n"/>
       <c r="G21" s="616" t="n"/>
+      <c r="I21" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J21" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K21" s="0" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="603" t="inlineStr">
@@ -33724,6 +35799,17 @@
       <c r="E22" s="618" t="n"/>
       <c r="F22" s="616" t="n"/>
       <c r="G22" s="616" t="n"/>
+      <c r="I22" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J22" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K22" s="0" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="603" t="inlineStr">
@@ -33746,6 +35832,17 @@
       <c r="E23" s="618" t="n"/>
       <c r="F23" s="616" t="n"/>
       <c r="G23" s="616" t="n"/>
+      <c r="I23" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J23" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" s="0" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="603" t="inlineStr">
@@ -33769,6 +35866,17 @@
       <c r="E24" s="618" t="n"/>
       <c r="F24" s="616" t="n"/>
       <c r="G24" s="616" t="n"/>
+      <c r="I24" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J24" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K24" s="0" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="603" t="inlineStr">
@@ -33792,6 +35900,17 @@
       <c r="E25" s="618" t="n"/>
       <c r="F25" s="616" t="n"/>
       <c r="G25" s="616" t="n"/>
+      <c r="I25" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J25" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K25" s="0" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="603" t="inlineStr">
@@ -33814,6 +35933,17 @@
       <c r="E26" s="618" t="n"/>
       <c r="F26" s="616" t="n"/>
       <c r="G26" s="616" t="n"/>
+      <c r="I26" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J26" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K26" s="0" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="603" t="inlineStr">
@@ -33837,6 +35967,17 @@
       <c r="E27" s="618" t="n"/>
       <c r="F27" s="616" t="n"/>
       <c r="G27" s="616" t="n"/>
+      <c r="I27" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J27" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K27" s="0" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="603" t="inlineStr">
@@ -33859,6 +36000,17 @@
       <c r="E28" s="618" t="n"/>
       <c r="F28" s="616" t="n"/>
       <c r="G28" s="616" t="n"/>
+      <c r="I28" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J28" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K28" s="0" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="603" t="inlineStr">
@@ -33881,6 +36033,17 @@
       <c r="E29" s="618" t="n"/>
       <c r="F29" s="616" t="n"/>
       <c r="G29" s="616" t="n"/>
+      <c r="I29" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J29" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K29" s="0" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="603" t="inlineStr">
@@ -33904,6 +36067,17 @@
       <c r="E30" s="618" t="n"/>
       <c r="F30" s="616" t="n"/>
       <c r="G30" s="616" t="n"/>
+      <c r="I30" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J30" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K30" s="0" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="603" t="inlineStr">
@@ -33927,6 +36101,17 @@
       <c r="E31" s="618" t="n"/>
       <c r="F31" s="616" t="n"/>
       <c r="G31" s="616" t="n"/>
+      <c r="I31" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J31" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K31" s="0" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="603" t="inlineStr">
@@ -33949,6 +36134,17 @@
       <c r="E32" s="618" t="n"/>
       <c r="F32" s="616" t="n"/>
       <c r="G32" s="616" t="n"/>
+      <c r="I32" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J32" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K32" s="0" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="603" t="inlineStr">
@@ -33970,6 +36166,17 @@
       <c r="E33" s="618" t="n"/>
       <c r="F33" s="616" t="n"/>
       <c r="G33" s="616" t="n"/>
+      <c r="I33" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J33" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K33" s="0" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="603" t="inlineStr">
@@ -33991,6 +36198,17 @@
       <c r="E34" s="618" t="n"/>
       <c r="F34" s="616" t="n"/>
       <c r="G34" s="616" t="n"/>
+      <c r="I34" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J34" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K34" s="0" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="603" t="inlineStr">
@@ -34013,6 +36231,17 @@
       <c r="E35" s="618" t="n"/>
       <c r="F35" s="616" t="n"/>
       <c r="G35" s="616" t="n"/>
+      <c r="I35" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J35" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K35" s="0" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="603" t="inlineStr">
@@ -34039,6 +36268,17 @@
       <c r="E36" s="618" t="n"/>
       <c r="F36" s="616" t="n"/>
       <c r="G36" s="616" t="n"/>
+      <c r="I36" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J36" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K36" s="0" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="603" t="inlineStr">
@@ -34061,6 +36301,17 @@
       <c r="E37" s="618" t="n"/>
       <c r="F37" s="616" t="n"/>
       <c r="G37" s="616" t="n"/>
+      <c r="I37" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J37" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K37" s="0" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="603" t="inlineStr">
@@ -34085,6 +36336,21 @@
       <c r="E38" s="618" t="n"/>
       <c r="F38" s="616" t="n"/>
       <c r="G38" s="616" t="n"/>
+      <c r="I38" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J38" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K38" s="0" t="inlineStr">
+        <is>
+          <t>(needs fingerprint enrollment - confirmed 2026-10-23)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="603" t="inlineStr">
@@ -34108,6 +36374,21 @@
       <c r="E39" s="618" t="n"/>
       <c r="F39" s="616" t="n"/>
       <c r="G39" s="616" t="n"/>
+      <c r="I39" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J39" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K39" s="0" t="inlineStr">
+        <is>
+          <t>(needs fingerprint enrollment - confirmed 2026-10-23)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="603" t="inlineStr">
@@ -34130,6 +36411,21 @@
       <c r="E40" s="618" t="n"/>
       <c r="F40" s="616" t="n"/>
       <c r="G40" s="616" t="n"/>
+      <c r="I40" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J40" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K40" s="0" t="inlineStr">
+        <is>
+          <t>(needs fingerprint enrollment - confirmed 2026-10-23)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="603" t="inlineStr">
@@ -34155,6 +36451,21 @@
       <c r="E41" s="618" t="n"/>
       <c r="F41" s="616" t="n"/>
       <c r="G41" s="616" t="n"/>
+      <c r="I41" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J41" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K41" s="0" t="inlineStr">
+        <is>
+          <t>(needs fingerprint enrollment - confirmed 2026-10-23)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="603" t="inlineStr">
@@ -34177,6 +36488,21 @@
       <c r="E42" s="618" t="n"/>
       <c r="F42" s="616" t="n"/>
       <c r="G42" s="616" t="n"/>
+      <c r="I42" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J42" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K42" s="0" t="inlineStr">
+        <is>
+          <t>(needs fingerprint enrollment - confirmed 2026-10-23)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="603" t="inlineStr">
@@ -34198,6 +36524,21 @@
       <c r="E43" s="618" t="n"/>
       <c r="F43" s="616" t="n"/>
       <c r="G43" s="616" t="n"/>
+      <c r="I43" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J43" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K43" s="0" t="inlineStr">
+        <is>
+          <t>(needs fingerprint enrollment - confirmed 2026-10-23)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="603" t="inlineStr">
@@ -34222,6 +36563,17 @@
       <c r="E44" s="618" t="n"/>
       <c r="F44" s="616" t="n"/>
       <c r="G44" s="616" t="n"/>
+      <c r="I44" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J44" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K44" s="0" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="603" t="inlineStr">
@@ -34243,6 +36595,17 @@
       <c r="E45" s="618" t="n"/>
       <c r="F45" s="616" t="n"/>
       <c r="G45" s="616" t="n"/>
+      <c r="I45" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J45" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K45" s="0" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="603" t="inlineStr">
@@ -34266,6 +36629,17 @@
       <c r="E46" s="618" t="n"/>
       <c r="F46" s="616" t="n"/>
       <c r="G46" s="616" t="n"/>
+      <c r="I46" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J46" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K46" s="0" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="603" t="inlineStr">
@@ -34289,6 +36663,17 @@
       <c r="E47" s="618" t="n"/>
       <c r="F47" s="616" t="n"/>
       <c r="G47" s="616" t="n"/>
+      <c r="I47" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J47" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K47" s="0" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="603" t="inlineStr">
@@ -34310,6 +36695,17 @@
       <c r="E48" s="618" t="n"/>
       <c r="F48" s="616" t="n"/>
       <c r="G48" s="616" t="n"/>
+      <c r="I48" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J48" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K48" s="0" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -36879,6 +39275,9 @@
     <col width="17.43" customWidth="1" style="629" min="5" max="5"/>
     <col width="24" customWidth="1" style="629" min="6" max="7"/>
     <col width="32.14" customWidth="1" style="629" min="8" max="8"/>
+    <col width="18" customWidth="1" style="629" min="9" max="9"/>
+    <col width="13" customWidth="1" style="629" min="10" max="10"/>
+    <col width="60" customWidth="1" style="629" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37050,9 +39449,21 @@
         </is>
       </c>
       <c r="H7" s="159" t="n"/>
-      <c r="I7" s="45" t="n"/>
-      <c r="J7" s="45" t="n"/>
-      <c r="K7" s="45" t="n"/>
+      <c r="I7" s="140" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
+        </is>
+      </c>
       <c r="L7" s="45" t="n"/>
     </row>
     <row r="8">
@@ -37082,9 +39493,21 @@
       <c r="F8" s="521" t="n"/>
       <c r="G8" s="521" t="n"/>
       <c r="H8" s="166" t="n"/>
-      <c r="I8" s="166" t="n"/>
-      <c r="J8" s="166" t="n"/>
-      <c r="K8" s="166" t="n"/>
+      <c r="I8" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>scripts/run_appium_non_core_upgrade_suite.py --scenario database_change_upgrade (CommCare 2.45 -&gt; release, mid-session upgrade)</t>
+        </is>
+      </c>
       <c r="L8" s="166" t="n"/>
     </row>
     <row r="9">
@@ -37120,9 +39543,21 @@
       <c r="F9" s="521" t="n"/>
       <c r="G9" s="521" t="n"/>
       <c r="H9" s="166" t="n"/>
-      <c r="I9" s="166" t="n"/>
-      <c r="J9" s="166" t="n"/>
-      <c r="K9" s="166" t="n"/>
+      <c r="I9" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/database_change/database_change_10_12_change_logs.yaml</t>
+        </is>
+      </c>
       <c r="L9" s="166" t="n"/>
     </row>
     <row r="10">
@@ -37151,9 +39586,21 @@
       <c r="F10" s="521" t="n"/>
       <c r="G10" s="521" t="n"/>
       <c r="H10" s="166" t="n"/>
-      <c r="I10" s="166" t="n"/>
-      <c r="J10" s="166" t="n"/>
-      <c r="K10" s="166" t="n"/>
+      <c r="I10" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/database_change/database_change_10_12_change_logs.yaml</t>
+        </is>
+      </c>
       <c r="L10" s="166" t="n"/>
     </row>
     <row r="11">
@@ -37184,9 +39631,17 @@
       <c r="F11" s="521" t="n"/>
       <c r="G11" s="521" t="n"/>
       <c r="H11" s="166" t="n"/>
-      <c r="I11" s="166" t="n"/>
-      <c r="J11" s="166" t="n"/>
-      <c r="K11" s="166" t="n"/>
+      <c r="I11" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="n"/>
       <c r="L11" s="166" t="n"/>
     </row>
     <row r="12">
@@ -37269,9 +39724,17 @@
       <c r="F14" s="521" t="n"/>
       <c r="G14" s="521" t="n"/>
       <c r="H14" s="166" t="n"/>
-      <c r="I14" s="166" t="n"/>
-      <c r="J14" s="166" t="n"/>
-      <c r="K14" s="166" t="n"/>
+      <c r="I14" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" s="0" t="n"/>
       <c r="L14" s="166" t="n"/>
     </row>
     <row r="15">
@@ -37306,9 +39769,21 @@
       <c r="F15" s="521" t="n"/>
       <c r="G15" s="521" t="n"/>
       <c r="H15" s="166" t="n"/>
-      <c r="I15" s="166" t="n"/>
-      <c r="J15" s="166" t="n"/>
-      <c r="K15" s="166" t="n"/>
+      <c r="I15" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K15" s="0" t="inlineStr">
+        <is>
+          <t>scripts/run_appium_non_core_upgrade_suite.py --scenario database_change_upgrade (CommCare 2.45 -&gt; release, mid-session upgrade)</t>
+        </is>
+      </c>
       <c r="L15" s="166" t="n"/>
     </row>
     <row r="16">
@@ -37343,9 +39818,17 @@
       <c r="F16" s="521" t="n"/>
       <c r="G16" s="521" t="n"/>
       <c r="H16" s="166" t="n"/>
-      <c r="I16" s="166" t="n"/>
-      <c r="J16" s="166" t="n"/>
-      <c r="K16" s="166" t="n"/>
+      <c r="I16" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" s="0" t="n"/>
       <c r="L16" s="166" t="n"/>
     </row>
     <row r="17">
@@ -37379,9 +39862,17 @@
       <c r="F17" s="521" t="n"/>
       <c r="G17" s="521" t="n"/>
       <c r="H17" s="166" t="n"/>
-      <c r="I17" s="166" t="n"/>
-      <c r="J17" s="166" t="n"/>
-      <c r="K17" s="166" t="n"/>
+      <c r="I17" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K17" s="0" t="n"/>
       <c r="L17" s="166" t="n"/>
     </row>
     <row r="18">
@@ -37415,9 +39906,17 @@
       <c r="F18" s="521" t="n"/>
       <c r="G18" s="521" t="n"/>
       <c r="H18" s="166" t="n"/>
-      <c r="I18" s="166" t="n"/>
-      <c r="J18" s="166" t="n"/>
-      <c r="K18" s="166" t="n"/>
+      <c r="I18" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" s="0" t="n"/>
       <c r="L18" s="166" t="n"/>
     </row>
     <row r="19">
@@ -37456,9 +39955,21 @@
         </is>
       </c>
       <c r="H19" s="166" t="n"/>
-      <c r="I19" s="166" t="n"/>
-      <c r="J19" s="166" t="n"/>
-      <c r="K19" s="166" t="n"/>
+      <c r="I19" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K19" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/database_change/database_06_multimedia_form_saved.yaml</t>
+        </is>
+      </c>
       <c r="L19" s="166" t="n"/>
     </row>
     <row r="20">
@@ -37515,9 +40026,21 @@
       <c r="F21" s="521" t="n"/>
       <c r="G21" s="521" t="n"/>
       <c r="H21" s="166" t="n"/>
-      <c r="I21" s="166" t="n"/>
-      <c r="J21" s="166" t="n"/>
-      <c r="K21" s="166" t="n"/>
+      <c r="I21" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J21" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K21" s="0" t="inlineStr">
+        <is>
+          <t>scripts/run_appium_non_core_upgrade_suite.py --scenario database_change_upgrade (CommCare 2.45 -&gt; release, mid-session upgrade)</t>
+        </is>
+      </c>
       <c r="L21" s="166" t="n"/>
     </row>
     <row r="22">
@@ -37544,9 +40067,21 @@
       <c r="F22" s="521" t="n"/>
       <c r="G22" s="521" t="n"/>
       <c r="H22" s="166" t="n"/>
-      <c r="I22" s="166" t="n"/>
-      <c r="J22" s="166" t="n"/>
-      <c r="K22" s="166" t="n"/>
+      <c r="I22" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J22" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K22" s="0" t="inlineStr">
+        <is>
+          <t>scripts/run_appium_non_core_upgrade_suite.py --scenario database_change_upgrade (CommCare 2.45 -&gt; release, mid-session upgrade)</t>
+        </is>
+      </c>
       <c r="L22" s="166" t="n"/>
     </row>
     <row r="23">
@@ -37572,9 +40107,17 @@
       <c r="F23" s="521" t="n"/>
       <c r="G23" s="521" t="n"/>
       <c r="H23" s="166" t="n"/>
-      <c r="I23" s="166" t="n"/>
-      <c r="J23" s="166" t="n"/>
-      <c r="K23" s="166" t="n"/>
+      <c r="I23" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J23" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" s="0" t="n"/>
       <c r="L23" s="166" t="n"/>
     </row>
     <row r="24">
@@ -37600,9 +40143,17 @@
       <c r="F24" s="521" t="n"/>
       <c r="G24" s="521" t="n"/>
       <c r="H24" s="166" t="n"/>
-      <c r="I24" s="166" t="n"/>
-      <c r="J24" s="166" t="n"/>
-      <c r="K24" s="166" t="n"/>
+      <c r="I24" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J24" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K24" s="0" t="n"/>
       <c r="L24" s="166" t="n"/>
     </row>
     <row r="25">
@@ -37683,9 +40234,21 @@
       <c r="F27" s="521" t="n"/>
       <c r="G27" s="521" t="n"/>
       <c r="H27" s="166" t="n"/>
-      <c r="I27" s="166" t="n"/>
-      <c r="J27" s="166" t="n"/>
-      <c r="K27" s="166" t="n"/>
+      <c r="I27" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J27" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K27" s="0" t="inlineStr">
+        <is>
+          <t>scripts/run_appium_non_core_upgrade_suite.py --scenario database_change_upgrade (CommCare 2.45 -&gt; release, mid-session upgrade)</t>
+        </is>
+      </c>
       <c r="L27" s="166" t="n"/>
     </row>
     <row r="28">
@@ -37727,9 +40290,17 @@
       <c r="F28" s="195" t="n"/>
       <c r="G28" s="195" t="n"/>
       <c r="H28" s="166" t="n"/>
-      <c r="I28" s="166" t="n"/>
-      <c r="J28" s="166" t="n"/>
-      <c r="K28" s="166" t="n"/>
+      <c r="I28" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J28" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K28" s="0" t="n"/>
       <c r="L28" s="166" t="n"/>
     </row>
     <row r="29">
@@ -37769,9 +40340,21 @@
       <c r="F29" s="195" t="n"/>
       <c r="G29" s="195" t="n"/>
       <c r="H29" s="166" t="n"/>
-      <c r="I29" s="166" t="n"/>
-      <c r="J29" s="166" t="n"/>
-      <c r="K29" s="166" t="n"/>
+      <c r="I29" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J29" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K29" s="0" t="inlineStr">
+        <is>
+          <t>scripts/run_appium_non_core_upgrade_suite.py --scenario database_change_upgrade (CommCare 2.45 -&gt; release, mid-session upgrade)</t>
+        </is>
+      </c>
       <c r="L29" s="166" t="n"/>
     </row>
     <row r="30">
@@ -37848,9 +40431,21 @@
         </is>
       </c>
       <c r="H32" s="166" t="n"/>
-      <c r="I32" s="166" t="n"/>
-      <c r="J32" s="166" t="n"/>
-      <c r="K32" s="166" t="n"/>
+      <c r="I32" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J32" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K32" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/database_change/database_change_10_12_change_logs.yaml</t>
+        </is>
+      </c>
       <c r="L32" s="166" t="n"/>
     </row>
     <row r="33">
@@ -37886,9 +40481,21 @@
         </is>
       </c>
       <c r="H33" s="166" t="n"/>
-      <c r="I33" s="166" t="n"/>
-      <c r="J33" s="166" t="n"/>
-      <c r="K33" s="166" t="n"/>
+      <c r="I33" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J33" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K33" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/database_change/database_change_10_12_change_logs.yaml</t>
+        </is>
+      </c>
       <c r="L33" s="166" t="n"/>
     </row>
     <row r="34">
@@ -37921,9 +40528,21 @@
       <c r="F34" s="204" t="n"/>
       <c r="G34" s="204" t="n"/>
       <c r="H34" s="166" t="n"/>
-      <c r="I34" s="166" t="n"/>
-      <c r="J34" s="166" t="n"/>
-      <c r="K34" s="166" t="n"/>
+      <c r="I34" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J34" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K34" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/database_change/database_change_10_12_change_logs.yaml</t>
+        </is>
+      </c>
       <c r="L34" s="166" t="n"/>
     </row>
     <row r="35">
@@ -37953,9 +40572,21 @@
       <c r="F35" s="204" t="n"/>
       <c r="G35" s="204" t="n"/>
       <c r="H35" s="166" t="n"/>
-      <c r="I35" s="166" t="n"/>
-      <c r="J35" s="166" t="n"/>
-      <c r="K35" s="166" t="n"/>
+      <c r="I35" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J35" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K35" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/database_change/database_change_13_share_logs_gmail.yaml</t>
+        </is>
+      </c>
       <c r="L35" s="166" t="n"/>
     </row>
   </sheetData>
@@ -38011,7 +40642,9 @@
     <col width="30.71" customWidth="1" style="629" min="6" max="6"/>
     <col width="19" customWidth="1" style="629" min="7" max="7"/>
     <col width="29.43" customWidth="1" style="629" min="8" max="8"/>
-    <col width="8.710000000000001" customWidth="1" style="629" min="9" max="14"/>
+    <col width="18" customWidth="1" style="629" min="9" max="14"/>
+    <col width="13" customWidth="1" style="629" min="10" max="10"/>
+    <col width="60" customWidth="1" style="629" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1" s="629">
@@ -38192,9 +40825,21 @@
       </c>
       <c r="G7" s="183" t="n"/>
       <c r="H7" s="175" t="n"/>
-      <c r="I7" s="175" t="n"/>
-      <c r="J7" s="175" t="n"/>
-      <c r="K7" s="175" t="n"/>
+      <c r="I7" s="140" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
+        </is>
+      </c>
       <c r="L7" s="175" t="n"/>
       <c r="M7" s="175" t="n"/>
       <c r="N7" s="175" t="n"/>
@@ -38224,9 +40869,21 @@
       <c r="F8" s="353" t="n"/>
       <c r="G8" s="175" t="n"/>
       <c r="H8" s="175" t="n"/>
-      <c r="I8" s="175" t="n"/>
-      <c r="J8" s="175" t="n"/>
-      <c r="K8" s="175" t="n"/>
+      <c r="I8" s="140" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>flows_non_core/sd_card_dump/sd_card_01_manage_sd_warning.yaml</t>
+        </is>
+      </c>
       <c r="L8" s="175" t="n"/>
       <c r="M8" s="175" t="n"/>
       <c r="N8" s="175" t="n"/>
@@ -38253,9 +40910,17 @@
       <c r="F9" s="353" t="n"/>
       <c r="G9" s="175" t="n"/>
       <c r="H9" s="175" t="n"/>
-      <c r="I9" s="175" t="n"/>
-      <c r="J9" s="175" t="n"/>
-      <c r="K9" s="175" t="n"/>
+      <c r="I9" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="n"/>
       <c r="L9" s="175" t="n"/>
       <c r="M9" s="175" t="n"/>
       <c r="N9" s="175" t="n"/>
@@ -38283,9 +40948,17 @@
       <c r="F10" s="353" t="n"/>
       <c r="G10" s="175" t="n"/>
       <c r="H10" s="175" t="n"/>
-      <c r="I10" s="175" t="n"/>
-      <c r="J10" s="175" t="n"/>
-      <c r="K10" s="175" t="n"/>
+      <c r="I10" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="n"/>
       <c r="L10" s="175" t="n"/>
       <c r="M10" s="175" t="n"/>
       <c r="N10" s="175" t="n"/>
@@ -38314,9 +40987,17 @@
       <c r="F11" s="353" t="n"/>
       <c r="G11" s="175" t="n"/>
       <c r="H11" s="175" t="n"/>
-      <c r="I11" s="175" t="n"/>
-      <c r="J11" s="175" t="n"/>
-      <c r="K11" s="175" t="n"/>
+      <c r="I11" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="n"/>
       <c r="L11" s="175" t="n"/>
       <c r="M11" s="175" t="n"/>
       <c r="N11" s="175" t="n"/>
@@ -38346,9 +41027,17 @@
       <c r="F12" s="353" t="n"/>
       <c r="G12" s="175" t="n"/>
       <c r="H12" s="175" t="n"/>
-      <c r="I12" s="175" t="n"/>
-      <c r="J12" s="175" t="n"/>
-      <c r="K12" s="175" t="n"/>
+      <c r="I12" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="n"/>
       <c r="L12" s="175" t="n"/>
       <c r="M12" s="175" t="n"/>
       <c r="N12" s="175" t="n"/>
@@ -38379,9 +41068,17 @@
       <c r="F13" s="198" t="n"/>
       <c r="G13" s="175" t="n"/>
       <c r="H13" s="175" t="n"/>
-      <c r="I13" s="175" t="n"/>
-      <c r="J13" s="175" t="n"/>
-      <c r="K13" s="175" t="n"/>
+      <c r="I13" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="0" t="n"/>
       <c r="L13" s="175" t="n"/>
       <c r="M13" s="175" t="n"/>
       <c r="N13" s="175" t="n"/>
@@ -38409,9 +41106,17 @@
       <c r="F14" s="353" t="n"/>
       <c r="G14" s="175" t="n"/>
       <c r="H14" s="175" t="n"/>
-      <c r="I14" s="175" t="n"/>
-      <c r="J14" s="175" t="n"/>
-      <c r="K14" s="175" t="n"/>
+      <c r="I14" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" s="0" t="n"/>
       <c r="L14" s="175" t="n"/>
       <c r="M14" s="175" t="n"/>
       <c r="N14" s="175" t="n"/>
@@ -38439,9 +41144,17 @@
       <c r="F15" s="353" t="n"/>
       <c r="G15" s="175" t="n"/>
       <c r="H15" s="175" t="n"/>
-      <c r="I15" s="175" t="n"/>
-      <c r="J15" s="175" t="n"/>
-      <c r="K15" s="175" t="n"/>
+      <c r="I15" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K15" s="0" t="n"/>
       <c r="L15" s="175" t="n"/>
       <c r="M15" s="175" t="n"/>
       <c r="N15" s="175" t="n"/>
@@ -38469,9 +41182,17 @@
       <c r="F16" s="353" t="n"/>
       <c r="G16" s="175" t="n"/>
       <c r="H16" s="175" t="n"/>
-      <c r="I16" s="175" t="n"/>
-      <c r="J16" s="175" t="n"/>
-      <c r="K16" s="175" t="n"/>
+      <c r="I16" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" s="0" t="n"/>
       <c r="L16" s="175" t="n"/>
       <c r="M16" s="175" t="n"/>
       <c r="N16" s="175" t="n"/>
@@ -38500,9 +41221,17 @@
       <c r="F17" s="353" t="n"/>
       <c r="G17" s="175" t="n"/>
       <c r="H17" s="175" t="n"/>
-      <c r="I17" s="175" t="n"/>
-      <c r="J17" s="175" t="n"/>
-      <c r="K17" s="175" t="n"/>
+      <c r="I17" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K17" s="0" t="n"/>
       <c r="L17" s="175" t="n"/>
       <c r="M17" s="175" t="n"/>
       <c r="N17" s="175" t="n"/>
@@ -38533,9 +41262,17 @@
       <c r="F18" s="353" t="n"/>
       <c r="G18" s="175" t="n"/>
       <c r="H18" s="175" t="n"/>
-      <c r="I18" s="175" t="n"/>
-      <c r="J18" s="175" t="n"/>
-      <c r="K18" s="175" t="n"/>
+      <c r="I18" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" s="0" t="n"/>
       <c r="L18" s="175" t="n"/>
       <c r="M18" s="175" t="n"/>
       <c r="N18" s="175" t="n"/>
@@ -38564,9 +41301,17 @@
       <c r="F19" s="353" t="n"/>
       <c r="G19" s="175" t="n"/>
       <c r="H19" s="175" t="n"/>
-      <c r="I19" s="175" t="n"/>
-      <c r="J19" s="175" t="n"/>
-      <c r="K19" s="175" t="n"/>
+      <c r="I19" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K19" s="0" t="n"/>
       <c r="L19" s="175" t="n"/>
       <c r="M19" s="175" t="n"/>
       <c r="N19" s="175" t="n"/>
@@ -38595,9 +41340,17 @@
       <c r="F20" s="198" t="n"/>
       <c r="G20" s="175" t="n"/>
       <c r="H20" s="175" t="n"/>
-      <c r="I20" s="175" t="n"/>
-      <c r="J20" s="175" t="n"/>
-      <c r="K20" s="175" t="n"/>
+      <c r="I20" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K20" s="0" t="n"/>
       <c r="L20" s="175" t="n"/>
       <c r="M20" s="175" t="n"/>
       <c r="N20" s="175" t="n"/>
@@ -38633,9 +41386,17 @@
       <c r="F21" s="206" t="n"/>
       <c r="G21" s="175" t="n"/>
       <c r="H21" s="175" t="n"/>
-      <c r="I21" s="175" t="n"/>
-      <c r="J21" s="175" t="n"/>
-      <c r="K21" s="175" t="n"/>
+      <c r="I21" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J21" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K21" s="0" t="n"/>
       <c r="L21" s="175" t="n"/>
       <c r="M21" s="175" t="n"/>
       <c r="N21" s="175" t="n"/>
@@ -38663,9 +41424,17 @@
       <c r="F22" s="353" t="n"/>
       <c r="G22" s="175" t="n"/>
       <c r="H22" s="175" t="n"/>
-      <c r="I22" s="175" t="n"/>
-      <c r="J22" s="175" t="n"/>
-      <c r="K22" s="175" t="n"/>
+      <c r="I22" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J22" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K22" s="0" t="n"/>
       <c r="L22" s="175" t="n"/>
       <c r="M22" s="175" t="n"/>
       <c r="N22" s="175" t="n"/>
@@ -38695,9 +41464,17 @@
       <c r="F23" s="208" t="n"/>
       <c r="G23" s="175" t="n"/>
       <c r="H23" s="175" t="n"/>
-      <c r="I23" s="175" t="n"/>
-      <c r="J23" s="175" t="n"/>
-      <c r="K23" s="175" t="n"/>
+      <c r="I23" s="140" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J23" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" s="0" t="n"/>
       <c r="L23" s="175" t="n"/>
       <c r="M23" s="175" t="n"/>
       <c r="N23" s="175" t="n"/>
